--- a/document/成果物ドキュメント_タスク登録機能.xlsx
+++ b/document/成果物ドキュメント_タスク登録機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER124\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395EBB96-371E-4676-804C-1DA96CFE7A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F97BC3-48B2-421D-B2BA-8487C2348996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,17 @@
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書(登録)" sheetId="5" r:id="rId5"/>
-    <sheet name="画面設計書 (登録成功)" sheetId="7" r:id="rId6"/>
-    <sheet name="画面設計書(登録失敗)" sheetId="9" r:id="rId7"/>
+    <sheet name="画面設計書 (登録完了)" sheetId="7" r:id="rId6"/>
+    <sheet name="画面設計書(登録エラー)" sheetId="9" r:id="rId7"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="122">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -228,34 +229,6 @@
 エラーの原因がユーザ名が未入力である旨通知する</t>
   </si>
   <si>
-    <t>6a.システムが入力された内容をデータベースに登録できない場合
-6a1.システムがタスク登録失敗画面を表示する
-a.ログインセッションが切断された場合
-a1.システムがログイン失敗画面を表示する</t>
-    <rPh sb="29" eb="31">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="69" eb="71">
-      <t>セツダン</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="89" eb="91">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>例外フロー</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -277,91 +250,6 @@
     </rPh>
     <rPh sb="6" eb="9">
       <t>ジュウギョウイン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.ユーザーがメニュー画面を開く
-2.ユーザーが「タスク登録」ボタンを押下する
-3.システムがタスク登録画面を表示する
-4.ユーザーがタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを入力する
-5.ユーザーが「タスク登録」ボタンを押下する
-6.システムが入力された内容と現在日時をデータベースに登録する
-7.システムがタスク登録完了画面を表示する</t>
-    <rPh sb="11" eb="13">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="70" eb="71">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="82" eb="85">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="93" eb="95">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="99" eb="101">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="134" eb="136">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="139" eb="141">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="142" eb="144">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="144" eb="146">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="154" eb="156">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="169" eb="171">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="171" eb="173">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="173" eb="175">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="176" eb="178">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -574,16 +462,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>期限をカレンダーから選択する</t>
-    <rPh sb="0" eb="2">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>担当者をユーザー一覧から選択する</t>
     <rPh sb="0" eb="3">
       <t>タントウシャ</t>
@@ -641,10 +519,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>task-registrater-servlet</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>62期</t>
     <rPh sb="2" eb="3">
       <t>キ</t>
@@ -652,43 +526,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>Webブラウザ上でユーザが入力したタスクをデータベースに登録する</t>
-    <rPh sb="13" eb="15">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク登録成功画面</t>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>menu.jsp</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク登録失敗画面</t>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -712,6 +550,169 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Webブラウザ上でユーザが入力したタスクをDBに登録する</t>
+    <rPh sb="13" eb="15">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-register-servlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザーがメニュー画面のタスク登録を選択する
+2.システムがタスク登録画面を表示する
+3.ユーザーがタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを入力する
+4.ユーザーがタスク登録を確定する
+5.システムが入力された内容と現在日時をデータベースに登録する
+6.システムがタスク登録完了画面を表示する</t>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="67" eb="70">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="119" eb="121">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="124" eb="126">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="151" eb="153">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="153" eb="155">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク登録完了画面</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク登録エラー画面</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>期限をカレンダーから選択する
+カレンダーに過去の日付は表示されないようにする</t>
+    <rPh sb="0" eb="2">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>(空文字)</t>
+    <rPh sb="1" eb="4">
+      <t>カラモジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>(空文字)</t>
+    <rPh sb="0" eb="3">
+      <t>カラモジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>6a.システムが入力された内容をデータベースに登録できない場合
+6a1.システムがタスク登録エラー画面を表示する</t>
+    <rPh sb="29" eb="31">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1470,7 +1471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1591,35 +1592,56 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1633,83 +1655,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1726,65 +1742,53 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1798,11 +1802,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1810,47 +1820,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1874,22 +1857,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1070040</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>113029</xdr:rowOff>
+      <xdr:colOff>676956</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161159</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>170795</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>37353</xdr:rowOff>
+      <xdr:colOff>1074964</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>35241</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D730C0EC-D51E-5ED0-ABD6-E151EE538386}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48A278B9-7AB9-AF77-7ABE-B21391CB6A44}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1912,8 +1895,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2078569" y="1849941"/>
-          <a:ext cx="3583108" cy="2613736"/>
+          <a:off x="1697492" y="1576302"/>
+          <a:ext cx="4861151" cy="3466368"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1940,22 +1923,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>277311</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>62783</xdr:rowOff>
+      <xdr:rowOff>110434</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>687247</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>104888</xdr:rowOff>
+      <xdr:colOff>386522</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>16209</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EAED95F-F40B-1F82-F9FA-00B6E039D3DC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD77C3F9-81F7-F769-7BEE-43D1F98A46AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1978,8 +1961,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="277311" y="979112"/>
-          <a:ext cx="8078164" cy="4430839"/>
+          <a:off x="0" y="1049130"/>
+          <a:ext cx="8130761" cy="4709688"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2396,85 +2379,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="60"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="60"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="53"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="60"/>
+      <c r="O6" s="60"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2494,46 +2477,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="84" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
+      <c r="E8" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="60"/>
+      <c r="M8" s="60"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="80" t="s">
+      <c r="G13" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="63"/>
-      <c r="I13" s="80" t="s">
+      <c r="H13" s="68"/>
+      <c r="I13" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="62"/>
-      <c r="K13" s="63"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="68"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="80"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="63"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="68"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="80"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="63"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="68"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2542,13 +2525,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="81" t="s">
+      <c r="G17" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="53"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3562,19 +3545,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3586,192 +3569,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="84">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="87">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="46" t="s">
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="51"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="49"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="51"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="47"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="48"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="89"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="96" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="100" t="s">
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="52"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="51"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="52"/>
+    </row>
+    <row r="9" spans="1:10" ht="114" customHeight="1">
+      <c r="A9" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="68"/>
+      <c r="D9" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="52"/>
+    </row>
+    <row r="10" spans="1:10" ht="56.25" customHeight="1">
+      <c r="A10" s="70"/>
+      <c r="B10" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="68"/>
+      <c r="D10" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="52"/>
+    </row>
+    <row r="11" spans="1:10" ht="56.25" customHeight="1">
+      <c r="A11" s="71"/>
+      <c r="B11" s="72" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="68"/>
+      <c r="D11" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="52"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="51"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="66"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="91" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="101" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="103"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="91" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="72" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="67"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="91" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="67"/>
-    </row>
-    <row r="9" spans="1:10" ht="114" customHeight="1">
-      <c r="A9" s="97" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="90" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="104" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="67"/>
-    </row>
-    <row r="10" spans="1:10" ht="65.25" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="104" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="67"/>
-    </row>
-    <row r="11" spans="1:10" ht="82.5" customHeight="1">
-      <c r="A11" s="99"/>
-      <c r="B11" s="90" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="104" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="67"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="91" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="67"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="52"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="92" t="s">
+      <c r="A13" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="75"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="43"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4762,6 +4745,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4770,25 +4772,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4807,19 +4790,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4831,48 +4814,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="90">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="44">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="47"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="48"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="89"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6227,19 +6210,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6251,48 +6234,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="90">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="44">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="47"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="48"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="89"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7643,19 +7626,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7667,203 +7650,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="90">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="44">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="47"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="48"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="48"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="65" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="66"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="100" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="52"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="68"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="70"/>
+      <c r="A7" s="101"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="103"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="71"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="104"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="71"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="104"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="71"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="104"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="52"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="71"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="104"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="52"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="71"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="104"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="52"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="71"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="104"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="67"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="52"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="68"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="61" t="s">
+      <c r="A16" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="63"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="68"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -7876,187 +7859,191 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="73" t="s">
+      <c r="H16" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="52"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="92" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="I17" s="51"/>
+      <c r="J17" s="52"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="92" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="51"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" s="51"/>
+      <c r="J18" s="52"/>
+    </row>
+    <row r="19" spans="1:10" ht="29.25" customHeight="1">
+      <c r="A19" s="92" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="17" t="s">
+      <c r="B19" s="51"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="72" t="s">
+      <c r="E19" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="120" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="I19" s="51"/>
+      <c r="J19" s="52"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="92" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="51"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="18"/>
+      <c r="H20" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="I17" s="62"/>
-      <c r="J17" s="67"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="18"/>
-      <c r="H18" s="72" t="s">
+      <c r="I20" s="51"/>
+      <c r="J20" s="52"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="92" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="51"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="18"/>
+      <c r="H21" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="I18" s="62"/>
-      <c r="J18" s="67"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="64" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="62"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="18"/>
-      <c r="H19" s="72" t="s">
+      <c r="I21" s="51"/>
+      <c r="J21" s="52"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="92" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="51"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="I19" s="62"/>
-      <c r="J19" s="67"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="62"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20" s="18"/>
-      <c r="H20" s="72" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" s="62"/>
-      <c r="J20" s="67"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="64" t="s">
+      <c r="I22" s="51"/>
+      <c r="J22" s="52"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="62"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="F21" s="18" t="s">
+      <c r="B23" s="93"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="18"/>
-      <c r="H21" s="72" t="s">
-        <v>106</v>
-      </c>
-      <c r="I21" s="62"/>
-      <c r="J21" s="67"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="G22" s="18"/>
-      <c r="H22" s="72" t="s">
-        <v>107</v>
-      </c>
-      <c r="I22" s="62"/>
-      <c r="J22" s="67"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="64" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="76"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="38" t="s">
-        <v>100</v>
-      </c>
       <c r="E23" s="38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F23" s="39"/>
       <c r="G23" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="H23" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="I23" s="78"/>
-      <c r="J23" s="79"/>
+        <v>98</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="58" t="s">
+      <c r="A24" s="98" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="42"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>96</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="H24" s="74" t="s">
-        <v>109</v>
-      </c>
-      <c r="I24" s="59"/>
-      <c r="J24" s="75"/>
+        <v>93</v>
+      </c>
+      <c r="H24" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="I24" s="42"/>
+      <c r="J24" s="43"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9037,18 +9024,11 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9065,11 +9045,18 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H24:J24"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9093,19 +9080,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="57" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -9117,203 +9104,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="90">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="44">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="47"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="48"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="48"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="65" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="66"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="100" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="52"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="68"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="70"/>
+      <c r="A7" s="101"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="103"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="71"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="104"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="71"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="104"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="71"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="104"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="52"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="71"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="104"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="52"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="71"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="104"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="52"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="71"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="104"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="67"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="52"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="72" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="68"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="61" t="s">
+      <c r="A16" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="63"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="68"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -9326,1341 +9313,45 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="73" t="s">
+      <c r="H16" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="52"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="121" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="119"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="120" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="120" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="120"/>
-      <c r="G17" s="126" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" s="123" t="s">
-        <v>109</v>
-      </c>
-      <c r="I17" s="124"/>
-      <c r="J17" s="125"/>
+      <c r="A17" s="92" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="93"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="38"/>
+      <c r="G17" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" s="95"/>
+      <c r="J17" s="96"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="58"/>
-      <c r="B18" s="105"/>
-      <c r="C18" s="106"/>
+      <c r="A18" s="98"/>
+      <c r="B18" s="106"/>
+      <c r="C18" s="107"/>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="108"/>
-    </row>
-    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="33" ht="12.75" customHeight="1"/>
-    <row r="34" ht="12.75" customHeight="1"/>
-    <row r="35" ht="12.75" customHeight="1"/>
-    <row r="36" ht="12.75" customHeight="1"/>
-    <row r="37" ht="12.75" customHeight="1"/>
-    <row r="38" ht="12.75" customHeight="1"/>
-    <row r="39" ht="12.75" customHeight="1"/>
-    <row r="40" ht="12.75" customHeight="1"/>
-    <row r="41" ht="12.75" customHeight="1"/>
-    <row r="42" ht="12.75" customHeight="1"/>
-    <row r="43" ht="12.75" customHeight="1"/>
-    <row r="44" ht="12.75" customHeight="1"/>
-    <row r="45" ht="12.75" customHeight="1"/>
-    <row r="46" ht="12.75" customHeight="1"/>
-    <row r="47" ht="12.75" customHeight="1"/>
-    <row r="48" ht="12.75" customHeight="1"/>
-    <row r="49" ht="12.75" customHeight="1"/>
-    <row r="50" ht="12.75" customHeight="1"/>
-    <row r="51" ht="12.75" customHeight="1"/>
-    <row r="52" ht="12.75" customHeight="1"/>
-    <row r="53" ht="12.75" customHeight="1"/>
-    <row r="54" ht="12.75" customHeight="1"/>
-    <row r="55" ht="12.75" customHeight="1"/>
-    <row r="56" ht="12.75" customHeight="1"/>
-    <row r="57" ht="12.75" customHeight="1"/>
-    <row r="58" ht="12.75" customHeight="1"/>
-    <row r="59" ht="12.75" customHeight="1"/>
-    <row r="60" ht="12.75" customHeight="1"/>
-    <row r="61" ht="12.75" customHeight="1"/>
-    <row r="62" ht="12.75" customHeight="1"/>
-    <row r="63" ht="12.75" customHeight="1"/>
-    <row r="64" ht="12.75" customHeight="1"/>
-    <row r="65" ht="12.75" customHeight="1"/>
-    <row r="66" ht="12.75" customHeight="1"/>
-    <row r="67" ht="12.75" customHeight="1"/>
-    <row r="68" ht="12.75" customHeight="1"/>
-    <row r="69" ht="12.75" customHeight="1"/>
-    <row r="70" ht="12.75" customHeight="1"/>
-    <row r="71" ht="12.75" customHeight="1"/>
-    <row r="72" ht="12.75" customHeight="1"/>
-    <row r="73" ht="12.75" customHeight="1"/>
-    <row r="74" ht="12.75" customHeight="1"/>
-    <row r="75" ht="12.75" customHeight="1"/>
-    <row r="76" ht="12.75" customHeight="1"/>
-    <row r="77" ht="12.75" customHeight="1"/>
-    <row r="78" ht="12.75" customHeight="1"/>
-    <row r="79" ht="12.75" customHeight="1"/>
-    <row r="80" ht="12.75" customHeight="1"/>
-    <row r="81" ht="12.75" customHeight="1"/>
-    <row r="82" ht="12.75" customHeight="1"/>
-    <row r="83" ht="12.75" customHeight="1"/>
-    <row r="84" ht="12.75" customHeight="1"/>
-    <row r="85" ht="12.75" customHeight="1"/>
-    <row r="86" ht="12.75" customHeight="1"/>
-    <row r="87" ht="12.75" customHeight="1"/>
-    <row r="88" ht="12.75" customHeight="1"/>
-    <row r="89" ht="12.75" customHeight="1"/>
-    <row r="90" ht="12.75" customHeight="1"/>
-    <row r="91" ht="12.75" customHeight="1"/>
-    <row r="92" ht="12.75" customHeight="1"/>
-    <row r="93" ht="12.75" customHeight="1"/>
-    <row r="94" ht="12.75" customHeight="1"/>
-    <row r="95" ht="12.75" customHeight="1"/>
-    <row r="96" ht="12.75" customHeight="1"/>
-    <row r="97" ht="12.75" customHeight="1"/>
-    <row r="98" ht="12.75" customHeight="1"/>
-    <row r="99" ht="12.75" customHeight="1"/>
-    <row r="100" ht="12.75" customHeight="1"/>
-    <row r="101" ht="12.75" customHeight="1"/>
-    <row r="102" ht="12.75" customHeight="1"/>
-    <row r="103" ht="12.75" customHeight="1"/>
-    <row r="104" ht="12.75" customHeight="1"/>
-    <row r="105" ht="12.75" customHeight="1"/>
-    <row r="106" ht="12.75" customHeight="1"/>
-    <row r="107" ht="12.75" customHeight="1"/>
-    <row r="108" ht="12.75" customHeight="1"/>
-    <row r="109" ht="12.75" customHeight="1"/>
-    <row r="110" ht="12.75" customHeight="1"/>
-    <row r="111" ht="12.75" customHeight="1"/>
-    <row r="112" ht="12.75" customHeight="1"/>
-    <row r="113" ht="12.75" customHeight="1"/>
-    <row r="114" ht="12.75" customHeight="1"/>
-    <row r="115" ht="12.75" customHeight="1"/>
-    <row r="116" ht="12.75" customHeight="1"/>
-    <row r="117" ht="12.75" customHeight="1"/>
-    <row r="118" ht="12.75" customHeight="1"/>
-    <row r="119" ht="12.75" customHeight="1"/>
-    <row r="120" ht="12.75" customHeight="1"/>
-    <row r="121" ht="12.75" customHeight="1"/>
-    <row r="122" ht="12.75" customHeight="1"/>
-    <row r="123" ht="12.75" customHeight="1"/>
-    <row r="124" ht="12.75" customHeight="1"/>
-    <row r="125" ht="12.75" customHeight="1"/>
-    <row r="126" ht="12.75" customHeight="1"/>
-    <row r="127" ht="12.75" customHeight="1"/>
-    <row r="128" ht="12.75" customHeight="1"/>
-    <row r="129" ht="12.75" customHeight="1"/>
-    <row r="130" ht="12.75" customHeight="1"/>
-    <row r="131" ht="12.75" customHeight="1"/>
-    <row r="132" ht="12.75" customHeight="1"/>
-    <row r="133" ht="12.75" customHeight="1"/>
-    <row r="134" ht="12.75" customHeight="1"/>
-    <row r="135" ht="12.75" customHeight="1"/>
-    <row r="136" ht="12.75" customHeight="1"/>
-    <row r="137" ht="12.75" customHeight="1"/>
-    <row r="138" ht="12.75" customHeight="1"/>
-    <row r="139" ht="12.75" customHeight="1"/>
-    <row r="140" ht="12.75" customHeight="1"/>
-    <row r="141" ht="12.75" customHeight="1"/>
-    <row r="142" ht="12.75" customHeight="1"/>
-    <row r="143" ht="12.75" customHeight="1"/>
-    <row r="144" ht="12.75" customHeight="1"/>
-    <row r="145" ht="12.75" customHeight="1"/>
-    <row r="146" ht="12.75" customHeight="1"/>
-    <row r="147" ht="12.75" customHeight="1"/>
-    <row r="148" ht="12.75" customHeight="1"/>
-    <row r="149" ht="12.75" customHeight="1"/>
-    <row r="150" ht="12.75" customHeight="1"/>
-    <row r="151" ht="12.75" customHeight="1"/>
-    <row r="152" ht="12.75" customHeight="1"/>
-    <row r="153" ht="12.75" customHeight="1"/>
-    <row r="154" ht="12.75" customHeight="1"/>
-    <row r="155" ht="12.75" customHeight="1"/>
-    <row r="156" ht="12.75" customHeight="1"/>
-    <row r="157" ht="12.75" customHeight="1"/>
-    <row r="158" ht="12.75" customHeight="1"/>
-    <row r="159" ht="12.75" customHeight="1"/>
-    <row r="160" ht="12.75" customHeight="1"/>
-    <row r="161" ht="12.75" customHeight="1"/>
-    <row r="162" ht="12.75" customHeight="1"/>
-    <row r="163" ht="12.75" customHeight="1"/>
-    <row r="164" ht="12.75" customHeight="1"/>
-    <row r="165" ht="12.75" customHeight="1"/>
-    <row r="166" ht="12.75" customHeight="1"/>
-    <row r="167" ht="12.75" customHeight="1"/>
-    <row r="168" ht="12.75" customHeight="1"/>
-    <row r="169" ht="12.75" customHeight="1"/>
-    <row r="170" ht="12.75" customHeight="1"/>
-    <row r="171" ht="12.75" customHeight="1"/>
-    <row r="172" ht="12.75" customHeight="1"/>
-    <row r="173" ht="12.75" customHeight="1"/>
-    <row r="174" ht="12.75" customHeight="1"/>
-    <row r="175" ht="12.75" customHeight="1"/>
-    <row r="176" ht="12.75" customHeight="1"/>
-    <row r="177" ht="12.75" customHeight="1"/>
-    <row r="178" ht="12.75" customHeight="1"/>
-    <row r="179" ht="12.75" customHeight="1"/>
-    <row r="180" ht="12.75" customHeight="1"/>
-    <row r="181" ht="12.75" customHeight="1"/>
-    <row r="182" ht="12.75" customHeight="1"/>
-    <row r="183" ht="12.75" customHeight="1"/>
-    <row r="184" ht="12.75" customHeight="1"/>
-    <row r="185" ht="12.75" customHeight="1"/>
-    <row r="186" ht="12.75" customHeight="1"/>
-    <row r="187" ht="12.75" customHeight="1"/>
-    <row r="188" ht="12.75" customHeight="1"/>
-    <row r="189" ht="12.75" customHeight="1"/>
-    <row r="190" ht="12.75" customHeight="1"/>
-    <row r="191" ht="12.75" customHeight="1"/>
-    <row r="192" ht="12.75" customHeight="1"/>
-    <row r="193" ht="12.75" customHeight="1"/>
-    <row r="194" ht="12.75" customHeight="1"/>
-    <row r="195" ht="12.75" customHeight="1"/>
-    <row r="196" ht="12.75" customHeight="1"/>
-    <row r="197" ht="12.75" customHeight="1"/>
-    <row r="198" ht="12.75" customHeight="1"/>
-    <row r="199" ht="12.75" customHeight="1"/>
-    <row r="200" ht="12.75" customHeight="1"/>
-    <row r="201" ht="12.75" customHeight="1"/>
-    <row r="202" ht="12.75" customHeight="1"/>
-    <row r="203" ht="12.75" customHeight="1"/>
-    <row r="204" ht="12.75" customHeight="1"/>
-    <row r="205" ht="12.75" customHeight="1"/>
-    <row r="206" ht="12.75" customHeight="1"/>
-    <row r="207" ht="12.75" customHeight="1"/>
-    <row r="208" ht="12.75" customHeight="1"/>
-    <row r="209" ht="12.75" customHeight="1"/>
-    <row r="210" ht="12.75" customHeight="1"/>
-    <row r="211" ht="12.75" customHeight="1"/>
-    <row r="212" ht="12.75" customHeight="1"/>
-    <row r="213" ht="12.75" customHeight="1"/>
-    <row r="214" ht="12.75" customHeight="1"/>
-    <row r="215" ht="12.75" customHeight="1"/>
-    <row r="216" ht="12.75" customHeight="1"/>
-    <row r="217" ht="12.75" customHeight="1"/>
-    <row r="218" ht="12.75" customHeight="1"/>
-    <row r="219" ht="12.75" customHeight="1"/>
-    <row r="220" ht="12.75" customHeight="1"/>
-    <row r="221" ht="12.75" customHeight="1"/>
-    <row r="222" ht="12.75" customHeight="1"/>
-    <row r="223" ht="12.75" customHeight="1"/>
-    <row r="224" ht="12.75" customHeight="1"/>
-    <row r="225" ht="12.75" customHeight="1"/>
-    <row r="226" ht="12.75" customHeight="1"/>
-    <row r="227" ht="12.75" customHeight="1"/>
-    <row r="228" ht="12.75" customHeight="1"/>
-    <row r="229" ht="12.75" customHeight="1"/>
-    <row r="230" ht="12.75" customHeight="1"/>
-    <row r="231" ht="12.75" customHeight="1"/>
-    <row r="232" ht="12.75" customHeight="1"/>
-    <row r="233" ht="12.75" customHeight="1"/>
-    <row r="234" ht="12.75" customHeight="1"/>
-    <row r="235" ht="12.75" customHeight="1"/>
-    <row r="236" ht="12.75" customHeight="1"/>
-    <row r="237" ht="12.75" customHeight="1"/>
-    <row r="238" ht="12.75" customHeight="1"/>
-    <row r="239" ht="12.75" customHeight="1"/>
-    <row r="240" ht="12.75" customHeight="1"/>
-    <row r="241" ht="12.75" customHeight="1"/>
-    <row r="242" ht="12.75" customHeight="1"/>
-    <row r="243" ht="12.75" customHeight="1"/>
-    <row r="244" ht="12.75" customHeight="1"/>
-    <row r="245" ht="12.75" customHeight="1"/>
-    <row r="246" ht="12.75" customHeight="1"/>
-    <row r="247" ht="12.75" customHeight="1"/>
-    <row r="248" ht="12.75" customHeight="1"/>
-    <row r="249" ht="12.75" customHeight="1"/>
-    <row r="250" ht="12.75" customHeight="1"/>
-    <row r="251" ht="12.75" customHeight="1"/>
-    <row r="252" ht="12.75" customHeight="1"/>
-    <row r="253" ht="12.75" customHeight="1"/>
-    <row r="254" ht="12.75" customHeight="1"/>
-    <row r="255" ht="12.75" customHeight="1"/>
-    <row r="256" ht="12.75" customHeight="1"/>
-    <row r="257" ht="12.75" customHeight="1"/>
-    <row r="258" ht="12.75" customHeight="1"/>
-    <row r="259" ht="12.75" customHeight="1"/>
-    <row r="260" ht="12.75" customHeight="1"/>
-    <row r="261" ht="12.75" customHeight="1"/>
-    <row r="262" ht="12.75" customHeight="1"/>
-    <row r="263" ht="12.75" customHeight="1"/>
-    <row r="264" ht="12.75" customHeight="1"/>
-    <row r="265" ht="12.75" customHeight="1"/>
-    <row r="266" ht="12.75" customHeight="1"/>
-    <row r="267" ht="12.75" customHeight="1"/>
-    <row r="268" ht="12.75" customHeight="1"/>
-    <row r="269" ht="12.75" customHeight="1"/>
-    <row r="270" ht="12.75" customHeight="1"/>
-    <row r="271" ht="12.75" customHeight="1"/>
-    <row r="272" ht="12.75" customHeight="1"/>
-    <row r="273" ht="12.75" customHeight="1"/>
-    <row r="274" ht="12.75" customHeight="1"/>
-    <row r="275" ht="12.75" customHeight="1"/>
-    <row r="276" ht="12.75" customHeight="1"/>
-    <row r="277" ht="12.75" customHeight="1"/>
-    <row r="278" ht="12.75" customHeight="1"/>
-    <row r="279" ht="12.75" customHeight="1"/>
-    <row r="280" ht="12.75" customHeight="1"/>
-    <row r="281" ht="12.75" customHeight="1"/>
-    <row r="282" ht="12.75" customHeight="1"/>
-    <row r="283" ht="12.75" customHeight="1"/>
-    <row r="284" ht="12.75" customHeight="1"/>
-    <row r="285" ht="12.75" customHeight="1"/>
-    <row r="286" ht="12.75" customHeight="1"/>
-    <row r="287" ht="12.75" customHeight="1"/>
-    <row r="288" ht="12.75" customHeight="1"/>
-    <row r="289" ht="12.75" customHeight="1"/>
-    <row r="290" ht="12.75" customHeight="1"/>
-    <row r="291" ht="12.75" customHeight="1"/>
-    <row r="292" ht="12.75" customHeight="1"/>
-    <row r="293" ht="12.75" customHeight="1"/>
-    <row r="294" ht="12.75" customHeight="1"/>
-    <row r="295" ht="12.75" customHeight="1"/>
-    <row r="296" ht="12.75" customHeight="1"/>
-    <row r="297" ht="12.75" customHeight="1"/>
-    <row r="298" ht="12.75" customHeight="1"/>
-    <row r="299" ht="12.75" customHeight="1"/>
-    <row r="300" ht="12.75" customHeight="1"/>
-    <row r="301" ht="12.75" customHeight="1"/>
-    <row r="302" ht="12.75" customHeight="1"/>
-    <row r="303" ht="12.75" customHeight="1"/>
-    <row r="304" ht="12.75" customHeight="1"/>
-    <row r="305" ht="12.75" customHeight="1"/>
-    <row r="306" ht="12.75" customHeight="1"/>
-    <row r="307" ht="12.75" customHeight="1"/>
-    <row r="308" ht="12.75" customHeight="1"/>
-    <row r="309" ht="12.75" customHeight="1"/>
-    <row r="310" ht="12.75" customHeight="1"/>
-    <row r="311" ht="12.75" customHeight="1"/>
-    <row r="312" ht="12.75" customHeight="1"/>
-    <row r="313" ht="12.75" customHeight="1"/>
-    <row r="314" ht="12.75" customHeight="1"/>
-    <row r="315" ht="12.75" customHeight="1"/>
-    <row r="316" ht="12.75" customHeight="1"/>
-    <row r="317" ht="12.75" customHeight="1"/>
-    <row r="318" ht="12.75" customHeight="1"/>
-    <row r="319" ht="12.75" customHeight="1"/>
-    <row r="320" ht="12.75" customHeight="1"/>
-    <row r="321" ht="12.75" customHeight="1"/>
-    <row r="322" ht="12.75" customHeight="1"/>
-    <row r="323" ht="12.75" customHeight="1"/>
-    <row r="324" ht="12.75" customHeight="1"/>
-    <row r="325" ht="12.75" customHeight="1"/>
-    <row r="326" ht="12.75" customHeight="1"/>
-    <row r="327" ht="12.75" customHeight="1"/>
-    <row r="328" ht="12.75" customHeight="1"/>
-    <row r="329" ht="12.75" customHeight="1"/>
-    <row r="330" ht="12.75" customHeight="1"/>
-    <row r="331" ht="12.75" customHeight="1"/>
-    <row r="332" ht="12.75" customHeight="1"/>
-    <row r="333" ht="12.75" customHeight="1"/>
-    <row r="334" ht="12.75" customHeight="1"/>
-    <row r="335" ht="12.75" customHeight="1"/>
-    <row r="336" ht="12.75" customHeight="1"/>
-    <row r="337" ht="12.75" customHeight="1"/>
-    <row r="338" ht="12.75" customHeight="1"/>
-    <row r="339" ht="12.75" customHeight="1"/>
-    <row r="340" ht="12.75" customHeight="1"/>
-    <row r="341" ht="12.75" customHeight="1"/>
-    <row r="342" ht="12.75" customHeight="1"/>
-    <row r="343" ht="12.75" customHeight="1"/>
-    <row r="344" ht="12.75" customHeight="1"/>
-    <row r="345" ht="12.75" customHeight="1"/>
-    <row r="346" ht="12.75" customHeight="1"/>
-    <row r="347" ht="12.75" customHeight="1"/>
-    <row r="348" ht="12.75" customHeight="1"/>
-    <row r="349" ht="12.75" customHeight="1"/>
-    <row r="350" ht="12.75" customHeight="1"/>
-    <row r="351" ht="12.75" customHeight="1"/>
-    <row r="352" ht="12.75" customHeight="1"/>
-    <row r="353" ht="12.75" customHeight="1"/>
-    <row r="354" ht="12.75" customHeight="1"/>
-    <row r="355" ht="12.75" customHeight="1"/>
-    <row r="356" ht="12.75" customHeight="1"/>
-    <row r="357" ht="12.75" customHeight="1"/>
-    <row r="358" ht="12.75" customHeight="1"/>
-    <row r="359" ht="12.75" customHeight="1"/>
-    <row r="360" ht="12.75" customHeight="1"/>
-    <row r="361" ht="12.75" customHeight="1"/>
-    <row r="362" ht="12.75" customHeight="1"/>
-    <row r="363" ht="12.75" customHeight="1"/>
-    <row r="364" ht="12.75" customHeight="1"/>
-    <row r="365" ht="12.75" customHeight="1"/>
-    <row r="366" ht="12.75" customHeight="1"/>
-    <row r="367" ht="12.75" customHeight="1"/>
-    <row r="368" ht="12.75" customHeight="1"/>
-    <row r="369" ht="12.75" customHeight="1"/>
-    <row r="370" ht="12.75" customHeight="1"/>
-    <row r="371" ht="12.75" customHeight="1"/>
-    <row r="372" ht="12.75" customHeight="1"/>
-    <row r="373" ht="12.75" customHeight="1"/>
-    <row r="374" ht="12.75" customHeight="1"/>
-    <row r="375" ht="12.75" customHeight="1"/>
-    <row r="376" ht="12.75" customHeight="1"/>
-    <row r="377" ht="12.75" customHeight="1"/>
-    <row r="378" ht="12.75" customHeight="1"/>
-    <row r="379" ht="12.75" customHeight="1"/>
-    <row r="380" ht="12.75" customHeight="1"/>
-    <row r="381" ht="12.75" customHeight="1"/>
-    <row r="382" ht="12.75" customHeight="1"/>
-    <row r="383" ht="12.75" customHeight="1"/>
-    <row r="384" ht="12.75" customHeight="1"/>
-    <row r="385" ht="12.75" customHeight="1"/>
-    <row r="386" ht="12.75" customHeight="1"/>
-    <row r="387" ht="12.75" customHeight="1"/>
-    <row r="388" ht="12.75" customHeight="1"/>
-    <row r="389" ht="12.75" customHeight="1"/>
-    <row r="390" ht="12.75" customHeight="1"/>
-    <row r="391" ht="12.75" customHeight="1"/>
-    <row r="392" ht="12.75" customHeight="1"/>
-    <row r="393" ht="12.75" customHeight="1"/>
-    <row r="394" ht="12.75" customHeight="1"/>
-    <row r="395" ht="12.75" customHeight="1"/>
-    <row r="396" ht="12.75" customHeight="1"/>
-    <row r="397" ht="12.75" customHeight="1"/>
-    <row r="398" ht="12.75" customHeight="1"/>
-    <row r="399" ht="12.75" customHeight="1"/>
-    <row r="400" ht="12.75" customHeight="1"/>
-    <row r="401" ht="12.75" customHeight="1"/>
-    <row r="402" ht="12.75" customHeight="1"/>
-    <row r="403" ht="12.75" customHeight="1"/>
-    <row r="404" ht="12.75" customHeight="1"/>
-    <row r="405" ht="12.75" customHeight="1"/>
-    <row r="406" ht="12.75" customHeight="1"/>
-    <row r="407" ht="12.75" customHeight="1"/>
-    <row r="408" ht="12.75" customHeight="1"/>
-    <row r="409" ht="12.75" customHeight="1"/>
-    <row r="410" ht="12.75" customHeight="1"/>
-    <row r="411" ht="12.75" customHeight="1"/>
-    <row r="412" ht="12.75" customHeight="1"/>
-    <row r="413" ht="12.75" customHeight="1"/>
-    <row r="414" ht="12.75" customHeight="1"/>
-    <row r="415" ht="12.75" customHeight="1"/>
-    <row r="416" ht="12.75" customHeight="1"/>
-    <row r="417" ht="12.75" customHeight="1"/>
-    <row r="418" ht="12.75" customHeight="1"/>
-    <row r="419" ht="12.75" customHeight="1"/>
-    <row r="420" ht="12.75" customHeight="1"/>
-    <row r="421" ht="12.75" customHeight="1"/>
-    <row r="422" ht="12.75" customHeight="1"/>
-    <row r="423" ht="12.75" customHeight="1"/>
-    <row r="424" ht="12.75" customHeight="1"/>
-    <row r="425" ht="12.75" customHeight="1"/>
-    <row r="426" ht="12.75" customHeight="1"/>
-    <row r="427" ht="12.75" customHeight="1"/>
-    <row r="428" ht="12.75" customHeight="1"/>
-    <row r="429" ht="12.75" customHeight="1"/>
-    <row r="430" ht="12.75" customHeight="1"/>
-    <row r="431" ht="12.75" customHeight="1"/>
-    <row r="432" ht="12.75" customHeight="1"/>
-    <row r="433" ht="12.75" customHeight="1"/>
-    <row r="434" ht="12.75" customHeight="1"/>
-    <row r="435" ht="12.75" customHeight="1"/>
-    <row r="436" ht="12.75" customHeight="1"/>
-    <row r="437" ht="12.75" customHeight="1"/>
-    <row r="438" ht="12.75" customHeight="1"/>
-    <row r="439" ht="12.75" customHeight="1"/>
-    <row r="440" ht="12.75" customHeight="1"/>
-    <row r="441" ht="12.75" customHeight="1"/>
-    <row r="442" ht="12.75" customHeight="1"/>
-    <row r="443" ht="12.75" customHeight="1"/>
-    <row r="444" ht="12.75" customHeight="1"/>
-    <row r="445" ht="12.75" customHeight="1"/>
-    <row r="446" ht="12.75" customHeight="1"/>
-    <row r="447" ht="12.75" customHeight="1"/>
-    <row r="448" ht="12.75" customHeight="1"/>
-    <row r="449" ht="12.75" customHeight="1"/>
-    <row r="450" ht="12.75" customHeight="1"/>
-    <row r="451" ht="12.75" customHeight="1"/>
-    <row r="452" ht="12.75" customHeight="1"/>
-    <row r="453" ht="12.75" customHeight="1"/>
-    <row r="454" ht="12.75" customHeight="1"/>
-    <row r="455" ht="12.75" customHeight="1"/>
-    <row r="456" ht="12.75" customHeight="1"/>
-    <row r="457" ht="12.75" customHeight="1"/>
-    <row r="458" ht="12.75" customHeight="1"/>
-    <row r="459" ht="12.75" customHeight="1"/>
-    <row r="460" ht="12.75" customHeight="1"/>
-    <row r="461" ht="12.75" customHeight="1"/>
-    <row r="462" ht="12.75" customHeight="1"/>
-    <row r="463" ht="12.75" customHeight="1"/>
-    <row r="464" ht="12.75" customHeight="1"/>
-    <row r="465" ht="12.75" customHeight="1"/>
-    <row r="466" ht="12.75" customHeight="1"/>
-    <row r="467" ht="12.75" customHeight="1"/>
-    <row r="468" ht="12.75" customHeight="1"/>
-    <row r="469" ht="12.75" customHeight="1"/>
-    <row r="470" ht="12.75" customHeight="1"/>
-    <row r="471" ht="12.75" customHeight="1"/>
-    <row r="472" ht="12.75" customHeight="1"/>
-    <row r="473" ht="12.75" customHeight="1"/>
-    <row r="474" ht="12.75" customHeight="1"/>
-    <row r="475" ht="12.75" customHeight="1"/>
-    <row r="476" ht="12.75" customHeight="1"/>
-    <row r="477" ht="12.75" customHeight="1"/>
-    <row r="478" ht="12.75" customHeight="1"/>
-    <row r="479" ht="12.75" customHeight="1"/>
-    <row r="480" ht="12.75" customHeight="1"/>
-    <row r="481" ht="12.75" customHeight="1"/>
-    <row r="482" ht="12.75" customHeight="1"/>
-    <row r="483" ht="12.75" customHeight="1"/>
-    <row r="484" ht="12.75" customHeight="1"/>
-    <row r="485" ht="12.75" customHeight="1"/>
-    <row r="486" ht="12.75" customHeight="1"/>
-    <row r="487" ht="12.75" customHeight="1"/>
-    <row r="488" ht="12.75" customHeight="1"/>
-    <row r="489" ht="12.75" customHeight="1"/>
-    <row r="490" ht="12.75" customHeight="1"/>
-    <row r="491" ht="12.75" customHeight="1"/>
-    <row r="492" ht="12.75" customHeight="1"/>
-    <row r="493" ht="12.75" customHeight="1"/>
-    <row r="494" ht="12.75" customHeight="1"/>
-    <row r="495" ht="12.75" customHeight="1"/>
-    <row r="496" ht="12.75" customHeight="1"/>
-    <row r="497" ht="12.75" customHeight="1"/>
-    <row r="498" ht="12.75" customHeight="1"/>
-    <row r="499" ht="12.75" customHeight="1"/>
-    <row r="500" ht="12.75" customHeight="1"/>
-    <row r="501" ht="12.75" customHeight="1"/>
-    <row r="502" ht="12.75" customHeight="1"/>
-    <row r="503" ht="12.75" customHeight="1"/>
-    <row r="504" ht="12.75" customHeight="1"/>
-    <row r="505" ht="12.75" customHeight="1"/>
-    <row r="506" ht="12.75" customHeight="1"/>
-    <row r="507" ht="12.75" customHeight="1"/>
-    <row r="508" ht="12.75" customHeight="1"/>
-    <row r="509" ht="12.75" customHeight="1"/>
-    <row r="510" ht="12.75" customHeight="1"/>
-    <row r="511" ht="12.75" customHeight="1"/>
-    <row r="512" ht="12.75" customHeight="1"/>
-    <row r="513" ht="12.75" customHeight="1"/>
-    <row r="514" ht="12.75" customHeight="1"/>
-    <row r="515" ht="12.75" customHeight="1"/>
-    <row r="516" ht="12.75" customHeight="1"/>
-    <row r="517" ht="12.75" customHeight="1"/>
-    <row r="518" ht="12.75" customHeight="1"/>
-    <row r="519" ht="12.75" customHeight="1"/>
-    <row r="520" ht="12.75" customHeight="1"/>
-    <row r="521" ht="12.75" customHeight="1"/>
-    <row r="522" ht="12.75" customHeight="1"/>
-    <row r="523" ht="12.75" customHeight="1"/>
-    <row r="524" ht="12.75" customHeight="1"/>
-    <row r="525" ht="12.75" customHeight="1"/>
-    <row r="526" ht="12.75" customHeight="1"/>
-    <row r="527" ht="12.75" customHeight="1"/>
-    <row r="528" ht="12.75" customHeight="1"/>
-    <row r="529" ht="12.75" customHeight="1"/>
-    <row r="530" ht="12.75" customHeight="1"/>
-    <row r="531" ht="12.75" customHeight="1"/>
-    <row r="532" ht="12.75" customHeight="1"/>
-    <row r="533" ht="12.75" customHeight="1"/>
-    <row r="534" ht="12.75" customHeight="1"/>
-    <row r="535" ht="12.75" customHeight="1"/>
-    <row r="536" ht="12.75" customHeight="1"/>
-    <row r="537" ht="12.75" customHeight="1"/>
-    <row r="538" ht="12.75" customHeight="1"/>
-    <row r="539" ht="12.75" customHeight="1"/>
-    <row r="540" ht="12.75" customHeight="1"/>
-    <row r="541" ht="12.75" customHeight="1"/>
-    <row r="542" ht="12.75" customHeight="1"/>
-    <row r="543" ht="12.75" customHeight="1"/>
-    <row r="544" ht="12.75" customHeight="1"/>
-    <row r="545" ht="12.75" customHeight="1"/>
-    <row r="546" ht="12.75" customHeight="1"/>
-    <row r="547" ht="12.75" customHeight="1"/>
-    <row r="548" ht="12.75" customHeight="1"/>
-    <row r="549" ht="12.75" customHeight="1"/>
-    <row r="550" ht="12.75" customHeight="1"/>
-    <row r="551" ht="12.75" customHeight="1"/>
-    <row r="552" ht="12.75" customHeight="1"/>
-    <row r="553" ht="12.75" customHeight="1"/>
-    <row r="554" ht="12.75" customHeight="1"/>
-    <row r="555" ht="12.75" customHeight="1"/>
-    <row r="556" ht="12.75" customHeight="1"/>
-    <row r="557" ht="12.75" customHeight="1"/>
-    <row r="558" ht="12.75" customHeight="1"/>
-    <row r="559" ht="12.75" customHeight="1"/>
-    <row r="560" ht="12.75" customHeight="1"/>
-    <row r="561" ht="12.75" customHeight="1"/>
-    <row r="562" ht="12.75" customHeight="1"/>
-    <row r="563" ht="12.75" customHeight="1"/>
-    <row r="564" ht="12.75" customHeight="1"/>
-    <row r="565" ht="12.75" customHeight="1"/>
-    <row r="566" ht="12.75" customHeight="1"/>
-    <row r="567" ht="12.75" customHeight="1"/>
-    <row r="568" ht="12.75" customHeight="1"/>
-    <row r="569" ht="12.75" customHeight="1"/>
-    <row r="570" ht="12.75" customHeight="1"/>
-    <row r="571" ht="12.75" customHeight="1"/>
-    <row r="572" ht="12.75" customHeight="1"/>
-    <row r="573" ht="12.75" customHeight="1"/>
-    <row r="574" ht="12.75" customHeight="1"/>
-    <row r="575" ht="12.75" customHeight="1"/>
-    <row r="576" ht="12.75" customHeight="1"/>
-    <row r="577" ht="12.75" customHeight="1"/>
-    <row r="578" ht="12.75" customHeight="1"/>
-    <row r="579" ht="12.75" customHeight="1"/>
-    <row r="580" ht="12.75" customHeight="1"/>
-    <row r="581" ht="12.75" customHeight="1"/>
-    <row r="582" ht="12.75" customHeight="1"/>
-    <row r="583" ht="12.75" customHeight="1"/>
-    <row r="584" ht="12.75" customHeight="1"/>
-    <row r="585" ht="12.75" customHeight="1"/>
-    <row r="586" ht="12.75" customHeight="1"/>
-    <row r="587" ht="12.75" customHeight="1"/>
-    <row r="588" ht="12.75" customHeight="1"/>
-    <row r="589" ht="12.75" customHeight="1"/>
-    <row r="590" ht="12.75" customHeight="1"/>
-    <row r="591" ht="12.75" customHeight="1"/>
-    <row r="592" ht="12.75" customHeight="1"/>
-    <row r="593" ht="12.75" customHeight="1"/>
-    <row r="594" ht="12.75" customHeight="1"/>
-    <row r="595" ht="12.75" customHeight="1"/>
-    <row r="596" ht="12.75" customHeight="1"/>
-    <row r="597" ht="12.75" customHeight="1"/>
-    <row r="598" ht="12.75" customHeight="1"/>
-    <row r="599" ht="12.75" customHeight="1"/>
-    <row r="600" ht="12.75" customHeight="1"/>
-    <row r="601" ht="12.75" customHeight="1"/>
-    <row r="602" ht="12.75" customHeight="1"/>
-    <row r="603" ht="12.75" customHeight="1"/>
-    <row r="604" ht="12.75" customHeight="1"/>
-    <row r="605" ht="12.75" customHeight="1"/>
-    <row r="606" ht="12.75" customHeight="1"/>
-    <row r="607" ht="12.75" customHeight="1"/>
-    <row r="608" ht="12.75" customHeight="1"/>
-    <row r="609" ht="12.75" customHeight="1"/>
-    <row r="610" ht="12.75" customHeight="1"/>
-    <row r="611" ht="12.75" customHeight="1"/>
-    <row r="612" ht="12.75" customHeight="1"/>
-    <row r="613" ht="12.75" customHeight="1"/>
-    <row r="614" ht="12.75" customHeight="1"/>
-    <row r="615" ht="12.75" customHeight="1"/>
-    <row r="616" ht="12.75" customHeight="1"/>
-    <row r="617" ht="12.75" customHeight="1"/>
-    <row r="618" ht="12.75" customHeight="1"/>
-    <row r="619" ht="12.75" customHeight="1"/>
-    <row r="620" ht="12.75" customHeight="1"/>
-    <row r="621" ht="12.75" customHeight="1"/>
-    <row r="622" ht="12.75" customHeight="1"/>
-    <row r="623" ht="12.75" customHeight="1"/>
-    <row r="624" ht="12.75" customHeight="1"/>
-    <row r="625" ht="12.75" customHeight="1"/>
-    <row r="626" ht="12.75" customHeight="1"/>
-    <row r="627" ht="12.75" customHeight="1"/>
-    <row r="628" ht="12.75" customHeight="1"/>
-    <row r="629" ht="12.75" customHeight="1"/>
-    <row r="630" ht="12.75" customHeight="1"/>
-    <row r="631" ht="12.75" customHeight="1"/>
-    <row r="632" ht="12.75" customHeight="1"/>
-    <row r="633" ht="12.75" customHeight="1"/>
-    <row r="634" ht="12.75" customHeight="1"/>
-    <row r="635" ht="12.75" customHeight="1"/>
-    <row r="636" ht="12.75" customHeight="1"/>
-    <row r="637" ht="12.75" customHeight="1"/>
-    <row r="638" ht="12.75" customHeight="1"/>
-    <row r="639" ht="12.75" customHeight="1"/>
-    <row r="640" ht="12.75" customHeight="1"/>
-    <row r="641" ht="12.75" customHeight="1"/>
-    <row r="642" ht="12.75" customHeight="1"/>
-    <row r="643" ht="12.75" customHeight="1"/>
-    <row r="644" ht="12.75" customHeight="1"/>
-    <row r="645" ht="12.75" customHeight="1"/>
-    <row r="646" ht="12.75" customHeight="1"/>
-    <row r="647" ht="12.75" customHeight="1"/>
-    <row r="648" ht="12.75" customHeight="1"/>
-    <row r="649" ht="12.75" customHeight="1"/>
-    <row r="650" ht="12.75" customHeight="1"/>
-    <row r="651" ht="12.75" customHeight="1"/>
-    <row r="652" ht="12.75" customHeight="1"/>
-    <row r="653" ht="12.75" customHeight="1"/>
-    <row r="654" ht="12.75" customHeight="1"/>
-    <row r="655" ht="12.75" customHeight="1"/>
-    <row r="656" ht="12.75" customHeight="1"/>
-    <row r="657" ht="12.75" customHeight="1"/>
-    <row r="658" ht="12.75" customHeight="1"/>
-    <row r="659" ht="12.75" customHeight="1"/>
-    <row r="660" ht="12.75" customHeight="1"/>
-    <row r="661" ht="12.75" customHeight="1"/>
-    <row r="662" ht="12.75" customHeight="1"/>
-    <row r="663" ht="12.75" customHeight="1"/>
-    <row r="664" ht="12.75" customHeight="1"/>
-    <row r="665" ht="12.75" customHeight="1"/>
-    <row r="666" ht="12.75" customHeight="1"/>
-    <row r="667" ht="12.75" customHeight="1"/>
-    <row r="668" ht="12.75" customHeight="1"/>
-    <row r="669" ht="12.75" customHeight="1"/>
-    <row r="670" ht="12.75" customHeight="1"/>
-    <row r="671" ht="12.75" customHeight="1"/>
-    <row r="672" ht="12.75" customHeight="1"/>
-    <row r="673" ht="12.75" customHeight="1"/>
-    <row r="674" ht="12.75" customHeight="1"/>
-    <row r="675" ht="12.75" customHeight="1"/>
-    <row r="676" ht="12.75" customHeight="1"/>
-    <row r="677" ht="12.75" customHeight="1"/>
-    <row r="678" ht="12.75" customHeight="1"/>
-    <row r="679" ht="12.75" customHeight="1"/>
-    <row r="680" ht="12.75" customHeight="1"/>
-    <row r="681" ht="12.75" customHeight="1"/>
-    <row r="682" ht="12.75" customHeight="1"/>
-    <row r="683" ht="12.75" customHeight="1"/>
-    <row r="684" ht="12.75" customHeight="1"/>
-    <row r="685" ht="12.75" customHeight="1"/>
-    <row r="686" ht="12.75" customHeight="1"/>
-    <row r="687" ht="12.75" customHeight="1"/>
-    <row r="688" ht="12.75" customHeight="1"/>
-    <row r="689" ht="12.75" customHeight="1"/>
-    <row r="690" ht="12.75" customHeight="1"/>
-    <row r="691" ht="12.75" customHeight="1"/>
-    <row r="692" ht="12.75" customHeight="1"/>
-    <row r="693" ht="12.75" customHeight="1"/>
-    <row r="694" ht="12.75" customHeight="1"/>
-    <row r="695" ht="12.75" customHeight="1"/>
-    <row r="696" ht="12.75" customHeight="1"/>
-    <row r="697" ht="12.75" customHeight="1"/>
-    <row r="698" ht="12.75" customHeight="1"/>
-    <row r="699" ht="12.75" customHeight="1"/>
-    <row r="700" ht="12.75" customHeight="1"/>
-    <row r="701" ht="12.75" customHeight="1"/>
-    <row r="702" ht="12.75" customHeight="1"/>
-    <row r="703" ht="12.75" customHeight="1"/>
-    <row r="704" ht="12.75" customHeight="1"/>
-    <row r="705" ht="12.75" customHeight="1"/>
-    <row r="706" ht="12.75" customHeight="1"/>
-    <row r="707" ht="12.75" customHeight="1"/>
-    <row r="708" ht="12.75" customHeight="1"/>
-    <row r="709" ht="12.75" customHeight="1"/>
-    <row r="710" ht="12.75" customHeight="1"/>
-    <row r="711" ht="12.75" customHeight="1"/>
-    <row r="712" ht="12.75" customHeight="1"/>
-    <row r="713" ht="12.75" customHeight="1"/>
-    <row r="714" ht="12.75" customHeight="1"/>
-    <row r="715" ht="12.75" customHeight="1"/>
-    <row r="716" ht="12.75" customHeight="1"/>
-    <row r="717" ht="12.75" customHeight="1"/>
-    <row r="718" ht="12.75" customHeight="1"/>
-    <row r="719" ht="12.75" customHeight="1"/>
-    <row r="720" ht="12.75" customHeight="1"/>
-    <row r="721" ht="12.75" customHeight="1"/>
-    <row r="722" ht="12.75" customHeight="1"/>
-    <row r="723" ht="12.75" customHeight="1"/>
-    <row r="724" ht="12.75" customHeight="1"/>
-    <row r="725" ht="12.75" customHeight="1"/>
-    <row r="726" ht="12.75" customHeight="1"/>
-    <row r="727" ht="12.75" customHeight="1"/>
-    <row r="728" ht="12.75" customHeight="1"/>
-    <row r="729" ht="12.75" customHeight="1"/>
-    <row r="730" ht="12.75" customHeight="1"/>
-    <row r="731" ht="12.75" customHeight="1"/>
-    <row r="732" ht="12.75" customHeight="1"/>
-    <row r="733" ht="12.75" customHeight="1"/>
-    <row r="734" ht="12.75" customHeight="1"/>
-    <row r="735" ht="12.75" customHeight="1"/>
-    <row r="736" ht="12.75" customHeight="1"/>
-    <row r="737" ht="12.75" customHeight="1"/>
-    <row r="738" ht="12.75" customHeight="1"/>
-    <row r="739" ht="12.75" customHeight="1"/>
-    <row r="740" ht="12.75" customHeight="1"/>
-    <row r="741" ht="12.75" customHeight="1"/>
-    <row r="742" ht="12.75" customHeight="1"/>
-    <row r="743" ht="12.75" customHeight="1"/>
-    <row r="744" ht="12.75" customHeight="1"/>
-    <row r="745" ht="12.75" customHeight="1"/>
-    <row r="746" ht="12.75" customHeight="1"/>
-    <row r="747" ht="12.75" customHeight="1"/>
-    <row r="748" ht="12.75" customHeight="1"/>
-    <row r="749" ht="12.75" customHeight="1"/>
-    <row r="750" ht="12.75" customHeight="1"/>
-    <row r="751" ht="12.75" customHeight="1"/>
-    <row r="752" ht="12.75" customHeight="1"/>
-    <row r="753" ht="12.75" customHeight="1"/>
-    <row r="754" ht="12.75" customHeight="1"/>
-    <row r="755" ht="12.75" customHeight="1"/>
-    <row r="756" ht="12.75" customHeight="1"/>
-    <row r="757" ht="12.75" customHeight="1"/>
-    <row r="758" ht="12.75" customHeight="1"/>
-    <row r="759" ht="12.75" customHeight="1"/>
-    <row r="760" ht="12.75" customHeight="1"/>
-    <row r="761" ht="12.75" customHeight="1"/>
-    <row r="762" ht="12.75" customHeight="1"/>
-    <row r="763" ht="12.75" customHeight="1"/>
-    <row r="764" ht="12.75" customHeight="1"/>
-    <row r="765" ht="12.75" customHeight="1"/>
-    <row r="766" ht="12.75" customHeight="1"/>
-    <row r="767" ht="12.75" customHeight="1"/>
-    <row r="768" ht="12.75" customHeight="1"/>
-    <row r="769" ht="12.75" customHeight="1"/>
-    <row r="770" ht="12.75" customHeight="1"/>
-    <row r="771" ht="12.75" customHeight="1"/>
-    <row r="772" ht="12.75" customHeight="1"/>
-    <row r="773" ht="12.75" customHeight="1"/>
-    <row r="774" ht="12.75" customHeight="1"/>
-    <row r="775" ht="12.75" customHeight="1"/>
-    <row r="776" ht="12.75" customHeight="1"/>
-    <row r="777" ht="12.75" customHeight="1"/>
-    <row r="778" ht="12.75" customHeight="1"/>
-    <row r="779" ht="12.75" customHeight="1"/>
-    <row r="780" ht="12.75" customHeight="1"/>
-    <row r="781" ht="12.75" customHeight="1"/>
-    <row r="782" ht="12.75" customHeight="1"/>
-    <row r="783" ht="12.75" customHeight="1"/>
-    <row r="784" ht="12.75" customHeight="1"/>
-    <row r="785" ht="12.75" customHeight="1"/>
-    <row r="786" ht="12.75" customHeight="1"/>
-    <row r="787" ht="12.75" customHeight="1"/>
-    <row r="788" ht="12.75" customHeight="1"/>
-    <row r="789" ht="12.75" customHeight="1"/>
-    <row r="790" ht="12.75" customHeight="1"/>
-    <row r="791" ht="12.75" customHeight="1"/>
-    <row r="792" ht="12.75" customHeight="1"/>
-    <row r="793" ht="12.75" customHeight="1"/>
-    <row r="794" ht="12.75" customHeight="1"/>
-    <row r="795" ht="12.75" customHeight="1"/>
-    <row r="796" ht="12.75" customHeight="1"/>
-    <row r="797" ht="12.75" customHeight="1"/>
-    <row r="798" ht="12.75" customHeight="1"/>
-    <row r="799" ht="12.75" customHeight="1"/>
-    <row r="800" ht="12.75" customHeight="1"/>
-    <row r="801" ht="12.75" customHeight="1"/>
-    <row r="802" ht="12.75" customHeight="1"/>
-    <row r="803" ht="12.75" customHeight="1"/>
-    <row r="804" ht="12.75" customHeight="1"/>
-    <row r="805" ht="12.75" customHeight="1"/>
-    <row r="806" ht="12.75" customHeight="1"/>
-    <row r="807" ht="12.75" customHeight="1"/>
-    <row r="808" ht="12.75" customHeight="1"/>
-    <row r="809" ht="12.75" customHeight="1"/>
-    <row r="810" ht="12.75" customHeight="1"/>
-    <row r="811" ht="12.75" customHeight="1"/>
-    <row r="812" ht="12.75" customHeight="1"/>
-    <row r="813" ht="12.75" customHeight="1"/>
-    <row r="814" ht="12.75" customHeight="1"/>
-    <row r="815" ht="12.75" customHeight="1"/>
-    <row r="816" ht="12.75" customHeight="1"/>
-    <row r="817" ht="12.75" customHeight="1"/>
-    <row r="818" ht="12.75" customHeight="1"/>
-    <row r="819" ht="12.75" customHeight="1"/>
-    <row r="820" ht="12.75" customHeight="1"/>
-    <row r="821" ht="12.75" customHeight="1"/>
-    <row r="822" ht="12.75" customHeight="1"/>
-    <row r="823" ht="12.75" customHeight="1"/>
-    <row r="824" ht="12.75" customHeight="1"/>
-    <row r="825" ht="12.75" customHeight="1"/>
-    <row r="826" ht="12.75" customHeight="1"/>
-    <row r="827" ht="12.75" customHeight="1"/>
-    <row r="828" ht="12.75" customHeight="1"/>
-    <row r="829" ht="12.75" customHeight="1"/>
-    <row r="830" ht="12.75" customHeight="1"/>
-    <row r="831" ht="12.75" customHeight="1"/>
-    <row r="832" ht="12.75" customHeight="1"/>
-    <row r="833" ht="12.75" customHeight="1"/>
-    <row r="834" ht="12.75" customHeight="1"/>
-    <row r="835" ht="12.75" customHeight="1"/>
-    <row r="836" ht="12.75" customHeight="1"/>
-    <row r="837" ht="12.75" customHeight="1"/>
-    <row r="838" ht="12.75" customHeight="1"/>
-    <row r="839" ht="12.75" customHeight="1"/>
-    <row r="840" ht="12.75" customHeight="1"/>
-    <row r="841" ht="12.75" customHeight="1"/>
-    <row r="842" ht="12.75" customHeight="1"/>
-    <row r="843" ht="12.75" customHeight="1"/>
-    <row r="844" ht="12.75" customHeight="1"/>
-    <row r="845" ht="12.75" customHeight="1"/>
-    <row r="846" ht="12.75" customHeight="1"/>
-    <row r="847" ht="12.75" customHeight="1"/>
-    <row r="848" ht="12.75" customHeight="1"/>
-    <row r="849" ht="12.75" customHeight="1"/>
-    <row r="850" ht="12.75" customHeight="1"/>
-    <row r="851" ht="12.75" customHeight="1"/>
-    <row r="852" ht="12.75" customHeight="1"/>
-    <row r="853" ht="12.75" customHeight="1"/>
-    <row r="854" ht="12.75" customHeight="1"/>
-    <row r="855" ht="12.75" customHeight="1"/>
-    <row r="856" ht="12.75" customHeight="1"/>
-    <row r="857" ht="12.75" customHeight="1"/>
-    <row r="858" ht="12.75" customHeight="1"/>
-    <row r="859" ht="12.75" customHeight="1"/>
-    <row r="860" ht="12.75" customHeight="1"/>
-    <row r="861" ht="12.75" customHeight="1"/>
-    <row r="862" ht="12.75" customHeight="1"/>
-    <row r="863" ht="12.75" customHeight="1"/>
-    <row r="864" ht="12.75" customHeight="1"/>
-    <row r="865" ht="12.75" customHeight="1"/>
-    <row r="866" ht="12.75" customHeight="1"/>
-    <row r="867" ht="12.75" customHeight="1"/>
-    <row r="868" ht="12.75" customHeight="1"/>
-    <row r="869" ht="12.75" customHeight="1"/>
-    <row r="870" ht="12.75" customHeight="1"/>
-    <row r="871" ht="12.75" customHeight="1"/>
-    <row r="872" ht="12.75" customHeight="1"/>
-    <row r="873" ht="12.75" customHeight="1"/>
-    <row r="874" ht="12.75" customHeight="1"/>
-    <row r="875" ht="12.75" customHeight="1"/>
-    <row r="876" ht="12.75" customHeight="1"/>
-    <row r="877" ht="12.75" customHeight="1"/>
-    <row r="878" ht="12.75" customHeight="1"/>
-    <row r="879" ht="12.75" customHeight="1"/>
-    <row r="880" ht="12.75" customHeight="1"/>
-    <row r="881" ht="12.75" customHeight="1"/>
-    <row r="882" ht="12.75" customHeight="1"/>
-    <row r="883" ht="12.75" customHeight="1"/>
-    <row r="884" ht="12.75" customHeight="1"/>
-    <row r="885" ht="12.75" customHeight="1"/>
-    <row r="886" ht="12.75" customHeight="1"/>
-    <row r="887" ht="12.75" customHeight="1"/>
-    <row r="888" ht="12.75" customHeight="1"/>
-    <row r="889" ht="12.75" customHeight="1"/>
-    <row r="890" ht="12.75" customHeight="1"/>
-    <row r="891" ht="12.75" customHeight="1"/>
-    <row r="892" ht="12.75" customHeight="1"/>
-    <row r="893" ht="12.75" customHeight="1"/>
-    <row r="894" ht="12.75" customHeight="1"/>
-    <row r="895" ht="12.75" customHeight="1"/>
-    <row r="896" ht="12.75" customHeight="1"/>
-    <row r="897" ht="12.75" customHeight="1"/>
-    <row r="898" ht="12.75" customHeight="1"/>
-    <row r="899" ht="12.75" customHeight="1"/>
-    <row r="900" ht="12.75" customHeight="1"/>
-    <row r="901" ht="12.75" customHeight="1"/>
-    <row r="902" ht="12.75" customHeight="1"/>
-    <row r="903" ht="12.75" customHeight="1"/>
-    <row r="904" ht="12.75" customHeight="1"/>
-    <row r="905" ht="12.75" customHeight="1"/>
-    <row r="906" ht="12.75" customHeight="1"/>
-    <row r="907" ht="12.75" customHeight="1"/>
-    <row r="908" ht="12.75" customHeight="1"/>
-    <row r="909" ht="12.75" customHeight="1"/>
-    <row r="910" ht="12.75" customHeight="1"/>
-    <row r="911" ht="12.75" customHeight="1"/>
-    <row r="912" ht="12.75" customHeight="1"/>
-    <row r="913" ht="12.75" customHeight="1"/>
-    <row r="914" ht="12.75" customHeight="1"/>
-    <row r="915" ht="12.75" customHeight="1"/>
-    <row r="916" ht="12.75" customHeight="1"/>
-    <row r="917" ht="12.75" customHeight="1"/>
-    <row r="918" ht="12.75" customHeight="1"/>
-    <row r="919" ht="12.75" customHeight="1"/>
-    <row r="920" ht="12.75" customHeight="1"/>
-    <row r="921" ht="12.75" customHeight="1"/>
-    <row r="922" ht="12.75" customHeight="1"/>
-    <row r="923" ht="12.75" customHeight="1"/>
-    <row r="924" ht="12.75" customHeight="1"/>
-    <row r="925" ht="12.75" customHeight="1"/>
-    <row r="926" ht="12.75" customHeight="1"/>
-    <row r="927" ht="12.75" customHeight="1"/>
-    <row r="928" ht="12.75" customHeight="1"/>
-    <row r="929" ht="12.75" customHeight="1"/>
-    <row r="930" ht="12.75" customHeight="1"/>
-    <row r="931" ht="12.75" customHeight="1"/>
-    <row r="932" ht="12.75" customHeight="1"/>
-    <row r="933" ht="12.75" customHeight="1"/>
-    <row r="934" ht="12.75" customHeight="1"/>
-    <row r="935" ht="12.75" customHeight="1"/>
-    <row r="936" ht="12.75" customHeight="1"/>
-    <row r="937" ht="12.75" customHeight="1"/>
-    <row r="938" ht="12.75" customHeight="1"/>
-    <row r="939" ht="12.75" customHeight="1"/>
-    <row r="940" ht="12.75" customHeight="1"/>
-    <row r="941" ht="12.75" customHeight="1"/>
-    <row r="942" ht="12.75" customHeight="1"/>
-    <row r="943" ht="12.75" customHeight="1"/>
-    <row r="944" ht="12.75" customHeight="1"/>
-    <row r="945" ht="12.75" customHeight="1"/>
-    <row r="946" ht="12.75" customHeight="1"/>
-    <row r="947" ht="12.75" customHeight="1"/>
-    <row r="948" ht="12.75" customHeight="1"/>
-    <row r="949" ht="12.75" customHeight="1"/>
-    <row r="950" ht="12.75" customHeight="1"/>
-    <row r="951" ht="12.75" customHeight="1"/>
-    <row r="952" ht="12.75" customHeight="1"/>
-    <row r="953" ht="12.75" customHeight="1"/>
-    <row r="954" ht="12.75" customHeight="1"/>
-    <row r="955" ht="12.75" customHeight="1"/>
-    <row r="956" ht="12.75" customHeight="1"/>
-    <row r="957" ht="12.75" customHeight="1"/>
-    <row r="958" ht="12.75" customHeight="1"/>
-    <row r="959" ht="12.75" customHeight="1"/>
-    <row r="960" ht="12.75" customHeight="1"/>
-    <row r="961" ht="12.75" customHeight="1"/>
-    <row r="962" ht="12.75" customHeight="1"/>
-    <row r="963" ht="12.75" customHeight="1"/>
-    <row r="964" ht="12.75" customHeight="1"/>
-    <row r="965" ht="12.75" customHeight="1"/>
-    <row r="966" ht="12.75" customHeight="1"/>
-    <row r="967" ht="12.75" customHeight="1"/>
-    <row r="968" ht="12.75" customHeight="1"/>
-    <row r="969" ht="12.75" customHeight="1"/>
-    <row r="970" ht="12.75" customHeight="1"/>
-    <row r="971" ht="12.75" customHeight="1"/>
-    <row r="972" ht="12.75" customHeight="1"/>
-    <row r="973" ht="12.75" customHeight="1"/>
-    <row r="974" ht="12.75" customHeight="1"/>
-    <row r="975" ht="12.75" customHeight="1"/>
-    <row r="976" ht="12.75" customHeight="1"/>
-    <row r="977" ht="12.75" customHeight="1"/>
-    <row r="978" ht="12.75" customHeight="1"/>
-    <row r="979" ht="12.75" customHeight="1"/>
-    <row r="980" ht="12.75" customHeight="1"/>
-    <row r="981" ht="12.75" customHeight="1"/>
-    <row r="982" ht="12.75" customHeight="1"/>
-    <row r="983" ht="12.75" customHeight="1"/>
-    <row r="984" ht="12.75" customHeight="1"/>
-    <row r="985" ht="12.75" customHeight="1"/>
-    <row r="986" ht="12.75" customHeight="1"/>
-    <row r="987" ht="12.75" customHeight="1"/>
-    <row r="988" ht="12.75" customHeight="1"/>
-    <row r="989" ht="12.75" customHeight="1"/>
-    <row r="990" ht="12.75" customHeight="1"/>
-    <row r="991" ht="12.75" customHeight="1"/>
-    <row r="992" ht="12.75" customHeight="1"/>
-    <row r="993" ht="12.75" customHeight="1"/>
-    <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B70C3665-E52C-464E-B22A-6BC197D77956}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J995"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="57" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="56"/>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="44">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="47"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="48"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="48"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="65" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="66"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="67"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="68"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="70"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="71"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="71"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="71"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="52"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="71"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="52"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="71"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="52"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="71"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="67"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="72" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="67"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="121" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="119"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="120" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="120" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="120"/>
-      <c r="G17" s="126" t="s">
-        <v>118</v>
-      </c>
-      <c r="H17" s="123" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="124"/>
-      <c r="J17" s="125"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="58"/>
-      <c r="B18" s="105"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="108"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="109"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11643,6 +10334,1307 @@
   <mergeCells count="21">
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B70C3665-E52C-464E-B22A-6BC197D77956}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J995"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="79" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="66"/>
+      <c r="F1" s="79" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="66"/>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="90">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="97" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="100" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="52"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="101"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="103"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="59"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="104"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="59"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="104"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="59"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="104"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="59"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="104"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="59"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="104"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="59"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="104"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="99" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="52"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="51"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="51"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="105" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="51"/>
+      <c r="J16" s="52"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="92" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="93"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="38"/>
+      <c r="G17" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="I17" s="95"/>
+      <c r="J17" s="96"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A18" s="98"/>
+      <c r="B18" s="106"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="109"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -11657,11 +11649,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11681,186 +11668,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="57" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="57" t="s">
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="57" t="s">
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="57" t="s">
+      <c r="P1" s="66"/>
+      <c r="Q1" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="56"/>
-      <c r="S1" s="57" t="s">
+      <c r="R1" s="66"/>
+      <c r="S1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="66"/>
+      <c r="T1" s="46"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="70"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="103"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="71"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="104"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="95"/>
-      <c r="N4" s="86"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="86"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="113"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="118"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="100" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="66"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="46"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="72" t="s">
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="67"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="52"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="72" t="s">
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="62"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="62"/>
-      <c r="T7" s="67"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="51"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="51"/>
+      <c r="T7" s="52"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12059,37 +12046,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="116" t="s">
+      <c r="B15" s="68"/>
+      <c r="C15" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="63"/>
-      <c r="E15" s="73" t="s">
+      <c r="D15" s="68"/>
+      <c r="E15" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="63"/>
-      <c r="G15" s="73" t="s">
+      <c r="F15" s="68"/>
+      <c r="G15" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="62"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="73" t="s">
+      <c r="H15" s="51"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="63"/>
-      <c r="L15" s="73" t="s">
+      <c r="K15" s="68"/>
+      <c r="L15" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="62"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="73" t="s">
+      <c r="M15" s="51"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="63"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="68"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -12101,37 +12088,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="114">
+      <c r="A16" s="110">
         <v>1</v>
       </c>
-      <c r="B16" s="63"/>
-      <c r="C16" s="115" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="111" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="63"/>
-      <c r="E16" s="115" t="s">
+      <c r="D16" s="68"/>
+      <c r="E16" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="63"/>
-      <c r="G16" s="109" t="s">
+      <c r="F16" s="68"/>
+      <c r="G16" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="62"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="109" t="s">
+      <c r="H16" s="51"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="63"/>
-      <c r="L16" s="111" t="s">
+      <c r="K16" s="68"/>
+      <c r="L16" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="62"/>
-      <c r="N16" s="63"/>
-      <c r="O16" s="111" t="s">
+      <c r="M16" s="51"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="62"/>
-      <c r="Q16" s="63"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="68"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12143,37 +12130,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="114">
+      <c r="A17" s="110">
         <v>2</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="115" t="s">
+      <c r="B17" s="68"/>
+      <c r="C17" s="111" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="63"/>
-      <c r="E17" s="115" t="s">
+      <c r="D17" s="68"/>
+      <c r="E17" s="111" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="63"/>
-      <c r="G17" s="109" t="s">
+      <c r="F17" s="68"/>
+      <c r="G17" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="62"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="109" t="s">
+      <c r="H17" s="51"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="116" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="63"/>
-      <c r="L17" s="111" t="s">
+      <c r="K17" s="68"/>
+      <c r="L17" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="62"/>
-      <c r="N17" s="63"/>
-      <c r="O17" s="111" t="s">
+      <c r="M17" s="51"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="114" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="62"/>
-      <c r="Q17" s="63"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="68"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12185,23 +12172,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="114"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="111"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="63"/>
+      <c r="A18" s="110"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="116"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="114"/>
+      <c r="M18" s="51"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="68"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -12213,23 +12200,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="114"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="109"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="111"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="63"/>
-      <c r="O19" s="111"/>
-      <c r="P19" s="62"/>
-      <c r="Q19" s="63"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="114"/>
+      <c r="M19" s="51"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="51"/>
+      <c r="Q19" s="68"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -12241,23 +12228,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="114"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="109"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="111"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="63"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="116"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="114"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="68"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -12269,23 +12256,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="114"/>
-      <c r="B21" s="63"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="109"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="62"/>
-      <c r="Q21" s="63"/>
+      <c r="A21" s="110"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="116"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="68"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -12297,23 +12284,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="114"/>
-      <c r="B22" s="63"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="63"/>
+      <c r="A22" s="110"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="116"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="114"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="68"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -12325,23 +12312,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="114"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="109"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="109"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="63"/>
-      <c r="O23" s="111"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="63"/>
+      <c r="A23" s="110"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="111"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="114"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="68"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -12353,23 +12340,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="114"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="115"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="115"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="109"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="62"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="62"/>
-      <c r="Q24" s="63"/>
+      <c r="A24" s="110"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="114"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="114"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="68"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -12381,23 +12368,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="114"/>
-      <c r="B25" s="63"/>
-      <c r="C25" s="115"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="115"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="109"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="63"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="63"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="62"/>
-      <c r="N25" s="63"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="62"/>
-      <c r="Q25" s="63"/>
+      <c r="A25" s="110"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="116"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="116"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="51"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="51"/>
+      <c r="Q25" s="68"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -12409,23 +12396,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="114"/>
-      <c r="B26" s="63"/>
-      <c r="C26" s="115"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="115"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="109"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="109"/>
-      <c r="K26" s="63"/>
-      <c r="L26" s="111"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="111"/>
-      <c r="P26" s="62"/>
-      <c r="Q26" s="63"/>
+      <c r="A26" s="110"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="51"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="68"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -12437,23 +12424,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="114"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="109"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="109"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="111"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="63"/>
+      <c r="A27" s="110"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="68"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -12465,23 +12452,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="114"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="109"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="109"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="62"/>
-      <c r="N28" s="63"/>
-      <c r="O28" s="111"/>
-      <c r="P28" s="62"/>
-      <c r="Q28" s="63"/>
+      <c r="A28" s="110"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="116"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="116"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="51"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="68"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -12493,23 +12480,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="114"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="109"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="109"/>
-      <c r="K29" s="63"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="62"/>
-      <c r="N29" s="63"/>
-      <c r="O29" s="111"/>
-      <c r="P29" s="62"/>
-      <c r="Q29" s="63"/>
+      <c r="A29" s="110"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="111"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="111"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="116"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="116"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="114"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="68"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -12521,23 +12508,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="114"/>
-      <c r="B30" s="63"/>
-      <c r="C30" s="115"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="109"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="109"/>
-      <c r="K30" s="63"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="62"/>
-      <c r="N30" s="63"/>
-      <c r="O30" s="111"/>
-      <c r="P30" s="62"/>
-      <c r="Q30" s="63"/>
+      <c r="A30" s="110"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="111"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="111"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="116"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="116"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="114"/>
+      <c r="M30" s="51"/>
+      <c r="N30" s="68"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="68"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -12549,23 +12536,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="117"/>
-      <c r="B31" s="60"/>
-      <c r="C31" s="118"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="110"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="112"/>
-      <c r="M31" s="59"/>
-      <c r="N31" s="60"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="59"/>
-      <c r="Q31" s="60"/>
+      <c r="A31" s="112"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="113"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="119"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="119"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="115"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="55"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -13563,6 +13550,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -13587,118 +13686,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク登録機能.xlsx
+++ b/document/成果物ドキュメント_タスク登録機能.xlsx
@@ -5,30 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER124\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F97BC3-48B2-421D-B2BA-8487C2348996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75090775-18C5-408C-A52A-311715ED60A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
     <sheet name="ユースケース記述" sheetId="2" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
-    <sheet name="画面設計書(登録)" sheetId="5" r:id="rId5"/>
-    <sheet name="画面設計書 (登録完了)" sheetId="7" r:id="rId6"/>
-    <sheet name="画面設計書(登録エラー)" sheetId="9" r:id="rId7"/>
+    <sheet name="画面設計書 (タスク登録画面)" sheetId="5" r:id="rId5"/>
+    <sheet name="画面設計書 (タスク登録完了画面)" sheetId="7" r:id="rId6"/>
+    <sheet name="画面設計書 (タスク登録エラー画面)" sheetId="9" r:id="rId7"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="123">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -554,16 +553,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>Webブラウザ上でユーザが入力したタスクをDBに登録する</t>
-    <rPh sb="13" eb="15">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>task-register-servlet</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -713,6 +702,17 @@
     </rPh>
     <rPh sb="49" eb="51">
       <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>TaskManager62</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクをDBに登録する</t>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1595,6 +1595,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1831,9 +1834,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2379,85 +2379,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="88"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="89"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2477,46 +2477,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="89" t="s">
+      <c r="E8" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="85" t="s">
+      <c r="G13" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="68"/>
-      <c r="I13" s="85" t="s">
+      <c r="H13" s="69"/>
+      <c r="I13" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="51"/>
-      <c r="K13" s="68"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="69"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="85"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="68"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="69"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="85"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="85"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="68"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="69"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2525,13 +2525,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="86" t="s">
+      <c r="G17" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3545,19 +3545,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3569,192 +3569,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="82"/>
+      <c r="F2" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="82"/>
+      <c r="H2" s="85">
         <v>46121</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="44" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="47"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="50"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="50" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="50" t="s">
+      <c r="B8" s="52"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" ht="114" customHeight="1">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="52"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="54" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A10" s="70"/>
-      <c r="B10" s="72" t="s">
+      <c r="A10" s="71"/>
+      <c r="B10" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="53" t="s">
+      <c r="C10" s="69"/>
+      <c r="D10" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="52"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="50" t="s">
+      <c r="B12" s="52"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="44"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4790,19 +4790,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4814,48 +4814,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="81" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="82"/>
+      <c r="F2" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="90">
+      <c r="G2" s="82"/>
+      <c r="H2" s="91">
         <v>46125</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6210,19 +6210,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6234,48 +6234,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="81" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="82"/>
+      <c r="F2" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="90">
+      <c r="G2" s="82"/>
+      <c r="H2" s="91">
         <v>46125</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7626,19 +7626,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7650,190 +7650,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="81" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="82"/>
+      <c r="F2" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="90">
+      <c r="G2" s="82"/>
+      <c r="H2" s="91">
         <v>46121</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="100" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="101" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="47"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="52"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="101"/>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="103"/>
+      <c r="A7" s="102"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="104"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="59"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="104"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="105"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="104"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="105"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="104"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="105"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="59"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="104"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="105"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="104"/>
+      <c r="A12" s="60"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="105"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="59"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="104"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="105"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="99" t="s">
+      <c r="A14" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="52"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="99" t="s">
+      <c r="A15" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="68"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -7842,11 +7842,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="68"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="69"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -7859,18 +7859,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="105" t="s">
+      <c r="H16" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="68"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="69"/>
       <c r="D17" s="17" t="s">
         <v>83</v>
       </c>
@@ -7881,18 +7881,18 @@
         <v>82</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="53"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="92" t="s">
+      <c r="A18" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="68"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="69"/>
       <c r="D18" s="17" t="s">
         <v>84</v>
       </c>
@@ -7903,18 +7903,18 @@
         <v>99</v>
       </c>
       <c r="G18" s="18"/>
-      <c r="H18" s="50" t="s">
+      <c r="H18" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="I18" s="51"/>
-      <c r="J18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A19" s="92" t="s">
+      <c r="A19" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="68"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="69"/>
       <c r="D19" s="17" t="s">
         <v>85</v>
       </c>
@@ -7924,21 +7924,21 @@
       <c r="F19" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="120" t="s">
-        <v>120</v>
-      </c>
-      <c r="H19" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="I19" s="51"/>
-      <c r="J19" s="52"/>
+      <c r="G19" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="I19" s="52"/>
+      <c r="J19" s="53"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="68"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="69"/>
       <c r="D20" s="17" t="s">
         <v>88</v>
       </c>
@@ -7949,18 +7949,18 @@
         <v>107</v>
       </c>
       <c r="G20" s="18"/>
-      <c r="H20" s="50" t="s">
+      <c r="H20" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="I20" s="51"/>
-      <c r="J20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="53"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="93" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="68"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="69"/>
       <c r="D21" s="17" t="s">
         <v>89</v>
       </c>
@@ -7971,18 +7971,18 @@
         <v>96</v>
       </c>
       <c r="G21" s="18"/>
-      <c r="H21" s="50" t="s">
+      <c r="H21" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="I21" s="51"/>
-      <c r="J21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="92" t="s">
+      <c r="A22" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="51"/>
-      <c r="C22" s="68"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="69"/>
       <c r="D22" s="17" t="s">
         <v>90</v>
       </c>
@@ -7993,20 +7993,20 @@
         <v>91</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="H22" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="I22" s="51"/>
-      <c r="J22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="92" t="s">
+      <c r="A23" s="93" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="93"/>
-      <c r="C23" s="94"/>
+      <c r="B23" s="94"/>
+      <c r="C23" s="95"/>
       <c r="D23" s="38" t="s">
         <v>98</v>
       </c>
@@ -8017,18 +8017,18 @@
       <c r="G23" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="H23" s="50" t="s">
+      <c r="H23" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="97"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="98" t="s">
+      <c r="A24" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="55"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="56"/>
       <c r="D24" s="19" t="s">
         <v>93</v>
       </c>
@@ -8039,11 +8039,11 @@
       <c r="G24" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="H24" s="41" t="s">
+      <c r="H24" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="I24" s="42"/>
-      <c r="J24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="44"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9080,19 +9080,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -9104,190 +9104,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="81" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="82"/>
+      <c r="F2" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="90">
+      <c r="G2" s="82"/>
+      <c r="H2" s="91">
         <v>46125</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="100" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="101" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="47"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="52"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="101"/>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="103"/>
+      <c r="A7" s="102"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="104"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="59"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="104"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="105"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="104"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="105"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="104"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="105"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="59"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="104"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="105"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="104"/>
+      <c r="A12" s="60"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="105"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="59"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="104"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="105"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="99" t="s">
+      <c r="A14" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="52"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="99" t="s">
+      <c r="A15" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="50" t="s">
+      <c r="B15" s="52"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="68"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -9296,11 +9296,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="68"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="69"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -9313,18 +9313,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="105" t="s">
+      <c r="H16" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="93"/>
-      <c r="C17" s="94"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="95"/>
       <c r="D17" s="38" t="s">
         <v>93</v>
       </c>
@@ -9335,23 +9335,23 @@
       <c r="G17" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="I17" s="95"/>
-      <c r="J17" s="96"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="97"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="98"/>
-      <c r="B18" s="106"/>
-      <c r="C18" s="107"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="108"/>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="109"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="109"/>
+      <c r="J18" s="110"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10376,19 +10376,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -10400,190 +10400,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="81" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="82"/>
+      <c r="F2" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="90">
+      <c r="G2" s="82"/>
+      <c r="H2" s="91">
         <v>46125</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="100" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="101" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="47"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="52"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="101"/>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="103"/>
+      <c r="A7" s="102"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="104"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="59"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="104"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="105"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="104"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="105"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="104"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="105"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="59"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="104"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="105"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="104"/>
+      <c r="A12" s="60"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="105"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="59"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="104"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="105"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="99" t="s">
+      <c r="A14" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="52"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="99" t="s">
+      <c r="A15" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="50" t="s">
+      <c r="B15" s="52"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="68"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -10592,11 +10592,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="68"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="69"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -10609,18 +10609,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="105" t="s">
+      <c r="H16" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="93"/>
-      <c r="C17" s="94"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="95"/>
       <c r="D17" s="38" t="s">
         <v>111</v>
       </c>
@@ -10631,23 +10631,23 @@
       <c r="G17" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="I17" s="95"/>
-      <c r="J17" s="96"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="97"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="98"/>
-      <c r="B18" s="106"/>
-      <c r="C18" s="107"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="108"/>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="109"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="109"/>
+      <c r="J18" s="110"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11668,186 +11668,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="79" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="79" t="s">
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="79" t="s">
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="79" t="s">
+      <c r="P1" s="67"/>
+      <c r="Q1" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="66"/>
-      <c r="S1" s="79" t="s">
+      <c r="R1" s="67"/>
+      <c r="S1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="46"/>
+      <c r="T1" s="47"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="80" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="81" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="82"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="104"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="61"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="104"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="105"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="118"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="84"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="84"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="84"/>
+      <c r="T4" s="119"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="44" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="47"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="50" t="s">
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="52"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
+      <c r="T6" s="53"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="50" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="53"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12046,37 +12046,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="99" t="s">
+      <c r="A15" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="117" t="s">
+      <c r="B15" s="69"/>
+      <c r="C15" s="118" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="105" t="s">
+      <c r="D15" s="69"/>
+      <c r="E15" s="106" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="105" t="s">
+      <c r="F15" s="69"/>
+      <c r="G15" s="106" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="51"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="105" t="s">
+      <c r="H15" s="52"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="68"/>
-      <c r="L15" s="105" t="s">
+      <c r="K15" s="69"/>
+      <c r="L15" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="51"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="105" t="s">
+      <c r="M15" s="52"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="68"/>
+      <c r="P15" s="52"/>
+      <c r="Q15" s="69"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -12088,37 +12088,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="110">
+      <c r="A16" s="111">
         <v>1</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="111" t="s">
+      <c r="B16" s="69"/>
+      <c r="C16" s="112" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="68"/>
-      <c r="E16" s="111" t="s">
+      <c r="D16" s="69"/>
+      <c r="E16" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="116" t="s">
+      <c r="F16" s="69"/>
+      <c r="G16" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="51"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="116" t="s">
+      <c r="H16" s="52"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="68"/>
-      <c r="L16" s="114" t="s">
+      <c r="K16" s="69"/>
+      <c r="L16" s="115" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="51"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="114" t="s">
+      <c r="M16" s="52"/>
+      <c r="N16" s="69"/>
+      <c r="O16" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="68"/>
+      <c r="P16" s="52"/>
+      <c r="Q16" s="69"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12130,37 +12130,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="110">
+      <c r="A17" s="111">
         <v>2</v>
       </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="111" t="s">
+      <c r="B17" s="69"/>
+      <c r="C17" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="111" t="s">
+      <c r="D17" s="69"/>
+      <c r="E17" s="112" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="116" t="s">
+      <c r="F17" s="69"/>
+      <c r="G17" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="51"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="116" t="s">
+      <c r="H17" s="52"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="117" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="68"/>
-      <c r="L17" s="114" t="s">
+      <c r="K17" s="69"/>
+      <c r="L17" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="51"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="114" t="s">
+      <c r="M17" s="52"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="115" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="68"/>
+      <c r="P17" s="52"/>
+      <c r="Q17" s="69"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12172,23 +12172,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="110"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="114"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="114"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="68"/>
+      <c r="A18" s="111"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="115"/>
+      <c r="P18" s="52"/>
+      <c r="Q18" s="69"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -12200,23 +12200,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="114"/>
-      <c r="M19" s="51"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="114"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="68"/>
+      <c r="A19" s="111"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="115"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="115"/>
+      <c r="P19" s="52"/>
+      <c r="Q19" s="69"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -12228,23 +12228,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="114"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="68"/>
+      <c r="A20" s="111"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="69"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="52"/>
+      <c r="Q20" s="69"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -12256,23 +12256,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="110"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="114"/>
-      <c r="M21" s="51"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="68"/>
+      <c r="A21" s="111"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="115"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="52"/>
+      <c r="Q21" s="69"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -12284,23 +12284,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="110"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="68"/>
-      <c r="O22" s="114"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="68"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="112"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="115"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="69"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="52"/>
+      <c r="Q22" s="69"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -12312,23 +12312,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="110"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="111"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="116"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="114"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="114"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="68"/>
+      <c r="A23" s="111"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="115"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="52"/>
+      <c r="Q23" s="69"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -12340,23 +12340,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="110"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="111"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="116"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="114"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="114"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="68"/>
+      <c r="A24" s="111"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="112"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="115"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="69"/>
+      <c r="O24" s="115"/>
+      <c r="P24" s="52"/>
+      <c r="Q24" s="69"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -12368,23 +12368,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="110"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="111"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="116"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="114"/>
-      <c r="M25" s="51"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="68"/>
+      <c r="A25" s="111"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="115"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="69"/>
+      <c r="O25" s="115"/>
+      <c r="P25" s="52"/>
+      <c r="Q25" s="69"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -12396,23 +12396,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="110"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="111"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="114"/>
-      <c r="M26" s="51"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="68"/>
+      <c r="A26" s="111"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="112"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="115"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="69"/>
+      <c r="O26" s="115"/>
+      <c r="P26" s="52"/>
+      <c r="Q26" s="69"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -12424,23 +12424,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="110"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="111"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="68"/>
+      <c r="A27" s="111"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="115"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="69"/>
+      <c r="O27" s="115"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="69"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -12452,23 +12452,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="110"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="111"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="114"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="68"/>
-      <c r="O28" s="114"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="68"/>
+      <c r="A28" s="111"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="115"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="69"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="69"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -12480,23 +12480,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="110"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="111"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="114"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="114"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="68"/>
+      <c r="A29" s="111"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="69"/>
+      <c r="L29" s="115"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="69"/>
+      <c r="O29" s="115"/>
+      <c r="P29" s="52"/>
+      <c r="Q29" s="69"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -12508,23 +12508,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="110"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="111"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="111"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="116"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="116"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="114"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="114"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="68"/>
+      <c r="A30" s="111"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="112"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="115"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="69"/>
+      <c r="O30" s="115"/>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="69"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -12536,23 +12536,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="112"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="113"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="113"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="119"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="119"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="115"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="115"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="55"/>
+      <c r="A31" s="113"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="114"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="114"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="116"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="116"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="56"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>

--- a/document/成果物ドキュメント_タスク登録機能.xlsx
+++ b/document/成果物ドキュメント_タスク登録機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75090775-18C5-408C-A52A-311715ED60A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D7D426-2185-46E0-A93E-98B33FF8D3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,18 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="115">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
     <t>初版</t>
-  </si>
-  <si>
-    <t>YYYY/MM/DD</t>
-  </si>
-  <si>
-    <t>チーム名</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -253,56 +247,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>4a.ユーザーが期限とメモの片方または両方を入力しなかった場合
-4a1.基本フロー5.へ</t>
-    <rPh sb="8" eb="10">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>カタホウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>リョウホウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>キホン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク登録機能</t>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ユーザーがシステムにログインしていること</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクがDBに登録され、タスク一覧表示画面に表示されていること</t>
-    <rPh sb="7" eb="9">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ヒョウジ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -441,79 +386,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク名を入力する</t>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>カテゴリ情報を選択する</t>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>担当者をユーザー一覧から選択する</t>
-    <rPh sb="0" eb="3">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ステータス情報を選択する</t>
-    <rPh sb="5" eb="7">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>メモを入力する</t>
-    <rPh sb="3" eb="5">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>入力した内容をサーブレットに送信する</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ソウシン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>メニュー画面に戻る</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>assigneeId</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -557,87 +429,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.ユーザーがメニュー画面のタスク登録を選択する
-2.システムがタスク登録画面を表示する
-3.ユーザーがタスク名・カテゴリ情報・期限・担当者情報・ステータス情報・メモを入力する
-4.ユーザーがタスク登録を確定する
-5.システムが入力された内容と現在日時をデータベースに登録する
-6.システムがタスク登録完了画面を表示する</t>
-    <rPh sb="11" eb="13">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="67" eb="70">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="99" eb="101">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="102" eb="104">
-      <t>カクテイ</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="119" eb="121">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>ゲンザイ</t>
-    </rPh>
-    <rPh sb="124" eb="126">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="134" eb="136">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="149" eb="151">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="151" eb="153">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="153" eb="155">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="156" eb="158">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク登録完了画面</t>
     <rPh sb="3" eb="5">
       <t>トウロク</t>
@@ -661,26 +452,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>期限をカレンダーから選択する
-カレンダーに過去の日付は表示されないようにする</t>
-    <rPh sb="0" eb="2">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>(空文字)</t>
     <rPh sb="1" eb="4">
       <t>カラモジ</t>
@@ -695,24 +466,162 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>6a.システムが入力された内容をデータベースに登録できない場合
-6a1.システムがタスク登録エラー画面を表示する</t>
-    <rPh sb="29" eb="31">
+    <t>TaskManager62</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクを登録する</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>対象のタスクがデータベースに登録されていること</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>システムに新規のタスクを登録する</t>
+    <rPh sb="5" eb="7">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1．ユーザーがメニュー画面でタスクの登録を選択する
+2．システムがタスク登録画面を表示する
+3．ユーザーが登録するタスクの情報を入力する
+4．ユーザーがタスクの登録を確定する
+5．システムが入力された内容と現在日時をデータベースに登録する
+6．システムがタスク登録完了画面を表示する</t>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>3a1．ユーザーがタスクの登録を中止し、直前の画面に戻る
+3a2．システムがメニュー画面を表示する</t>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チュウシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>チョクゼン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>6a．対象のタスクがデータベースに存在する場合
+6a1．システムがタスク登録エラー画面を表示する</t>
+    <rPh sb="3" eb="5">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
       <t>バアイ</t>
     </rPh>
-    <rPh sb="49" eb="51">
+    <rPh sb="41" eb="43">
       <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>TaskManager62</t>
+    <t>チーム名 62期</t>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスクをDBに登録する</t>
-    <rPh sb="7" eb="9">
-      <t>トウロク</t>
+    <t>過去の日付が表示されないようにする</t>
+    <rPh sb="0" eb="2">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オモテ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -721,8 +630,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
+    <numFmt numFmtId="181" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1471,7 +1381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1598,35 +1508,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1634,22 +1517,67 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1658,58 +1586,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1724,10 +1613,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1745,65 +1646,86 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1811,29 +1733,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1856,23 +1775,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>676956</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>161159</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>182118</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>77278</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1074964</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>35241</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>333329</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>138544</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48A278B9-7AB9-AF77-7ABE-B21391CB6A44}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA7B9EFF-AC8D-C0FF-63BA-8C1BE4218F44}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1895,8 +1814,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1697492" y="1576302"/>
-          <a:ext cx="4861151" cy="3466368"/>
+          <a:off x="528482" y="1601278"/>
+          <a:ext cx="7494120" cy="3178539"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1922,23 +1841,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>110434</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>138546</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>103909</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>386522</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>16209</xdr:rowOff>
+      <xdr:colOff>298029</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>134215</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD77C3F9-81F7-F769-7BEE-43D1F98A46AF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D86BE5E1-0044-7C1A-2AE3-AE1033F4312D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1961,8 +1880,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="1049130"/>
-          <a:ext cx="8130761" cy="4709688"/>
+          <a:off x="484910" y="1160318"/>
+          <a:ext cx="7502392" cy="4082761"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2379,85 +2298,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="61"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2477,46 +2396,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="90" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
+      <c r="E8" s="87" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="86" t="s">
+      <c r="G13" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="69"/>
-      <c r="I13" s="86" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="52"/>
-      <c r="K13" s="69"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="123">
+        <v>46127</v>
+      </c>
+      <c r="J13" s="43"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="86"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="69"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="45"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="86"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="69"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="45"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2525,13 +2444,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="87" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
+      <c r="G17" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3545,216 +3464,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="80" t="s">
+      <c r="G1" s="60"/>
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="80" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="120">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="56"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="57"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="91"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="62"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="93" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="81" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="106" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="108"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="93" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81" t="s">
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="44"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="43"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="44"/>
+    </row>
+    <row r="9" spans="1:10" ht="93.75" customHeight="1">
+      <c r="A9" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="109" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="44"/>
+    </row>
+    <row r="10" spans="1:10" ht="56.25" customHeight="1">
+      <c r="A10" s="102"/>
+      <c r="B10" s="92" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="45"/>
+      <c r="D10" s="109" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="44"/>
+    </row>
+    <row r="11" spans="1:10" ht="56.25" customHeight="1">
+      <c r="A11" s="103"/>
+      <c r="B11" s="92" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="45"/>
+      <c r="D11" s="109" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="44"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="85">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="77"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="50"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
-    </row>
-    <row r="9" spans="1:10" ht="114" customHeight="1">
-      <c r="A9" s="70" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="53"/>
-    </row>
-    <row r="10" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A10" s="71"/>
-      <c r="B10" s="73" t="s">
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="44"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="53"/>
-    </row>
-    <row r="11" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A11" s="72"/>
-      <c r="B11" s="73" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="54" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="53"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="44"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="104"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4745,17 +4664,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4764,14 +4680,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4790,72 +4709,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="80" t="s">
+      <c r="A1" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="60"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="80" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="91">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="77">
         <v>46125</v>
       </c>
-      <c r="I2" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="77"/>
+      <c r="I2" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="91"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5003,7 +4922,6 @@
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
@@ -6210,72 +6128,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="80" t="s">
+      <c r="A1" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="60"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="80" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="91">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="77">
         <v>46125</v>
       </c>
-      <c r="I2" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="77"/>
+      <c r="I2" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="91"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6330,7 +6248,6 @@
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
@@ -7626,424 +7543,410 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="60"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="77">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="56"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="57"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="57"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="62"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="91">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="77"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="60"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="65"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="68"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="66"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="68"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="68"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="68"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="66"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="68"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="101" t="s">
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="44"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="43"/>
+      <c r="J16" s="44"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="44"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="80" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="44"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.350000000000001" customHeight="1">
+      <c r="A19" s="80" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="43"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="109" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="43"/>
+      <c r="J19" s="44"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="102"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="104"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="60"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="105"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="105"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="105"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="60"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="105"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="60"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="105"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="60"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="105"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="100" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="53"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="100" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="16" t="s">
+      <c r="G20" s="18"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="44"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="80" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="100" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="106" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="52"/>
-      <c r="J16" s="53"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="93" t="s">
+      <c r="B21" s="43"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="18"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="44"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="I17" s="52"/>
-      <c r="J17" s="53"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="93" t="s">
+      <c r="B22" s="43"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="46"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="44"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="52"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="18"/>
-      <c r="H18" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="I18" s="52"/>
-      <c r="J18" s="53"/>
-    </row>
-    <row r="19" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A19" s="93" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="52"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="H19" s="54" t="s">
-        <v>117</v>
-      </c>
-      <c r="I19" s="52"/>
-      <c r="J19" s="53"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="93" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="G20" s="18"/>
-      <c r="H20" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="I20" s="52"/>
-      <c r="J20" s="53"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="93" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="52"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="17" t="s">
+      <c r="B23" s="81"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="38" t="s">
         <v>89</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="18"/>
-      <c r="H21" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="I21" s="52"/>
-      <c r="J21" s="53"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="93" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="H22" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="I22" s="52"/>
-      <c r="J22" s="53"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="93" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="94"/>
-      <c r="C23" s="95"/>
-      <c r="D23" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>94</v>
       </c>
       <c r="F23" s="39"/>
       <c r="G23" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="I23" s="96"/>
-      <c r="J23" s="97"/>
+        <v>93</v>
+      </c>
+      <c r="H23" s="46"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="79"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="99" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="56"/>
+      <c r="A24" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="95"/>
+      <c r="C24" s="96"/>
       <c r="D24" s="19" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="I24" s="43"/>
-      <c r="J24" s="44"/>
+        <v>88</v>
+      </c>
+      <c r="H24" s="51"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="104"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9024,11 +8927,18 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9045,18 +8955,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9080,278 +8983,1572 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="60"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="77">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="56"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="57"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="57"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="62"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="91">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="77"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="60"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="65"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="68"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="66"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="68"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="68"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="68"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="66"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="68"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="101" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="100" t="s">
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="44"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="102"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="104"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="60"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="105"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="105"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="105"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="60"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="105"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="60"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="105"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="60"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="105"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="100" t="s">
+      <c r="B15" s="43"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="53"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="100" t="s">
+      <c r="J15" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="15" t="s">
+      <c r="B16" s="43"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="100" t="s">
+      <c r="E16" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="106" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="52"/>
-      <c r="J16" s="53"/>
+      <c r="H16" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="43"/>
+      <c r="J16" s="44"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="93" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="94"/>
-      <c r="C17" s="95"/>
+      <c r="A17" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="81"/>
+      <c r="C17" s="82"/>
       <c r="D17" s="38" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F17" s="38"/>
       <c r="G17" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="H17" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="I17" s="96"/>
-      <c r="J17" s="97"/>
+        <v>88</v>
+      </c>
+      <c r="H17" s="46"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="79"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="99"/>
-      <c r="B18" s="107"/>
-      <c r="C18" s="108"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="110"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="53"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B70C3665-E52C-464E-B22A-6BC197D77956}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J995"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="60"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="77">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="56"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="57"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="57"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="62"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="65"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="68"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="66"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="68"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="68"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="68"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="66"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="68"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="44"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="43"/>
+      <c r="J16" s="44"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="81"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="38"/>
+      <c r="G17" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="I17" s="78"/>
+      <c r="J17" s="79"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A18" s="48"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10334,1307 +11531,6 @@
   <mergeCells count="21">
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B70C3665-E52C-464E-B22A-6BC197D77956}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J995"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="91">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="77"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="60"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="98" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="101" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="102"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="104"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="60"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="105"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="105"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="105"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="60"/>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="105"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="60"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="105"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="60"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="105"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="100" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="53"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="100" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="100" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="106" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="52"/>
-      <c r="J16" s="53"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="93" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="94"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="38"/>
-      <c r="G17" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="I17" s="96"/>
-      <c r="J17" s="97"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="99"/>
-      <c r="B18" s="107"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="110"/>
-    </row>
-    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="33" ht="12.75" customHeight="1"/>
-    <row r="34" ht="12.75" customHeight="1"/>
-    <row r="35" ht="12.75" customHeight="1"/>
-    <row r="36" ht="12.75" customHeight="1"/>
-    <row r="37" ht="12.75" customHeight="1"/>
-    <row r="38" ht="12.75" customHeight="1"/>
-    <row r="39" ht="12.75" customHeight="1"/>
-    <row r="40" ht="12.75" customHeight="1"/>
-    <row r="41" ht="12.75" customHeight="1"/>
-    <row r="42" ht="12.75" customHeight="1"/>
-    <row r="43" ht="12.75" customHeight="1"/>
-    <row r="44" ht="12.75" customHeight="1"/>
-    <row r="45" ht="12.75" customHeight="1"/>
-    <row r="46" ht="12.75" customHeight="1"/>
-    <row r="47" ht="12.75" customHeight="1"/>
-    <row r="48" ht="12.75" customHeight="1"/>
-    <row r="49" ht="12.75" customHeight="1"/>
-    <row r="50" ht="12.75" customHeight="1"/>
-    <row r="51" ht="12.75" customHeight="1"/>
-    <row r="52" ht="12.75" customHeight="1"/>
-    <row r="53" ht="12.75" customHeight="1"/>
-    <row r="54" ht="12.75" customHeight="1"/>
-    <row r="55" ht="12.75" customHeight="1"/>
-    <row r="56" ht="12.75" customHeight="1"/>
-    <row r="57" ht="12.75" customHeight="1"/>
-    <row r="58" ht="12.75" customHeight="1"/>
-    <row r="59" ht="12.75" customHeight="1"/>
-    <row r="60" ht="12.75" customHeight="1"/>
-    <row r="61" ht="12.75" customHeight="1"/>
-    <row r="62" ht="12.75" customHeight="1"/>
-    <row r="63" ht="12.75" customHeight="1"/>
-    <row r="64" ht="12.75" customHeight="1"/>
-    <row r="65" ht="12.75" customHeight="1"/>
-    <row r="66" ht="12.75" customHeight="1"/>
-    <row r="67" ht="12.75" customHeight="1"/>
-    <row r="68" ht="12.75" customHeight="1"/>
-    <row r="69" ht="12.75" customHeight="1"/>
-    <row r="70" ht="12.75" customHeight="1"/>
-    <row r="71" ht="12.75" customHeight="1"/>
-    <row r="72" ht="12.75" customHeight="1"/>
-    <row r="73" ht="12.75" customHeight="1"/>
-    <row r="74" ht="12.75" customHeight="1"/>
-    <row r="75" ht="12.75" customHeight="1"/>
-    <row r="76" ht="12.75" customHeight="1"/>
-    <row r="77" ht="12.75" customHeight="1"/>
-    <row r="78" ht="12.75" customHeight="1"/>
-    <row r="79" ht="12.75" customHeight="1"/>
-    <row r="80" ht="12.75" customHeight="1"/>
-    <row r="81" ht="12.75" customHeight="1"/>
-    <row r="82" ht="12.75" customHeight="1"/>
-    <row r="83" ht="12.75" customHeight="1"/>
-    <row r="84" ht="12.75" customHeight="1"/>
-    <row r="85" ht="12.75" customHeight="1"/>
-    <row r="86" ht="12.75" customHeight="1"/>
-    <row r="87" ht="12.75" customHeight="1"/>
-    <row r="88" ht="12.75" customHeight="1"/>
-    <row r="89" ht="12.75" customHeight="1"/>
-    <row r="90" ht="12.75" customHeight="1"/>
-    <row r="91" ht="12.75" customHeight="1"/>
-    <row r="92" ht="12.75" customHeight="1"/>
-    <row r="93" ht="12.75" customHeight="1"/>
-    <row r="94" ht="12.75" customHeight="1"/>
-    <row r="95" ht="12.75" customHeight="1"/>
-    <row r="96" ht="12.75" customHeight="1"/>
-    <row r="97" ht="12.75" customHeight="1"/>
-    <row r="98" ht="12.75" customHeight="1"/>
-    <row r="99" ht="12.75" customHeight="1"/>
-    <row r="100" ht="12.75" customHeight="1"/>
-    <row r="101" ht="12.75" customHeight="1"/>
-    <row r="102" ht="12.75" customHeight="1"/>
-    <row r="103" ht="12.75" customHeight="1"/>
-    <row r="104" ht="12.75" customHeight="1"/>
-    <row r="105" ht="12.75" customHeight="1"/>
-    <row r="106" ht="12.75" customHeight="1"/>
-    <row r="107" ht="12.75" customHeight="1"/>
-    <row r="108" ht="12.75" customHeight="1"/>
-    <row r="109" ht="12.75" customHeight="1"/>
-    <row r="110" ht="12.75" customHeight="1"/>
-    <row r="111" ht="12.75" customHeight="1"/>
-    <row r="112" ht="12.75" customHeight="1"/>
-    <row r="113" ht="12.75" customHeight="1"/>
-    <row r="114" ht="12.75" customHeight="1"/>
-    <row r="115" ht="12.75" customHeight="1"/>
-    <row r="116" ht="12.75" customHeight="1"/>
-    <row r="117" ht="12.75" customHeight="1"/>
-    <row r="118" ht="12.75" customHeight="1"/>
-    <row r="119" ht="12.75" customHeight="1"/>
-    <row r="120" ht="12.75" customHeight="1"/>
-    <row r="121" ht="12.75" customHeight="1"/>
-    <row r="122" ht="12.75" customHeight="1"/>
-    <row r="123" ht="12.75" customHeight="1"/>
-    <row r="124" ht="12.75" customHeight="1"/>
-    <row r="125" ht="12.75" customHeight="1"/>
-    <row r="126" ht="12.75" customHeight="1"/>
-    <row r="127" ht="12.75" customHeight="1"/>
-    <row r="128" ht="12.75" customHeight="1"/>
-    <row r="129" ht="12.75" customHeight="1"/>
-    <row r="130" ht="12.75" customHeight="1"/>
-    <row r="131" ht="12.75" customHeight="1"/>
-    <row r="132" ht="12.75" customHeight="1"/>
-    <row r="133" ht="12.75" customHeight="1"/>
-    <row r="134" ht="12.75" customHeight="1"/>
-    <row r="135" ht="12.75" customHeight="1"/>
-    <row r="136" ht="12.75" customHeight="1"/>
-    <row r="137" ht="12.75" customHeight="1"/>
-    <row r="138" ht="12.75" customHeight="1"/>
-    <row r="139" ht="12.75" customHeight="1"/>
-    <row r="140" ht="12.75" customHeight="1"/>
-    <row r="141" ht="12.75" customHeight="1"/>
-    <row r="142" ht="12.75" customHeight="1"/>
-    <row r="143" ht="12.75" customHeight="1"/>
-    <row r="144" ht="12.75" customHeight="1"/>
-    <row r="145" ht="12.75" customHeight="1"/>
-    <row r="146" ht="12.75" customHeight="1"/>
-    <row r="147" ht="12.75" customHeight="1"/>
-    <row r="148" ht="12.75" customHeight="1"/>
-    <row r="149" ht="12.75" customHeight="1"/>
-    <row r="150" ht="12.75" customHeight="1"/>
-    <row r="151" ht="12.75" customHeight="1"/>
-    <row r="152" ht="12.75" customHeight="1"/>
-    <row r="153" ht="12.75" customHeight="1"/>
-    <row r="154" ht="12.75" customHeight="1"/>
-    <row r="155" ht="12.75" customHeight="1"/>
-    <row r="156" ht="12.75" customHeight="1"/>
-    <row r="157" ht="12.75" customHeight="1"/>
-    <row r="158" ht="12.75" customHeight="1"/>
-    <row r="159" ht="12.75" customHeight="1"/>
-    <row r="160" ht="12.75" customHeight="1"/>
-    <row r="161" ht="12.75" customHeight="1"/>
-    <row r="162" ht="12.75" customHeight="1"/>
-    <row r="163" ht="12.75" customHeight="1"/>
-    <row r="164" ht="12.75" customHeight="1"/>
-    <row r="165" ht="12.75" customHeight="1"/>
-    <row r="166" ht="12.75" customHeight="1"/>
-    <row r="167" ht="12.75" customHeight="1"/>
-    <row r="168" ht="12.75" customHeight="1"/>
-    <row r="169" ht="12.75" customHeight="1"/>
-    <row r="170" ht="12.75" customHeight="1"/>
-    <row r="171" ht="12.75" customHeight="1"/>
-    <row r="172" ht="12.75" customHeight="1"/>
-    <row r="173" ht="12.75" customHeight="1"/>
-    <row r="174" ht="12.75" customHeight="1"/>
-    <row r="175" ht="12.75" customHeight="1"/>
-    <row r="176" ht="12.75" customHeight="1"/>
-    <row r="177" ht="12.75" customHeight="1"/>
-    <row r="178" ht="12.75" customHeight="1"/>
-    <row r="179" ht="12.75" customHeight="1"/>
-    <row r="180" ht="12.75" customHeight="1"/>
-    <row r="181" ht="12.75" customHeight="1"/>
-    <row r="182" ht="12.75" customHeight="1"/>
-    <row r="183" ht="12.75" customHeight="1"/>
-    <row r="184" ht="12.75" customHeight="1"/>
-    <row r="185" ht="12.75" customHeight="1"/>
-    <row r="186" ht="12.75" customHeight="1"/>
-    <row r="187" ht="12.75" customHeight="1"/>
-    <row r="188" ht="12.75" customHeight="1"/>
-    <row r="189" ht="12.75" customHeight="1"/>
-    <row r="190" ht="12.75" customHeight="1"/>
-    <row r="191" ht="12.75" customHeight="1"/>
-    <row r="192" ht="12.75" customHeight="1"/>
-    <row r="193" ht="12.75" customHeight="1"/>
-    <row r="194" ht="12.75" customHeight="1"/>
-    <row r="195" ht="12.75" customHeight="1"/>
-    <row r="196" ht="12.75" customHeight="1"/>
-    <row r="197" ht="12.75" customHeight="1"/>
-    <row r="198" ht="12.75" customHeight="1"/>
-    <row r="199" ht="12.75" customHeight="1"/>
-    <row r="200" ht="12.75" customHeight="1"/>
-    <row r="201" ht="12.75" customHeight="1"/>
-    <row r="202" ht="12.75" customHeight="1"/>
-    <row r="203" ht="12.75" customHeight="1"/>
-    <row r="204" ht="12.75" customHeight="1"/>
-    <row r="205" ht="12.75" customHeight="1"/>
-    <row r="206" ht="12.75" customHeight="1"/>
-    <row r="207" ht="12.75" customHeight="1"/>
-    <row r="208" ht="12.75" customHeight="1"/>
-    <row r="209" ht="12.75" customHeight="1"/>
-    <row r="210" ht="12.75" customHeight="1"/>
-    <row r="211" ht="12.75" customHeight="1"/>
-    <row r="212" ht="12.75" customHeight="1"/>
-    <row r="213" ht="12.75" customHeight="1"/>
-    <row r="214" ht="12.75" customHeight="1"/>
-    <row r="215" ht="12.75" customHeight="1"/>
-    <row r="216" ht="12.75" customHeight="1"/>
-    <row r="217" ht="12.75" customHeight="1"/>
-    <row r="218" ht="12.75" customHeight="1"/>
-    <row r="219" ht="12.75" customHeight="1"/>
-    <row r="220" ht="12.75" customHeight="1"/>
-    <row r="221" ht="12.75" customHeight="1"/>
-    <row r="222" ht="12.75" customHeight="1"/>
-    <row r="223" ht="12.75" customHeight="1"/>
-    <row r="224" ht="12.75" customHeight="1"/>
-    <row r="225" ht="12.75" customHeight="1"/>
-    <row r="226" ht="12.75" customHeight="1"/>
-    <row r="227" ht="12.75" customHeight="1"/>
-    <row r="228" ht="12.75" customHeight="1"/>
-    <row r="229" ht="12.75" customHeight="1"/>
-    <row r="230" ht="12.75" customHeight="1"/>
-    <row r="231" ht="12.75" customHeight="1"/>
-    <row r="232" ht="12.75" customHeight="1"/>
-    <row r="233" ht="12.75" customHeight="1"/>
-    <row r="234" ht="12.75" customHeight="1"/>
-    <row r="235" ht="12.75" customHeight="1"/>
-    <row r="236" ht="12.75" customHeight="1"/>
-    <row r="237" ht="12.75" customHeight="1"/>
-    <row r="238" ht="12.75" customHeight="1"/>
-    <row r="239" ht="12.75" customHeight="1"/>
-    <row r="240" ht="12.75" customHeight="1"/>
-    <row r="241" ht="12.75" customHeight="1"/>
-    <row r="242" ht="12.75" customHeight="1"/>
-    <row r="243" ht="12.75" customHeight="1"/>
-    <row r="244" ht="12.75" customHeight="1"/>
-    <row r="245" ht="12.75" customHeight="1"/>
-    <row r="246" ht="12.75" customHeight="1"/>
-    <row r="247" ht="12.75" customHeight="1"/>
-    <row r="248" ht="12.75" customHeight="1"/>
-    <row r="249" ht="12.75" customHeight="1"/>
-    <row r="250" ht="12.75" customHeight="1"/>
-    <row r="251" ht="12.75" customHeight="1"/>
-    <row r="252" ht="12.75" customHeight="1"/>
-    <row r="253" ht="12.75" customHeight="1"/>
-    <row r="254" ht="12.75" customHeight="1"/>
-    <row r="255" ht="12.75" customHeight="1"/>
-    <row r="256" ht="12.75" customHeight="1"/>
-    <row r="257" ht="12.75" customHeight="1"/>
-    <row r="258" ht="12.75" customHeight="1"/>
-    <row r="259" ht="12.75" customHeight="1"/>
-    <row r="260" ht="12.75" customHeight="1"/>
-    <row r="261" ht="12.75" customHeight="1"/>
-    <row r="262" ht="12.75" customHeight="1"/>
-    <row r="263" ht="12.75" customHeight="1"/>
-    <row r="264" ht="12.75" customHeight="1"/>
-    <row r="265" ht="12.75" customHeight="1"/>
-    <row r="266" ht="12.75" customHeight="1"/>
-    <row r="267" ht="12.75" customHeight="1"/>
-    <row r="268" ht="12.75" customHeight="1"/>
-    <row r="269" ht="12.75" customHeight="1"/>
-    <row r="270" ht="12.75" customHeight="1"/>
-    <row r="271" ht="12.75" customHeight="1"/>
-    <row r="272" ht="12.75" customHeight="1"/>
-    <row r="273" ht="12.75" customHeight="1"/>
-    <row r="274" ht="12.75" customHeight="1"/>
-    <row r="275" ht="12.75" customHeight="1"/>
-    <row r="276" ht="12.75" customHeight="1"/>
-    <row r="277" ht="12.75" customHeight="1"/>
-    <row r="278" ht="12.75" customHeight="1"/>
-    <row r="279" ht="12.75" customHeight="1"/>
-    <row r="280" ht="12.75" customHeight="1"/>
-    <row r="281" ht="12.75" customHeight="1"/>
-    <row r="282" ht="12.75" customHeight="1"/>
-    <row r="283" ht="12.75" customHeight="1"/>
-    <row r="284" ht="12.75" customHeight="1"/>
-    <row r="285" ht="12.75" customHeight="1"/>
-    <row r="286" ht="12.75" customHeight="1"/>
-    <row r="287" ht="12.75" customHeight="1"/>
-    <row r="288" ht="12.75" customHeight="1"/>
-    <row r="289" ht="12.75" customHeight="1"/>
-    <row r="290" ht="12.75" customHeight="1"/>
-    <row r="291" ht="12.75" customHeight="1"/>
-    <row r="292" ht="12.75" customHeight="1"/>
-    <row r="293" ht="12.75" customHeight="1"/>
-    <row r="294" ht="12.75" customHeight="1"/>
-    <row r="295" ht="12.75" customHeight="1"/>
-    <row r="296" ht="12.75" customHeight="1"/>
-    <row r="297" ht="12.75" customHeight="1"/>
-    <row r="298" ht="12.75" customHeight="1"/>
-    <row r="299" ht="12.75" customHeight="1"/>
-    <row r="300" ht="12.75" customHeight="1"/>
-    <row r="301" ht="12.75" customHeight="1"/>
-    <row r="302" ht="12.75" customHeight="1"/>
-    <row r="303" ht="12.75" customHeight="1"/>
-    <row r="304" ht="12.75" customHeight="1"/>
-    <row r="305" ht="12.75" customHeight="1"/>
-    <row r="306" ht="12.75" customHeight="1"/>
-    <row r="307" ht="12.75" customHeight="1"/>
-    <row r="308" ht="12.75" customHeight="1"/>
-    <row r="309" ht="12.75" customHeight="1"/>
-    <row r="310" ht="12.75" customHeight="1"/>
-    <row r="311" ht="12.75" customHeight="1"/>
-    <row r="312" ht="12.75" customHeight="1"/>
-    <row r="313" ht="12.75" customHeight="1"/>
-    <row r="314" ht="12.75" customHeight="1"/>
-    <row r="315" ht="12.75" customHeight="1"/>
-    <row r="316" ht="12.75" customHeight="1"/>
-    <row r="317" ht="12.75" customHeight="1"/>
-    <row r="318" ht="12.75" customHeight="1"/>
-    <row r="319" ht="12.75" customHeight="1"/>
-    <row r="320" ht="12.75" customHeight="1"/>
-    <row r="321" ht="12.75" customHeight="1"/>
-    <row r="322" ht="12.75" customHeight="1"/>
-    <row r="323" ht="12.75" customHeight="1"/>
-    <row r="324" ht="12.75" customHeight="1"/>
-    <row r="325" ht="12.75" customHeight="1"/>
-    <row r="326" ht="12.75" customHeight="1"/>
-    <row r="327" ht="12.75" customHeight="1"/>
-    <row r="328" ht="12.75" customHeight="1"/>
-    <row r="329" ht="12.75" customHeight="1"/>
-    <row r="330" ht="12.75" customHeight="1"/>
-    <row r="331" ht="12.75" customHeight="1"/>
-    <row r="332" ht="12.75" customHeight="1"/>
-    <row r="333" ht="12.75" customHeight="1"/>
-    <row r="334" ht="12.75" customHeight="1"/>
-    <row r="335" ht="12.75" customHeight="1"/>
-    <row r="336" ht="12.75" customHeight="1"/>
-    <row r="337" ht="12.75" customHeight="1"/>
-    <row r="338" ht="12.75" customHeight="1"/>
-    <row r="339" ht="12.75" customHeight="1"/>
-    <row r="340" ht="12.75" customHeight="1"/>
-    <row r="341" ht="12.75" customHeight="1"/>
-    <row r="342" ht="12.75" customHeight="1"/>
-    <row r="343" ht="12.75" customHeight="1"/>
-    <row r="344" ht="12.75" customHeight="1"/>
-    <row r="345" ht="12.75" customHeight="1"/>
-    <row r="346" ht="12.75" customHeight="1"/>
-    <row r="347" ht="12.75" customHeight="1"/>
-    <row r="348" ht="12.75" customHeight="1"/>
-    <row r="349" ht="12.75" customHeight="1"/>
-    <row r="350" ht="12.75" customHeight="1"/>
-    <row r="351" ht="12.75" customHeight="1"/>
-    <row r="352" ht="12.75" customHeight="1"/>
-    <row r="353" ht="12.75" customHeight="1"/>
-    <row r="354" ht="12.75" customHeight="1"/>
-    <row r="355" ht="12.75" customHeight="1"/>
-    <row r="356" ht="12.75" customHeight="1"/>
-    <row r="357" ht="12.75" customHeight="1"/>
-    <row r="358" ht="12.75" customHeight="1"/>
-    <row r="359" ht="12.75" customHeight="1"/>
-    <row r="360" ht="12.75" customHeight="1"/>
-    <row r="361" ht="12.75" customHeight="1"/>
-    <row r="362" ht="12.75" customHeight="1"/>
-    <row r="363" ht="12.75" customHeight="1"/>
-    <row r="364" ht="12.75" customHeight="1"/>
-    <row r="365" ht="12.75" customHeight="1"/>
-    <row r="366" ht="12.75" customHeight="1"/>
-    <row r="367" ht="12.75" customHeight="1"/>
-    <row r="368" ht="12.75" customHeight="1"/>
-    <row r="369" ht="12.75" customHeight="1"/>
-    <row r="370" ht="12.75" customHeight="1"/>
-    <row r="371" ht="12.75" customHeight="1"/>
-    <row r="372" ht="12.75" customHeight="1"/>
-    <row r="373" ht="12.75" customHeight="1"/>
-    <row r="374" ht="12.75" customHeight="1"/>
-    <row r="375" ht="12.75" customHeight="1"/>
-    <row r="376" ht="12.75" customHeight="1"/>
-    <row r="377" ht="12.75" customHeight="1"/>
-    <row r="378" ht="12.75" customHeight="1"/>
-    <row r="379" ht="12.75" customHeight="1"/>
-    <row r="380" ht="12.75" customHeight="1"/>
-    <row r="381" ht="12.75" customHeight="1"/>
-    <row r="382" ht="12.75" customHeight="1"/>
-    <row r="383" ht="12.75" customHeight="1"/>
-    <row r="384" ht="12.75" customHeight="1"/>
-    <row r="385" ht="12.75" customHeight="1"/>
-    <row r="386" ht="12.75" customHeight="1"/>
-    <row r="387" ht="12.75" customHeight="1"/>
-    <row r="388" ht="12.75" customHeight="1"/>
-    <row r="389" ht="12.75" customHeight="1"/>
-    <row r="390" ht="12.75" customHeight="1"/>
-    <row r="391" ht="12.75" customHeight="1"/>
-    <row r="392" ht="12.75" customHeight="1"/>
-    <row r="393" ht="12.75" customHeight="1"/>
-    <row r="394" ht="12.75" customHeight="1"/>
-    <row r="395" ht="12.75" customHeight="1"/>
-    <row r="396" ht="12.75" customHeight="1"/>
-    <row r="397" ht="12.75" customHeight="1"/>
-    <row r="398" ht="12.75" customHeight="1"/>
-    <row r="399" ht="12.75" customHeight="1"/>
-    <row r="400" ht="12.75" customHeight="1"/>
-    <row r="401" ht="12.75" customHeight="1"/>
-    <row r="402" ht="12.75" customHeight="1"/>
-    <row r="403" ht="12.75" customHeight="1"/>
-    <row r="404" ht="12.75" customHeight="1"/>
-    <row r="405" ht="12.75" customHeight="1"/>
-    <row r="406" ht="12.75" customHeight="1"/>
-    <row r="407" ht="12.75" customHeight="1"/>
-    <row r="408" ht="12.75" customHeight="1"/>
-    <row r="409" ht="12.75" customHeight="1"/>
-    <row r="410" ht="12.75" customHeight="1"/>
-    <row r="411" ht="12.75" customHeight="1"/>
-    <row r="412" ht="12.75" customHeight="1"/>
-    <row r="413" ht="12.75" customHeight="1"/>
-    <row r="414" ht="12.75" customHeight="1"/>
-    <row r="415" ht="12.75" customHeight="1"/>
-    <row r="416" ht="12.75" customHeight="1"/>
-    <row r="417" ht="12.75" customHeight="1"/>
-    <row r="418" ht="12.75" customHeight="1"/>
-    <row r="419" ht="12.75" customHeight="1"/>
-    <row r="420" ht="12.75" customHeight="1"/>
-    <row r="421" ht="12.75" customHeight="1"/>
-    <row r="422" ht="12.75" customHeight="1"/>
-    <row r="423" ht="12.75" customHeight="1"/>
-    <row r="424" ht="12.75" customHeight="1"/>
-    <row r="425" ht="12.75" customHeight="1"/>
-    <row r="426" ht="12.75" customHeight="1"/>
-    <row r="427" ht="12.75" customHeight="1"/>
-    <row r="428" ht="12.75" customHeight="1"/>
-    <row r="429" ht="12.75" customHeight="1"/>
-    <row r="430" ht="12.75" customHeight="1"/>
-    <row r="431" ht="12.75" customHeight="1"/>
-    <row r="432" ht="12.75" customHeight="1"/>
-    <row r="433" ht="12.75" customHeight="1"/>
-    <row r="434" ht="12.75" customHeight="1"/>
-    <row r="435" ht="12.75" customHeight="1"/>
-    <row r="436" ht="12.75" customHeight="1"/>
-    <row r="437" ht="12.75" customHeight="1"/>
-    <row r="438" ht="12.75" customHeight="1"/>
-    <row r="439" ht="12.75" customHeight="1"/>
-    <row r="440" ht="12.75" customHeight="1"/>
-    <row r="441" ht="12.75" customHeight="1"/>
-    <row r="442" ht="12.75" customHeight="1"/>
-    <row r="443" ht="12.75" customHeight="1"/>
-    <row r="444" ht="12.75" customHeight="1"/>
-    <row r="445" ht="12.75" customHeight="1"/>
-    <row r="446" ht="12.75" customHeight="1"/>
-    <row r="447" ht="12.75" customHeight="1"/>
-    <row r="448" ht="12.75" customHeight="1"/>
-    <row r="449" ht="12.75" customHeight="1"/>
-    <row r="450" ht="12.75" customHeight="1"/>
-    <row r="451" ht="12.75" customHeight="1"/>
-    <row r="452" ht="12.75" customHeight="1"/>
-    <row r="453" ht="12.75" customHeight="1"/>
-    <row r="454" ht="12.75" customHeight="1"/>
-    <row r="455" ht="12.75" customHeight="1"/>
-    <row r="456" ht="12.75" customHeight="1"/>
-    <row r="457" ht="12.75" customHeight="1"/>
-    <row r="458" ht="12.75" customHeight="1"/>
-    <row r="459" ht="12.75" customHeight="1"/>
-    <row r="460" ht="12.75" customHeight="1"/>
-    <row r="461" ht="12.75" customHeight="1"/>
-    <row r="462" ht="12.75" customHeight="1"/>
-    <row r="463" ht="12.75" customHeight="1"/>
-    <row r="464" ht="12.75" customHeight="1"/>
-    <row r="465" ht="12.75" customHeight="1"/>
-    <row r="466" ht="12.75" customHeight="1"/>
-    <row r="467" ht="12.75" customHeight="1"/>
-    <row r="468" ht="12.75" customHeight="1"/>
-    <row r="469" ht="12.75" customHeight="1"/>
-    <row r="470" ht="12.75" customHeight="1"/>
-    <row r="471" ht="12.75" customHeight="1"/>
-    <row r="472" ht="12.75" customHeight="1"/>
-    <row r="473" ht="12.75" customHeight="1"/>
-    <row r="474" ht="12.75" customHeight="1"/>
-    <row r="475" ht="12.75" customHeight="1"/>
-    <row r="476" ht="12.75" customHeight="1"/>
-    <row r="477" ht="12.75" customHeight="1"/>
-    <row r="478" ht="12.75" customHeight="1"/>
-    <row r="479" ht="12.75" customHeight="1"/>
-    <row r="480" ht="12.75" customHeight="1"/>
-    <row r="481" ht="12.75" customHeight="1"/>
-    <row r="482" ht="12.75" customHeight="1"/>
-    <row r="483" ht="12.75" customHeight="1"/>
-    <row r="484" ht="12.75" customHeight="1"/>
-    <row r="485" ht="12.75" customHeight="1"/>
-    <row r="486" ht="12.75" customHeight="1"/>
-    <row r="487" ht="12.75" customHeight="1"/>
-    <row r="488" ht="12.75" customHeight="1"/>
-    <row r="489" ht="12.75" customHeight="1"/>
-    <row r="490" ht="12.75" customHeight="1"/>
-    <row r="491" ht="12.75" customHeight="1"/>
-    <row r="492" ht="12.75" customHeight="1"/>
-    <row r="493" ht="12.75" customHeight="1"/>
-    <row r="494" ht="12.75" customHeight="1"/>
-    <row r="495" ht="12.75" customHeight="1"/>
-    <row r="496" ht="12.75" customHeight="1"/>
-    <row r="497" ht="12.75" customHeight="1"/>
-    <row r="498" ht="12.75" customHeight="1"/>
-    <row r="499" ht="12.75" customHeight="1"/>
-    <row r="500" ht="12.75" customHeight="1"/>
-    <row r="501" ht="12.75" customHeight="1"/>
-    <row r="502" ht="12.75" customHeight="1"/>
-    <row r="503" ht="12.75" customHeight="1"/>
-    <row r="504" ht="12.75" customHeight="1"/>
-    <row r="505" ht="12.75" customHeight="1"/>
-    <row r="506" ht="12.75" customHeight="1"/>
-    <row r="507" ht="12.75" customHeight="1"/>
-    <row r="508" ht="12.75" customHeight="1"/>
-    <row r="509" ht="12.75" customHeight="1"/>
-    <row r="510" ht="12.75" customHeight="1"/>
-    <row r="511" ht="12.75" customHeight="1"/>
-    <row r="512" ht="12.75" customHeight="1"/>
-    <row r="513" ht="12.75" customHeight="1"/>
-    <row r="514" ht="12.75" customHeight="1"/>
-    <row r="515" ht="12.75" customHeight="1"/>
-    <row r="516" ht="12.75" customHeight="1"/>
-    <row r="517" ht="12.75" customHeight="1"/>
-    <row r="518" ht="12.75" customHeight="1"/>
-    <row r="519" ht="12.75" customHeight="1"/>
-    <row r="520" ht="12.75" customHeight="1"/>
-    <row r="521" ht="12.75" customHeight="1"/>
-    <row r="522" ht="12.75" customHeight="1"/>
-    <row r="523" ht="12.75" customHeight="1"/>
-    <row r="524" ht="12.75" customHeight="1"/>
-    <row r="525" ht="12.75" customHeight="1"/>
-    <row r="526" ht="12.75" customHeight="1"/>
-    <row r="527" ht="12.75" customHeight="1"/>
-    <row r="528" ht="12.75" customHeight="1"/>
-    <row r="529" ht="12.75" customHeight="1"/>
-    <row r="530" ht="12.75" customHeight="1"/>
-    <row r="531" ht="12.75" customHeight="1"/>
-    <row r="532" ht="12.75" customHeight="1"/>
-    <row r="533" ht="12.75" customHeight="1"/>
-    <row r="534" ht="12.75" customHeight="1"/>
-    <row r="535" ht="12.75" customHeight="1"/>
-    <row r="536" ht="12.75" customHeight="1"/>
-    <row r="537" ht="12.75" customHeight="1"/>
-    <row r="538" ht="12.75" customHeight="1"/>
-    <row r="539" ht="12.75" customHeight="1"/>
-    <row r="540" ht="12.75" customHeight="1"/>
-    <row r="541" ht="12.75" customHeight="1"/>
-    <row r="542" ht="12.75" customHeight="1"/>
-    <row r="543" ht="12.75" customHeight="1"/>
-    <row r="544" ht="12.75" customHeight="1"/>
-    <row r="545" ht="12.75" customHeight="1"/>
-    <row r="546" ht="12.75" customHeight="1"/>
-    <row r="547" ht="12.75" customHeight="1"/>
-    <row r="548" ht="12.75" customHeight="1"/>
-    <row r="549" ht="12.75" customHeight="1"/>
-    <row r="550" ht="12.75" customHeight="1"/>
-    <row r="551" ht="12.75" customHeight="1"/>
-    <row r="552" ht="12.75" customHeight="1"/>
-    <row r="553" ht="12.75" customHeight="1"/>
-    <row r="554" ht="12.75" customHeight="1"/>
-    <row r="555" ht="12.75" customHeight="1"/>
-    <row r="556" ht="12.75" customHeight="1"/>
-    <row r="557" ht="12.75" customHeight="1"/>
-    <row r="558" ht="12.75" customHeight="1"/>
-    <row r="559" ht="12.75" customHeight="1"/>
-    <row r="560" ht="12.75" customHeight="1"/>
-    <row r="561" ht="12.75" customHeight="1"/>
-    <row r="562" ht="12.75" customHeight="1"/>
-    <row r="563" ht="12.75" customHeight="1"/>
-    <row r="564" ht="12.75" customHeight="1"/>
-    <row r="565" ht="12.75" customHeight="1"/>
-    <row r="566" ht="12.75" customHeight="1"/>
-    <row r="567" ht="12.75" customHeight="1"/>
-    <row r="568" ht="12.75" customHeight="1"/>
-    <row r="569" ht="12.75" customHeight="1"/>
-    <row r="570" ht="12.75" customHeight="1"/>
-    <row r="571" ht="12.75" customHeight="1"/>
-    <row r="572" ht="12.75" customHeight="1"/>
-    <row r="573" ht="12.75" customHeight="1"/>
-    <row r="574" ht="12.75" customHeight="1"/>
-    <row r="575" ht="12.75" customHeight="1"/>
-    <row r="576" ht="12.75" customHeight="1"/>
-    <row r="577" ht="12.75" customHeight="1"/>
-    <row r="578" ht="12.75" customHeight="1"/>
-    <row r="579" ht="12.75" customHeight="1"/>
-    <row r="580" ht="12.75" customHeight="1"/>
-    <row r="581" ht="12.75" customHeight="1"/>
-    <row r="582" ht="12.75" customHeight="1"/>
-    <row r="583" ht="12.75" customHeight="1"/>
-    <row r="584" ht="12.75" customHeight="1"/>
-    <row r="585" ht="12.75" customHeight="1"/>
-    <row r="586" ht="12.75" customHeight="1"/>
-    <row r="587" ht="12.75" customHeight="1"/>
-    <row r="588" ht="12.75" customHeight="1"/>
-    <row r="589" ht="12.75" customHeight="1"/>
-    <row r="590" ht="12.75" customHeight="1"/>
-    <row r="591" ht="12.75" customHeight="1"/>
-    <row r="592" ht="12.75" customHeight="1"/>
-    <row r="593" ht="12.75" customHeight="1"/>
-    <row r="594" ht="12.75" customHeight="1"/>
-    <row r="595" ht="12.75" customHeight="1"/>
-    <row r="596" ht="12.75" customHeight="1"/>
-    <row r="597" ht="12.75" customHeight="1"/>
-    <row r="598" ht="12.75" customHeight="1"/>
-    <row r="599" ht="12.75" customHeight="1"/>
-    <row r="600" ht="12.75" customHeight="1"/>
-    <row r="601" ht="12.75" customHeight="1"/>
-    <row r="602" ht="12.75" customHeight="1"/>
-    <row r="603" ht="12.75" customHeight="1"/>
-    <row r="604" ht="12.75" customHeight="1"/>
-    <row r="605" ht="12.75" customHeight="1"/>
-    <row r="606" ht="12.75" customHeight="1"/>
-    <row r="607" ht="12.75" customHeight="1"/>
-    <row r="608" ht="12.75" customHeight="1"/>
-    <row r="609" ht="12.75" customHeight="1"/>
-    <row r="610" ht="12.75" customHeight="1"/>
-    <row r="611" ht="12.75" customHeight="1"/>
-    <row r="612" ht="12.75" customHeight="1"/>
-    <row r="613" ht="12.75" customHeight="1"/>
-    <row r="614" ht="12.75" customHeight="1"/>
-    <row r="615" ht="12.75" customHeight="1"/>
-    <row r="616" ht="12.75" customHeight="1"/>
-    <row r="617" ht="12.75" customHeight="1"/>
-    <row r="618" ht="12.75" customHeight="1"/>
-    <row r="619" ht="12.75" customHeight="1"/>
-    <row r="620" ht="12.75" customHeight="1"/>
-    <row r="621" ht="12.75" customHeight="1"/>
-    <row r="622" ht="12.75" customHeight="1"/>
-    <row r="623" ht="12.75" customHeight="1"/>
-    <row r="624" ht="12.75" customHeight="1"/>
-    <row r="625" ht="12.75" customHeight="1"/>
-    <row r="626" ht="12.75" customHeight="1"/>
-    <row r="627" ht="12.75" customHeight="1"/>
-    <row r="628" ht="12.75" customHeight="1"/>
-    <row r="629" ht="12.75" customHeight="1"/>
-    <row r="630" ht="12.75" customHeight="1"/>
-    <row r="631" ht="12.75" customHeight="1"/>
-    <row r="632" ht="12.75" customHeight="1"/>
-    <row r="633" ht="12.75" customHeight="1"/>
-    <row r="634" ht="12.75" customHeight="1"/>
-    <row r="635" ht="12.75" customHeight="1"/>
-    <row r="636" ht="12.75" customHeight="1"/>
-    <row r="637" ht="12.75" customHeight="1"/>
-    <row r="638" ht="12.75" customHeight="1"/>
-    <row r="639" ht="12.75" customHeight="1"/>
-    <row r="640" ht="12.75" customHeight="1"/>
-    <row r="641" ht="12.75" customHeight="1"/>
-    <row r="642" ht="12.75" customHeight="1"/>
-    <row r="643" ht="12.75" customHeight="1"/>
-    <row r="644" ht="12.75" customHeight="1"/>
-    <row r="645" ht="12.75" customHeight="1"/>
-    <row r="646" ht="12.75" customHeight="1"/>
-    <row r="647" ht="12.75" customHeight="1"/>
-    <row r="648" ht="12.75" customHeight="1"/>
-    <row r="649" ht="12.75" customHeight="1"/>
-    <row r="650" ht="12.75" customHeight="1"/>
-    <row r="651" ht="12.75" customHeight="1"/>
-    <row r="652" ht="12.75" customHeight="1"/>
-    <row r="653" ht="12.75" customHeight="1"/>
-    <row r="654" ht="12.75" customHeight="1"/>
-    <row r="655" ht="12.75" customHeight="1"/>
-    <row r="656" ht="12.75" customHeight="1"/>
-    <row r="657" ht="12.75" customHeight="1"/>
-    <row r="658" ht="12.75" customHeight="1"/>
-    <row r="659" ht="12.75" customHeight="1"/>
-    <row r="660" ht="12.75" customHeight="1"/>
-    <row r="661" ht="12.75" customHeight="1"/>
-    <row r="662" ht="12.75" customHeight="1"/>
-    <row r="663" ht="12.75" customHeight="1"/>
-    <row r="664" ht="12.75" customHeight="1"/>
-    <row r="665" ht="12.75" customHeight="1"/>
-    <row r="666" ht="12.75" customHeight="1"/>
-    <row r="667" ht="12.75" customHeight="1"/>
-    <row r="668" ht="12.75" customHeight="1"/>
-    <row r="669" ht="12.75" customHeight="1"/>
-    <row r="670" ht="12.75" customHeight="1"/>
-    <row r="671" ht="12.75" customHeight="1"/>
-    <row r="672" ht="12.75" customHeight="1"/>
-    <row r="673" ht="12.75" customHeight="1"/>
-    <row r="674" ht="12.75" customHeight="1"/>
-    <row r="675" ht="12.75" customHeight="1"/>
-    <row r="676" ht="12.75" customHeight="1"/>
-    <row r="677" ht="12.75" customHeight="1"/>
-    <row r="678" ht="12.75" customHeight="1"/>
-    <row r="679" ht="12.75" customHeight="1"/>
-    <row r="680" ht="12.75" customHeight="1"/>
-    <row r="681" ht="12.75" customHeight="1"/>
-    <row r="682" ht="12.75" customHeight="1"/>
-    <row r="683" ht="12.75" customHeight="1"/>
-    <row r="684" ht="12.75" customHeight="1"/>
-    <row r="685" ht="12.75" customHeight="1"/>
-    <row r="686" ht="12.75" customHeight="1"/>
-    <row r="687" ht="12.75" customHeight="1"/>
-    <row r="688" ht="12.75" customHeight="1"/>
-    <row r="689" ht="12.75" customHeight="1"/>
-    <row r="690" ht="12.75" customHeight="1"/>
-    <row r="691" ht="12.75" customHeight="1"/>
-    <row r="692" ht="12.75" customHeight="1"/>
-    <row r="693" ht="12.75" customHeight="1"/>
-    <row r="694" ht="12.75" customHeight="1"/>
-    <row r="695" ht="12.75" customHeight="1"/>
-    <row r="696" ht="12.75" customHeight="1"/>
-    <row r="697" ht="12.75" customHeight="1"/>
-    <row r="698" ht="12.75" customHeight="1"/>
-    <row r="699" ht="12.75" customHeight="1"/>
-    <row r="700" ht="12.75" customHeight="1"/>
-    <row r="701" ht="12.75" customHeight="1"/>
-    <row r="702" ht="12.75" customHeight="1"/>
-    <row r="703" ht="12.75" customHeight="1"/>
-    <row r="704" ht="12.75" customHeight="1"/>
-    <row r="705" ht="12.75" customHeight="1"/>
-    <row r="706" ht="12.75" customHeight="1"/>
-    <row r="707" ht="12.75" customHeight="1"/>
-    <row r="708" ht="12.75" customHeight="1"/>
-    <row r="709" ht="12.75" customHeight="1"/>
-    <row r="710" ht="12.75" customHeight="1"/>
-    <row r="711" ht="12.75" customHeight="1"/>
-    <row r="712" ht="12.75" customHeight="1"/>
-    <row r="713" ht="12.75" customHeight="1"/>
-    <row r="714" ht="12.75" customHeight="1"/>
-    <row r="715" ht="12.75" customHeight="1"/>
-    <row r="716" ht="12.75" customHeight="1"/>
-    <row r="717" ht="12.75" customHeight="1"/>
-    <row r="718" ht="12.75" customHeight="1"/>
-    <row r="719" ht="12.75" customHeight="1"/>
-    <row r="720" ht="12.75" customHeight="1"/>
-    <row r="721" ht="12.75" customHeight="1"/>
-    <row r="722" ht="12.75" customHeight="1"/>
-    <row r="723" ht="12.75" customHeight="1"/>
-    <row r="724" ht="12.75" customHeight="1"/>
-    <row r="725" ht="12.75" customHeight="1"/>
-    <row r="726" ht="12.75" customHeight="1"/>
-    <row r="727" ht="12.75" customHeight="1"/>
-    <row r="728" ht="12.75" customHeight="1"/>
-    <row r="729" ht="12.75" customHeight="1"/>
-    <row r="730" ht="12.75" customHeight="1"/>
-    <row r="731" ht="12.75" customHeight="1"/>
-    <row r="732" ht="12.75" customHeight="1"/>
-    <row r="733" ht="12.75" customHeight="1"/>
-    <row r="734" ht="12.75" customHeight="1"/>
-    <row r="735" ht="12.75" customHeight="1"/>
-    <row r="736" ht="12.75" customHeight="1"/>
-    <row r="737" ht="12.75" customHeight="1"/>
-    <row r="738" ht="12.75" customHeight="1"/>
-    <row r="739" ht="12.75" customHeight="1"/>
-    <row r="740" ht="12.75" customHeight="1"/>
-    <row r="741" ht="12.75" customHeight="1"/>
-    <row r="742" ht="12.75" customHeight="1"/>
-    <row r="743" ht="12.75" customHeight="1"/>
-    <row r="744" ht="12.75" customHeight="1"/>
-    <row r="745" ht="12.75" customHeight="1"/>
-    <row r="746" ht="12.75" customHeight="1"/>
-    <row r="747" ht="12.75" customHeight="1"/>
-    <row r="748" ht="12.75" customHeight="1"/>
-    <row r="749" ht="12.75" customHeight="1"/>
-    <row r="750" ht="12.75" customHeight="1"/>
-    <row r="751" ht="12.75" customHeight="1"/>
-    <row r="752" ht="12.75" customHeight="1"/>
-    <row r="753" ht="12.75" customHeight="1"/>
-    <row r="754" ht="12.75" customHeight="1"/>
-    <row r="755" ht="12.75" customHeight="1"/>
-    <row r="756" ht="12.75" customHeight="1"/>
-    <row r="757" ht="12.75" customHeight="1"/>
-    <row r="758" ht="12.75" customHeight="1"/>
-    <row r="759" ht="12.75" customHeight="1"/>
-    <row r="760" ht="12.75" customHeight="1"/>
-    <row r="761" ht="12.75" customHeight="1"/>
-    <row r="762" ht="12.75" customHeight="1"/>
-    <row r="763" ht="12.75" customHeight="1"/>
-    <row r="764" ht="12.75" customHeight="1"/>
-    <row r="765" ht="12.75" customHeight="1"/>
-    <row r="766" ht="12.75" customHeight="1"/>
-    <row r="767" ht="12.75" customHeight="1"/>
-    <row r="768" ht="12.75" customHeight="1"/>
-    <row r="769" ht="12.75" customHeight="1"/>
-    <row r="770" ht="12.75" customHeight="1"/>
-    <row r="771" ht="12.75" customHeight="1"/>
-    <row r="772" ht="12.75" customHeight="1"/>
-    <row r="773" ht="12.75" customHeight="1"/>
-    <row r="774" ht="12.75" customHeight="1"/>
-    <row r="775" ht="12.75" customHeight="1"/>
-    <row r="776" ht="12.75" customHeight="1"/>
-    <row r="777" ht="12.75" customHeight="1"/>
-    <row r="778" ht="12.75" customHeight="1"/>
-    <row r="779" ht="12.75" customHeight="1"/>
-    <row r="780" ht="12.75" customHeight="1"/>
-    <row r="781" ht="12.75" customHeight="1"/>
-    <row r="782" ht="12.75" customHeight="1"/>
-    <row r="783" ht="12.75" customHeight="1"/>
-    <row r="784" ht="12.75" customHeight="1"/>
-    <row r="785" ht="12.75" customHeight="1"/>
-    <row r="786" ht="12.75" customHeight="1"/>
-    <row r="787" ht="12.75" customHeight="1"/>
-    <row r="788" ht="12.75" customHeight="1"/>
-    <row r="789" ht="12.75" customHeight="1"/>
-    <row r="790" ht="12.75" customHeight="1"/>
-    <row r="791" ht="12.75" customHeight="1"/>
-    <row r="792" ht="12.75" customHeight="1"/>
-    <row r="793" ht="12.75" customHeight="1"/>
-    <row r="794" ht="12.75" customHeight="1"/>
-    <row r="795" ht="12.75" customHeight="1"/>
-    <row r="796" ht="12.75" customHeight="1"/>
-    <row r="797" ht="12.75" customHeight="1"/>
-    <row r="798" ht="12.75" customHeight="1"/>
-    <row r="799" ht="12.75" customHeight="1"/>
-    <row r="800" ht="12.75" customHeight="1"/>
-    <row r="801" ht="12.75" customHeight="1"/>
-    <row r="802" ht="12.75" customHeight="1"/>
-    <row r="803" ht="12.75" customHeight="1"/>
-    <row r="804" ht="12.75" customHeight="1"/>
-    <row r="805" ht="12.75" customHeight="1"/>
-    <row r="806" ht="12.75" customHeight="1"/>
-    <row r="807" ht="12.75" customHeight="1"/>
-    <row r="808" ht="12.75" customHeight="1"/>
-    <row r="809" ht="12.75" customHeight="1"/>
-    <row r="810" ht="12.75" customHeight="1"/>
-    <row r="811" ht="12.75" customHeight="1"/>
-    <row r="812" ht="12.75" customHeight="1"/>
-    <row r="813" ht="12.75" customHeight="1"/>
-    <row r="814" ht="12.75" customHeight="1"/>
-    <row r="815" ht="12.75" customHeight="1"/>
-    <row r="816" ht="12.75" customHeight="1"/>
-    <row r="817" ht="12.75" customHeight="1"/>
-    <row r="818" ht="12.75" customHeight="1"/>
-    <row r="819" ht="12.75" customHeight="1"/>
-    <row r="820" ht="12.75" customHeight="1"/>
-    <row r="821" ht="12.75" customHeight="1"/>
-    <row r="822" ht="12.75" customHeight="1"/>
-    <row r="823" ht="12.75" customHeight="1"/>
-    <row r="824" ht="12.75" customHeight="1"/>
-    <row r="825" ht="12.75" customHeight="1"/>
-    <row r="826" ht="12.75" customHeight="1"/>
-    <row r="827" ht="12.75" customHeight="1"/>
-    <row r="828" ht="12.75" customHeight="1"/>
-    <row r="829" ht="12.75" customHeight="1"/>
-    <row r="830" ht="12.75" customHeight="1"/>
-    <row r="831" ht="12.75" customHeight="1"/>
-    <row r="832" ht="12.75" customHeight="1"/>
-    <row r="833" ht="12.75" customHeight="1"/>
-    <row r="834" ht="12.75" customHeight="1"/>
-    <row r="835" ht="12.75" customHeight="1"/>
-    <row r="836" ht="12.75" customHeight="1"/>
-    <row r="837" ht="12.75" customHeight="1"/>
-    <row r="838" ht="12.75" customHeight="1"/>
-    <row r="839" ht="12.75" customHeight="1"/>
-    <row r="840" ht="12.75" customHeight="1"/>
-    <row r="841" ht="12.75" customHeight="1"/>
-    <row r="842" ht="12.75" customHeight="1"/>
-    <row r="843" ht="12.75" customHeight="1"/>
-    <row r="844" ht="12.75" customHeight="1"/>
-    <row r="845" ht="12.75" customHeight="1"/>
-    <row r="846" ht="12.75" customHeight="1"/>
-    <row r="847" ht="12.75" customHeight="1"/>
-    <row r="848" ht="12.75" customHeight="1"/>
-    <row r="849" ht="12.75" customHeight="1"/>
-    <row r="850" ht="12.75" customHeight="1"/>
-    <row r="851" ht="12.75" customHeight="1"/>
-    <row r="852" ht="12.75" customHeight="1"/>
-    <row r="853" ht="12.75" customHeight="1"/>
-    <row r="854" ht="12.75" customHeight="1"/>
-    <row r="855" ht="12.75" customHeight="1"/>
-    <row r="856" ht="12.75" customHeight="1"/>
-    <row r="857" ht="12.75" customHeight="1"/>
-    <row r="858" ht="12.75" customHeight="1"/>
-    <row r="859" ht="12.75" customHeight="1"/>
-    <row r="860" ht="12.75" customHeight="1"/>
-    <row r="861" ht="12.75" customHeight="1"/>
-    <row r="862" ht="12.75" customHeight="1"/>
-    <row r="863" ht="12.75" customHeight="1"/>
-    <row r="864" ht="12.75" customHeight="1"/>
-    <row r="865" ht="12.75" customHeight="1"/>
-    <row r="866" ht="12.75" customHeight="1"/>
-    <row r="867" ht="12.75" customHeight="1"/>
-    <row r="868" ht="12.75" customHeight="1"/>
-    <row r="869" ht="12.75" customHeight="1"/>
-    <row r="870" ht="12.75" customHeight="1"/>
-    <row r="871" ht="12.75" customHeight="1"/>
-    <row r="872" ht="12.75" customHeight="1"/>
-    <row r="873" ht="12.75" customHeight="1"/>
-    <row r="874" ht="12.75" customHeight="1"/>
-    <row r="875" ht="12.75" customHeight="1"/>
-    <row r="876" ht="12.75" customHeight="1"/>
-    <row r="877" ht="12.75" customHeight="1"/>
-    <row r="878" ht="12.75" customHeight="1"/>
-    <row r="879" ht="12.75" customHeight="1"/>
-    <row r="880" ht="12.75" customHeight="1"/>
-    <row r="881" ht="12.75" customHeight="1"/>
-    <row r="882" ht="12.75" customHeight="1"/>
-    <row r="883" ht="12.75" customHeight="1"/>
-    <row r="884" ht="12.75" customHeight="1"/>
-    <row r="885" ht="12.75" customHeight="1"/>
-    <row r="886" ht="12.75" customHeight="1"/>
-    <row r="887" ht="12.75" customHeight="1"/>
-    <row r="888" ht="12.75" customHeight="1"/>
-    <row r="889" ht="12.75" customHeight="1"/>
-    <row r="890" ht="12.75" customHeight="1"/>
-    <row r="891" ht="12.75" customHeight="1"/>
-    <row r="892" ht="12.75" customHeight="1"/>
-    <row r="893" ht="12.75" customHeight="1"/>
-    <row r="894" ht="12.75" customHeight="1"/>
-    <row r="895" ht="12.75" customHeight="1"/>
-    <row r="896" ht="12.75" customHeight="1"/>
-    <row r="897" ht="12.75" customHeight="1"/>
-    <row r="898" ht="12.75" customHeight="1"/>
-    <row r="899" ht="12.75" customHeight="1"/>
-    <row r="900" ht="12.75" customHeight="1"/>
-    <row r="901" ht="12.75" customHeight="1"/>
-    <row r="902" ht="12.75" customHeight="1"/>
-    <row r="903" ht="12.75" customHeight="1"/>
-    <row r="904" ht="12.75" customHeight="1"/>
-    <row r="905" ht="12.75" customHeight="1"/>
-    <row r="906" ht="12.75" customHeight="1"/>
-    <row r="907" ht="12.75" customHeight="1"/>
-    <row r="908" ht="12.75" customHeight="1"/>
-    <row r="909" ht="12.75" customHeight="1"/>
-    <row r="910" ht="12.75" customHeight="1"/>
-    <row r="911" ht="12.75" customHeight="1"/>
-    <row r="912" ht="12.75" customHeight="1"/>
-    <row r="913" ht="12.75" customHeight="1"/>
-    <row r="914" ht="12.75" customHeight="1"/>
-    <row r="915" ht="12.75" customHeight="1"/>
-    <row r="916" ht="12.75" customHeight="1"/>
-    <row r="917" ht="12.75" customHeight="1"/>
-    <row r="918" ht="12.75" customHeight="1"/>
-    <row r="919" ht="12.75" customHeight="1"/>
-    <row r="920" ht="12.75" customHeight="1"/>
-    <row r="921" ht="12.75" customHeight="1"/>
-    <row r="922" ht="12.75" customHeight="1"/>
-    <row r="923" ht="12.75" customHeight="1"/>
-    <row r="924" ht="12.75" customHeight="1"/>
-    <row r="925" ht="12.75" customHeight="1"/>
-    <row r="926" ht="12.75" customHeight="1"/>
-    <row r="927" ht="12.75" customHeight="1"/>
-    <row r="928" ht="12.75" customHeight="1"/>
-    <row r="929" ht="12.75" customHeight="1"/>
-    <row r="930" ht="12.75" customHeight="1"/>
-    <row r="931" ht="12.75" customHeight="1"/>
-    <row r="932" ht="12.75" customHeight="1"/>
-    <row r="933" ht="12.75" customHeight="1"/>
-    <row r="934" ht="12.75" customHeight="1"/>
-    <row r="935" ht="12.75" customHeight="1"/>
-    <row r="936" ht="12.75" customHeight="1"/>
-    <row r="937" ht="12.75" customHeight="1"/>
-    <row r="938" ht="12.75" customHeight="1"/>
-    <row r="939" ht="12.75" customHeight="1"/>
-    <row r="940" ht="12.75" customHeight="1"/>
-    <row r="941" ht="12.75" customHeight="1"/>
-    <row r="942" ht="12.75" customHeight="1"/>
-    <row r="943" ht="12.75" customHeight="1"/>
-    <row r="944" ht="12.75" customHeight="1"/>
-    <row r="945" ht="12.75" customHeight="1"/>
-    <row r="946" ht="12.75" customHeight="1"/>
-    <row r="947" ht="12.75" customHeight="1"/>
-    <row r="948" ht="12.75" customHeight="1"/>
-    <row r="949" ht="12.75" customHeight="1"/>
-    <row r="950" ht="12.75" customHeight="1"/>
-    <row r="951" ht="12.75" customHeight="1"/>
-    <row r="952" ht="12.75" customHeight="1"/>
-    <row r="953" ht="12.75" customHeight="1"/>
-    <row r="954" ht="12.75" customHeight="1"/>
-    <row r="955" ht="12.75" customHeight="1"/>
-    <row r="956" ht="12.75" customHeight="1"/>
-    <row r="957" ht="12.75" customHeight="1"/>
-    <row r="958" ht="12.75" customHeight="1"/>
-    <row r="959" ht="12.75" customHeight="1"/>
-    <row r="960" ht="12.75" customHeight="1"/>
-    <row r="961" ht="12.75" customHeight="1"/>
-    <row r="962" ht="12.75" customHeight="1"/>
-    <row r="963" ht="12.75" customHeight="1"/>
-    <row r="964" ht="12.75" customHeight="1"/>
-    <row r="965" ht="12.75" customHeight="1"/>
-    <row r="966" ht="12.75" customHeight="1"/>
-    <row r="967" ht="12.75" customHeight="1"/>
-    <row r="968" ht="12.75" customHeight="1"/>
-    <row r="969" ht="12.75" customHeight="1"/>
-    <row r="970" ht="12.75" customHeight="1"/>
-    <row r="971" ht="12.75" customHeight="1"/>
-    <row r="972" ht="12.75" customHeight="1"/>
-    <row r="973" ht="12.75" customHeight="1"/>
-    <row r="974" ht="12.75" customHeight="1"/>
-    <row r="975" ht="12.75" customHeight="1"/>
-    <row r="976" ht="12.75" customHeight="1"/>
-    <row r="977" ht="12.75" customHeight="1"/>
-    <row r="978" ht="12.75" customHeight="1"/>
-    <row r="979" ht="12.75" customHeight="1"/>
-    <row r="980" ht="12.75" customHeight="1"/>
-    <row r="981" ht="12.75" customHeight="1"/>
-    <row r="982" ht="12.75" customHeight="1"/>
-    <row r="983" ht="12.75" customHeight="1"/>
-    <row r="984" ht="12.75" customHeight="1"/>
-    <row r="985" ht="12.75" customHeight="1"/>
-    <row r="986" ht="12.75" customHeight="1"/>
-    <row r="987" ht="12.75" customHeight="1"/>
-    <row r="988" ht="12.75" customHeight="1"/>
-    <row r="989" ht="12.75" customHeight="1"/>
-    <row r="990" ht="12.75" customHeight="1"/>
-    <row r="991" ht="12.75" customHeight="1"/>
-    <row r="992" ht="12.75" customHeight="1"/>
-    <row r="993" ht="12.75" customHeight="1"/>
-    <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -11649,6 +11545,11 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11668,186 +11569,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="73" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="60"/>
+      <c r="S1" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="62"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="65"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="68"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="114"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="80" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="80" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="67"/>
-      <c r="S1" s="80" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="47"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="82"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="104"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="105"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="84"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="84"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="84"/>
-      <c r="T4" s="119"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="62"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="45" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="44"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="47"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="100" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="52"/>
-      <c r="S6" s="52"/>
-      <c r="T6" s="53"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="100" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="53"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="44"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11875,11 +11776,11 @@
       <c r="A9" s="21"/>
       <c r="B9" s="22"/>
       <c r="C9" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
@@ -11909,7 +11810,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="28"/>
@@ -11939,7 +11840,7 @@
       <c r="C11" s="27"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="28"/>
@@ -11969,7 +11870,7 @@
       <c r="C12" s="27"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="28"/>
@@ -11999,7 +11900,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="31"/>
@@ -12046,79 +11947,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="117" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="45"/>
+      <c r="E15" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="45"/>
+      <c r="G15" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="69"/>
-      <c r="C15" s="118" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="106" t="s">
+      <c r="H15" s="43"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="69"/>
-      <c r="G15" s="106" t="s">
+      <c r="K15" s="45"/>
+      <c r="L15" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="52"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="106" t="s">
+      <c r="M15" s="43"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="69"/>
-      <c r="L15" s="106" t="s">
+      <c r="P15" s="43"/>
+      <c r="Q15" s="45"/>
+      <c r="R15" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="52"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="106" t="s">
+      <c r="S15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="69"/>
-      <c r="R15" s="15" t="s">
+      <c r="T15" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="15" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="115">
+        <v>1</v>
+      </c>
+      <c r="B16" s="45"/>
+      <c r="C16" s="116" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="32" t="s">
+      <c r="D16" s="45"/>
+      <c r="E16" s="116" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="111">
-        <v>1</v>
-      </c>
-      <c r="B16" s="69"/>
-      <c r="C16" s="112" t="s">
+      <c r="F16" s="45"/>
+      <c r="G16" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="112" t="s">
+      <c r="H16" s="43"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="69"/>
-      <c r="G16" s="117" t="s">
+      <c r="K16" s="45"/>
+      <c r="L16" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="52"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="117" t="s">
+      <c r="M16" s="43"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="69"/>
-      <c r="L16" s="115" t="s">
-        <v>57</v>
-      </c>
-      <c r="M16" s="52"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="115" t="s">
-        <v>58</v>
-      </c>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="69"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="45"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12130,37 +12031,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="111">
+      <c r="A17" s="115">
         <v>2</v>
       </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="112" t="s">
+      <c r="B17" s="45"/>
+      <c r="C17" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="45"/>
+      <c r="E17" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="45"/>
+      <c r="G17" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="112" t="s">
+      <c r="H17" s="43"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="69"/>
-      <c r="G17" s="117" t="s">
+      <c r="K17" s="45"/>
+      <c r="L17" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="117" t="s">
+      <c r="M17" s="43"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="112" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="69"/>
-      <c r="L17" s="115" t="s">
-        <v>63</v>
-      </c>
-      <c r="M17" s="52"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="115" t="s">
-        <v>64</v>
-      </c>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="69"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="45"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12172,23 +12073,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="111"/>
-      <c r="B18" s="69"/>
-      <c r="C18" s="112"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="115"/>
-      <c r="P18" s="52"/>
-      <c r="Q18" s="69"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="45"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -12200,23 +12101,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="111"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="115"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="115"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="69"/>
+      <c r="A19" s="115"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="45"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -12228,23 +12129,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="111"/>
-      <c r="B20" s="69"/>
-      <c r="C20" s="112"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="115"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="69"/>
+      <c r="A20" s="115"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="45"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -12256,23 +12157,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="111"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="112"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="112"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="117"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="115"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="115"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="69"/>
+      <c r="A21" s="115"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="45"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -12284,23 +12185,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="111"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="112"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="112"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="117"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="115"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="69"/>
+      <c r="A22" s="115"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="45"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -12312,23 +12213,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="111"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="112"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="112"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="117"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="115"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="115"/>
-      <c r="P23" s="52"/>
-      <c r="Q23" s="69"/>
+      <c r="A23" s="115"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="45"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -12340,23 +12241,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="111"/>
-      <c r="B24" s="69"/>
-      <c r="C24" s="112"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="117"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="115"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="115"/>
-      <c r="P24" s="52"/>
-      <c r="Q24" s="69"/>
+      <c r="A24" s="115"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="45"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -12368,23 +12269,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="111"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="112"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="117"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="115"/>
-      <c r="M25" s="52"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="115"/>
-      <c r="P25" s="52"/>
-      <c r="Q25" s="69"/>
+      <c r="A25" s="115"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="45"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -12396,23 +12297,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="111"/>
-      <c r="B26" s="69"/>
-      <c r="C26" s="112"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="112"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="117"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="115"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="69"/>
-      <c r="O26" s="115"/>
-      <c r="P26" s="52"/>
-      <c r="Q26" s="69"/>
+      <c r="A26" s="115"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="116"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="45"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -12424,23 +12325,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="111"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="112"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="117"/>
-      <c r="K27" s="69"/>
-      <c r="L27" s="115"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="69"/>
-      <c r="O27" s="115"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="69"/>
+      <c r="A27" s="115"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="45"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -12452,23 +12353,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="111"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="117"/>
-      <c r="K28" s="69"/>
-      <c r="L28" s="115"/>
-      <c r="M28" s="52"/>
-      <c r="N28" s="69"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="52"/>
-      <c r="Q28" s="69"/>
+      <c r="A28" s="115"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="45"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -12480,23 +12381,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="111"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="112"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="112"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="117"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="117"/>
-      <c r="K29" s="69"/>
-      <c r="L29" s="115"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="69"/>
-      <c r="O29" s="115"/>
-      <c r="P29" s="52"/>
-      <c r="Q29" s="69"/>
+      <c r="A29" s="115"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="45"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -12508,23 +12409,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="111"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="112"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="112"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="117"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="69"/>
-      <c r="J30" s="117"/>
-      <c r="K30" s="69"/>
-      <c r="L30" s="115"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="69"/>
-      <c r="O30" s="115"/>
-      <c r="P30" s="52"/>
-      <c r="Q30" s="69"/>
+      <c r="A30" s="115"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="45"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -12536,23 +12437,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="113"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="114"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="120"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="120"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="116"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="116"/>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="56"/>
+      <c r="A31" s="118"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="119"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="119"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="96"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="96"/>
+      <c r="O31" s="113"/>
+      <c r="P31" s="95"/>
+      <c r="Q31" s="96"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -13550,62 +13451,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -13630,62 +13531,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク登録機能.xlsx
+++ b/document/成果物ドキュメント_タスク登録機能.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER123\Desktop\設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28888A23-D171-4C1B-B7A5-EEE6CFAEBEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0D3F6E-32C0-43A5-9924-75D883756CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="117">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -349,10 +349,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>メニュー</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>submit</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -616,6 +612,33 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>GET</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入力必須、最大50文字</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクヒッス</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>最大100文字</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>モジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1375,7 +1398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1490,15 +1513,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1592,32 +1606,20 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1625,11 +1627,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1640,8 +1642,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1652,32 +1654,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1686,6 +1682,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1706,6 +1705,18 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1718,17 +1729,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1736,17 +1741,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1836,22 +1847,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>27214</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>18143</xdr:rowOff>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>57742</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>160111</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>583312</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{553DEC02-B58A-2CAF-86B8-0423F8430F19}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{283B040E-0DF9-804D-1687-356CC3F5FB10}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1874,8 +1885,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="371928" y="1415143"/>
-          <a:ext cx="8530457" cy="4060825"/>
+          <a:off x="523876" y="1285876"/>
+          <a:ext cx="7774686" cy="3786187"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1902,22 +1913,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>896327</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>259815</xdr:rowOff>
+      <xdr:colOff>994832</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>105833</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>358320</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>1903</xdr:rowOff>
+      <xdr:colOff>105833</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>146566</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BC80C4C-5253-7E96-406F-A4C25B67D69D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F1BF084-8BD6-8373-E6F8-7E2FBF2D8E93}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1940,8 +1951,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2991827" y="1550982"/>
-          <a:ext cx="2795743" cy="1837588"/>
+          <a:off x="3090332" y="1661583"/>
+          <a:ext cx="2444751" cy="1628233"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1968,22 +1979,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>984606</xdr:colOff>
+      <xdr:colOff>995309</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>96321</xdr:rowOff>
+      <xdr:rowOff>117724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>139129</xdr:colOff>
+      <xdr:colOff>21404</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>171220</xdr:rowOff>
+      <xdr:rowOff>101388</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BE02404-556D-C06C-19FE-DBEF2347C50F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E14C047-62C6-2ECE-840E-07107F1B278C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2006,8 +2017,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3092949" y="1626742"/>
-          <a:ext cx="2493624" cy="1680236"/>
+          <a:off x="3103652" y="1648145"/>
+          <a:ext cx="2365196" cy="1589001"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2033,23 +2044,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>984605</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>139128</xdr:rowOff>
+      <xdr:rowOff>181938</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>104747</xdr:colOff>
+      <xdr:colOff>92867</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>192640</xdr:rowOff>
+      <xdr:rowOff>139129</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B4783D3-88AE-549A-0488-3966D64868B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE760D75-BAB5-2CEB-130E-5D003D5349A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2072,8 +2083,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3092948" y="1669549"/>
-          <a:ext cx="2459243" cy="1658849"/>
+          <a:off x="3221377" y="1712359"/>
+          <a:ext cx="2318934" cy="1562528"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2302,85 +2313,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="53"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="50"/>
+      <c r="O6" s="50"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2400,46 +2411,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="66"/>
-      <c r="I13" s="71">
+      <c r="H13" s="63"/>
+      <c r="I13" s="68">
         <v>46127</v>
       </c>
-      <c r="J13" s="65"/>
-      <c r="K13" s="66"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="63"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="64"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="66"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="63"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="64"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="66"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="63"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2448,13 +2459,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="67" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="53"/>
+      <c r="G17" s="64" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="50"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3468,19 +3479,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="58" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="59"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -3492,192 +3503,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="93">
+      <c r="E2" s="58"/>
+      <c r="F2" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="58"/>
+      <c r="H2" s="69">
         <v>46121</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="46"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="55"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="48"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="45"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="75" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="87" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="88"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="62"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="62"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="75"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="62"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="75"/>
+    </row>
+    <row r="9" spans="1:10" ht="93.75" customHeight="1">
+      <c r="A9" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="63"/>
+      <c r="D9" s="91" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="75"/>
+    </row>
+    <row r="10" spans="1:10" ht="56.25" customHeight="1">
+      <c r="A10" s="83"/>
+      <c r="B10" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="91" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="75"/>
+    </row>
+    <row r="11" spans="1:10" ht="56.25" customHeight="1">
+      <c r="A11" s="84"/>
+      <c r="B11" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="63"/>
+      <c r="D11" s="91" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="75"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="62"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="74" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="77"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="88" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="78" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="80"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="65"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="81" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="82"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="88" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="65"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="81" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="82"/>
-    </row>
-    <row r="9" spans="1:10" ht="93.75" customHeight="1">
-      <c r="A9" s="89" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="92" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="83" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="82"/>
-    </row>
-    <row r="10" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A10" s="90"/>
-      <c r="B10" s="92" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="83" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="82"/>
-    </row>
-    <row r="11" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A11" s="91"/>
-      <c r="B11" s="92" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="83" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="82"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="65"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="81" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="82"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="75"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="84" t="s">
+      <c r="A13" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="74"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="86"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4668,17 +4679,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4687,14 +4695,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4713,19 +4724,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="58" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="59"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -4737,48 +4748,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="42">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="58"/>
+      <c r="F2" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="58"/>
+      <c r="H2" s="39">
         <v>46125</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="46"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="55"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="48"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="45"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6132,19 +6143,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="58" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="59"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -6156,48 +6167,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="42">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="58"/>
+      <c r="F2" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="58"/>
+      <c r="H2" s="39">
         <v>46125</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="46"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="55"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="48"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="45"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7536,7 +7547,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1001"/>
+  <dimension ref="A1:J993"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -7546,19 +7557,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="58" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="59"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7570,190 +7581,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="42">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="58"/>
+      <c r="F2" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="58"/>
+      <c r="H2" s="39">
         <v>46121</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="46"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="44"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="104" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="96" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="88"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="82"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="75"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="105"/>
-      <c r="B7" s="106"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="107"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="108"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="100"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="108"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="100"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="108"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="100"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="52"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="108"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="100"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="52"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="108"/>
+      <c r="A12" s="49"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="100"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="52"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="108"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="100"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="103" t="s">
+      <c r="A14" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="82"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="75"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="103" t="s">
+      <c r="A15" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="81" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="66"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="63"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
@@ -7762,11 +7773,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="103" t="s">
+      <c r="A16" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="66"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="63"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -7779,18 +7790,18 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="109" t="s">
+      <c r="H16" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="65"/>
-      <c r="J16" s="82"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="75"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="96" t="s">
+      <c r="A17" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="63"/>
       <c r="D17" s="17" t="s">
         <v>78</v>
       </c>
@@ -7801,36 +7812,38 @@
         <v>77</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="82"/>
+      <c r="H17" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="62"/>
+      <c r="J17" s="75"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="96" t="s">
+      <c r="A18" s="95" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="65"/>
-      <c r="C18" s="66"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="63"/>
       <c r="D18" s="17" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18" s="18"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="82"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="75"/>
     </row>
     <row r="19" spans="1:10" ht="19.350000000000001" customHeight="1">
-      <c r="A19" s="96" t="s">
+      <c r="A19" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="65"/>
-      <c r="C19" s="66"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="63"/>
       <c r="D19" s="17" t="s">
         <v>80</v>
       </c>
@@ -7840,61 +7853,61 @@
       <c r="F19" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G19" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="H19" s="83" t="s">
-        <v>114</v>
-      </c>
-      <c r="I19" s="65"/>
-      <c r="J19" s="82"/>
+      <c r="G19" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" s="91" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" s="62"/>
+      <c r="J19" s="75"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="65"/>
-      <c r="C20" s="66"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="63"/>
       <c r="D20" s="17" t="s">
         <v>83</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G20" s="18"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="82"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="75"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="96" t="s">
+      <c r="A21" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="63"/>
       <c r="D21" s="17" t="s">
         <v>84</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G21" s="18"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="82"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="75"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="65"/>
-      <c r="C22" s="66"/>
+      <c r="B22" s="102"/>
+      <c r="C22" s="103"/>
       <c r="D22" s="17" t="s">
         <v>85</v>
       </c>
@@ -7905,55 +7918,112 @@
         <v>86</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="H22" s="81"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="82"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="96" t="s">
+        <v>101</v>
+      </c>
+      <c r="H22" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" s="104"/>
+      <c r="J22" s="105"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A23" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="97"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="H23" s="81"/>
-      <c r="I23" s="99"/>
-      <c r="J23" s="100"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="85"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="86"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="102" t="s">
+      <c r="A24" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="62"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="75"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="62"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="62"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="101" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="62"/>
+      <c r="J26" s="75"/>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A27" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="73"/>
-      <c r="C24" s="85"/>
-      <c r="D24" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="H24" s="72"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="74"/>
-    </row>
-    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="B27" s="106"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H27" s="85"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="86"/>
+    </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8920,25 +8990,29 @@
     <row r="991" ht="12.75" customHeight="1"/>
     <row r="992" ht="12.75" customHeight="1"/>
     <row r="993" ht="12.75" customHeight="1"/>
-    <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
-    <row r="996" ht="12.75" customHeight="1"/>
-    <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
-    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+  <mergeCells count="38">
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D5:J5"/>
@@ -8950,19 +9024,12 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8976,7 +9043,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J995"/>
+  <dimension ref="A1:J994"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -8986,19 +9053,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="58" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="59"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9010,203 +9077,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="58"/>
+      <c r="F2" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="58"/>
+      <c r="H2" s="39">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="43"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="44"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="49"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="44"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="81"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="96" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="88"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="75"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="49"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="100"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="49"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="100"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="49"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="100"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="49"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="100"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="49"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="100"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="49"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="100"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="75"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="62"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="42">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="46"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="47"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="47"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="104" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="77"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="103" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="82"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="105"/>
-      <c r="B7" s="106"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="107"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="108"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="108"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="108"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="52"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="108"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="52"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="108"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="52"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="108"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="103" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="82"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="103" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="81" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="66"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="63"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="103" t="s">
+      <c r="A16" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="66"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="63"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -9219,44 +9286,33 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="109" t="s">
+      <c r="H16" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="65"/>
-      <c r="J16" s="82"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="96" t="s">
+      <c r="I16" s="62"/>
+      <c r="J16" s="75"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="93" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="97"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="F17" s="38"/>
-      <c r="G17" s="40" t="s">
+      <c r="B17" s="106"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="H17" s="81"/>
-      <c r="I17" s="99"/>
-      <c r="J17" s="100"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="110"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="113"/>
-    </row>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="H17" s="85"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="109"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10233,18 +10289,8 @@
     <row r="992" ht="12.75" customHeight="1"/>
     <row r="993" ht="12.75" customHeight="1"/>
     <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
+  <mergeCells count="19">
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -10257,6 +10303,13 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10270,7 +10323,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J995"/>
+  <dimension ref="A1:J994"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -10280,19 +10333,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="58" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="59"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10304,203 +10357,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="42">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="58"/>
+      <c r="F2" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="58"/>
+      <c r="H2" s="39">
         <v>46125</v>
       </c>
-      <c r="I2" s="45" t="s">
+      <c r="I2" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="46"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="47"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="44"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="104" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="88"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="82"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="75"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="105"/>
-      <c r="B7" s="106"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="107"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="108"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="100"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="108"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="100"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="52"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="108"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="100"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="52"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="108"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="100"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="52"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="108"/>
+      <c r="A12" s="49"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="100"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="52"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="108"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="100"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="103" t="s">
+      <c r="A14" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="82"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="75"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="103" t="s">
+      <c r="A15" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="81" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="66"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="63"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="103" t="s">
+      <c r="A16" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="66"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="63"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -10513,41 +10566,33 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="109" t="s">
+      <c r="H16" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="65"/>
-      <c r="J16" s="82"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="96" t="s">
+      <c r="I16" s="62"/>
+      <c r="J16" s="75"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="93" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="97"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="F17" s="38"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="99"/>
-      <c r="J17" s="100"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="110"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="113"/>
-    </row>
+      <c r="B17" s="106"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" s="85"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="109"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11524,16 +11569,10 @@
     <row r="992" ht="12.75" customHeight="1"/>
     <row r="993" ht="12.75" customHeight="1"/>
     <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
+  <mergeCells count="19">
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -11546,8 +11585,11 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11567,186 +11609,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="58" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="58" t="s">
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="58" t="s">
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="58" t="s">
+      <c r="P1" s="56"/>
+      <c r="Q1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="59"/>
-      <c r="S1" s="58" t="s">
+      <c r="R1" s="56"/>
+      <c r="S1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="77"/>
+      <c r="T1" s="88"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="107"/>
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="99"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="108"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="100"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="55"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="57"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="122"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="60"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="114"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="75" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="77"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="81"/>
+      <c r="O5" s="81"/>
+      <c r="P5" s="81"/>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="81"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="88"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="81" t="s">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="82"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="75"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="103" t="s">
+      <c r="A7" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="81" t="s">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="65"/>
-      <c r="M7" s="65"/>
-      <c r="N7" s="65"/>
-      <c r="O7" s="65"/>
-      <c r="P7" s="65"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="65"/>
-      <c r="S7" s="65"/>
-      <c r="T7" s="82"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="62"/>
+      <c r="T7" s="75"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11945,37 +11987,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="103" t="s">
+      <c r="A15" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="121" t="s">
+      <c r="B15" s="63"/>
+      <c r="C15" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="66"/>
-      <c r="E15" s="109" t="s">
+      <c r="D15" s="63"/>
+      <c r="E15" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="66"/>
-      <c r="G15" s="109" t="s">
+      <c r="F15" s="63"/>
+      <c r="G15" s="101" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="65"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="109" t="s">
+      <c r="H15" s="62"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="66"/>
-      <c r="L15" s="109" t="s">
+      <c r="K15" s="63"/>
+      <c r="L15" s="101" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="65"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="109" t="s">
+      <c r="M15" s="62"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="65"/>
-      <c r="Q15" s="66"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="63"/>
       <c r="R15" s="15" t="s">
         <v>48</v>
       </c>
@@ -11987,37 +12029,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="114">
+      <c r="A16" s="115">
         <v>1</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="115" t="s">
+      <c r="B16" s="63"/>
+      <c r="C16" s="116" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="66"/>
-      <c r="E16" s="115" t="s">
+      <c r="D16" s="63"/>
+      <c r="E16" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="66"/>
-      <c r="G16" s="120" t="s">
+      <c r="F16" s="63"/>
+      <c r="G16" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="65"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="120" t="s">
+      <c r="H16" s="62"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="66"/>
-      <c r="L16" s="118" t="s">
+      <c r="K16" s="63"/>
+      <c r="L16" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="65"/>
-      <c r="N16" s="66"/>
-      <c r="O16" s="118" t="s">
+      <c r="M16" s="62"/>
+      <c r="N16" s="63"/>
+      <c r="O16" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="65"/>
-      <c r="Q16" s="66"/>
+      <c r="P16" s="62"/>
+      <c r="Q16" s="63"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12029,37 +12071,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="114">
+      <c r="A17" s="115">
         <v>2</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="115" t="s">
+      <c r="B17" s="63"/>
+      <c r="C17" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="66"/>
-      <c r="E17" s="115" t="s">
+      <c r="D17" s="63"/>
+      <c r="E17" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="66"/>
-      <c r="G17" s="120" t="s">
+      <c r="F17" s="63"/>
+      <c r="G17" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="65"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="120" t="s">
+      <c r="H17" s="62"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="K17" s="66"/>
-      <c r="L17" s="118" t="s">
+      <c r="K17" s="63"/>
+      <c r="L17" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="65"/>
-      <c r="N17" s="66"/>
-      <c r="O17" s="118" t="s">
+      <c r="M17" s="62"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="112" t="s">
         <v>62</v>
       </c>
-      <c r="P17" s="65"/>
-      <c r="Q17" s="66"/>
+      <c r="P17" s="62"/>
+      <c r="Q17" s="63"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12071,23 +12113,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="114"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="66"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="65"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="65"/>
-      <c r="Q18" s="66"/>
+      <c r="A18" s="115"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="63"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -12099,23 +12141,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="114"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="120"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="65"/>
-      <c r="Q19" s="66"/>
+      <c r="A19" s="115"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="62"/>
+      <c r="Q19" s="63"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -12127,23 +12169,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="114"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="65"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="65"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="65"/>
-      <c r="Q20" s="66"/>
+      <c r="A20" s="115"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="63"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="63"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -12155,23 +12197,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="114"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="120"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="66"/>
+      <c r="A21" s="115"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="63"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -12183,23 +12225,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="114"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="120"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="120"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="118"/>
-      <c r="P22" s="65"/>
-      <c r="Q22" s="66"/>
+      <c r="A22" s="115"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="63"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="63"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -12211,23 +12253,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="114"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="120"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="66"/>
+      <c r="A23" s="115"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="63"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="63"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -12239,23 +12281,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="114"/>
-      <c r="B24" s="66"/>
-      <c r="C24" s="115"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="115"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="120"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="120"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="118"/>
-      <c r="M24" s="65"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="65"/>
-      <c r="Q24" s="66"/>
+      <c r="A24" s="115"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="63"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -12267,23 +12309,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="114"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="115"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="115"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="120"/>
-      <c r="K25" s="66"/>
-      <c r="L25" s="118"/>
-      <c r="M25" s="65"/>
-      <c r="N25" s="66"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="65"/>
-      <c r="Q25" s="66"/>
+      <c r="A25" s="115"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="63"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="62"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="63"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -12295,23 +12337,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="114"/>
-      <c r="B26" s="66"/>
-      <c r="C26" s="115"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="115"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="120"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="118"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="65"/>
-      <c r="Q26" s="66"/>
+      <c r="A26" s="115"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="116"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="63"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="63"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -12323,23 +12365,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="114"/>
-      <c r="B27" s="66"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="120"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="118"/>
-      <c r="M27" s="65"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="118"/>
-      <c r="P27" s="65"/>
-      <c r="Q27" s="66"/>
+      <c r="A27" s="115"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="63"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -12351,23 +12393,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="114"/>
-      <c r="B28" s="66"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="120"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="120"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="65"/>
-      <c r="Q28" s="66"/>
+      <c r="A28" s="115"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="62"/>
+      <c r="N28" s="63"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="62"/>
+      <c r="Q28" s="63"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -12379,23 +12421,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="114"/>
-      <c r="B29" s="66"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="66"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="120"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="118"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="66"/>
-      <c r="O29" s="118"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="66"/>
+      <c r="A29" s="115"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="63"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="62"/>
+      <c r="N29" s="63"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="62"/>
+      <c r="Q29" s="63"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -12407,23 +12449,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="114"/>
-      <c r="B30" s="66"/>
-      <c r="C30" s="115"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="120"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="66"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="65"/>
-      <c r="Q30" s="66"/>
+      <c r="A30" s="115"/>
+      <c r="B30" s="63"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="63"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="63"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="62"/>
+      <c r="Q30" s="63"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -12435,23 +12477,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="116"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="123"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="123"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="119"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="119"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="85"/>
+      <c r="A31" s="118"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="119"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="119"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="78"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="77"/>
+      <c r="N31" s="78"/>
+      <c r="O31" s="113"/>
+      <c r="P31" s="77"/>
+      <c r="Q31" s="78"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -13449,62 +13491,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -13529,62 +13571,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク登録機能.xlsx
+++ b/document/成果物ドキュメント_タスク登録機能.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER123\Desktop\設計書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0D3F6E-32C0-43A5-9924-75D883756CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96654957-C9C2-4091-B8FF-AC2E6B4F602F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -1516,29 +1516,50 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1564,11 +1585,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1582,14 +1642,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1606,85 +1669,43 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1702,38 +1723,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1741,23 +1747,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1846,23 +1846,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>190501</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>289543</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>140805</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>583312</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>119063</xdr:rowOff>
+      <xdr:colOff>1098687</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>119685</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{283B040E-0DF9-804D-1687-356CC3F5FB10}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51590EE9-5D6E-3062-7915-0111A1D09CBF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1885,8 +1885,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="523876" y="1285876"/>
-          <a:ext cx="7774686" cy="3786187"/>
+          <a:off x="1308304" y="1068457"/>
+          <a:ext cx="7518057" cy="3623228"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2313,85 +2313,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2411,46 +2411,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="67" t="s">
+      <c r="E8" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="61" t="s">
+      <c r="G13" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="63"/>
-      <c r="I13" s="68">
+      <c r="H13" s="65"/>
+      <c r="I13" s="89">
         <v>46127</v>
       </c>
-      <c r="J13" s="62"/>
-      <c r="K13" s="63"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="65"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="61"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="63"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="65"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="61"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="63"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="65"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2459,13 +2459,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="64" t="s">
+      <c r="G17" s="85" t="s">
         <v>110</v>
       </c>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3479,19 +3479,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -3503,192 +3503,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="57" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="69">
+      <c r="G2" s="78"/>
+      <c r="H2" s="81">
         <v>46121</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="43"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="45"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="87" t="s">
+      <c r="B5" s="43"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="88"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="74" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="74" t="s">
+      <c r="B7" s="48"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="75"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="74" t="s">
+      <c r="B8" s="48"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="75"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="49"/>
     </row>
     <row r="9" spans="1:10" ht="93.75" customHeight="1">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="91" t="s">
+      <c r="C9" s="65"/>
+      <c r="D9" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="75"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A10" s="83"/>
-      <c r="B10" s="72" t="s">
+      <c r="A10" s="67"/>
+      <c r="B10" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="91" t="s">
+      <c r="C10" s="65"/>
+      <c r="D10" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="75"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="49"/>
     </row>
     <row r="11" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A11" s="84"/>
-      <c r="B11" s="72" t="s">
+      <c r="A11" s="68"/>
+      <c r="B11" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="91" t="s">
+      <c r="C11" s="65"/>
+      <c r="D11" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="75"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="49"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="74" t="s">
+      <c r="B12" s="48"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="75"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="49"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="86"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="41"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4679,6 +4679,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4687,25 +4706,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4724,19 +4724,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -4748,48 +4748,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="57" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="39">
+      <c r="G2" s="78"/>
+      <c r="H2" s="90">
         <v>46125</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="43"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="45"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6143,19 +6143,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -6167,48 +6167,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="57" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="39">
+      <c r="G2" s="78"/>
+      <c r="H2" s="90">
         <v>46125</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="43"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="45"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7557,19 +7557,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7581,190 +7581,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="57" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="39">
+      <c r="G2" s="78"/>
+      <c r="H2" s="90">
         <v>46121</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="43"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="49"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="44"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="96" t="s">
+      <c r="B5" s="43"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="88"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="75"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="49"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="97"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="106"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="49"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="100"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="107"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="49"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="100"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="107"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="49"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="100"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="107"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="49"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="100"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="107"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="49"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="100"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="107"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="49"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="100"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="107"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="75"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="49"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="74" t="s">
+      <c r="B15" s="48"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
@@ -7773,11 +7773,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="94" t="s">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="63"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -7790,18 +7790,18 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="101" t="s">
+      <c r="H16" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="75"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="49"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="63"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="65"/>
       <c r="D17" s="17" t="s">
         <v>78</v>
       </c>
@@ -7812,18 +7812,18 @@
         <v>77</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="74" t="s">
+      <c r="H17" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="I17" s="62"/>
-      <c r="J17" s="75"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="49"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="95" t="s">
+      <c r="A18" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="63"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="65"/>
       <c r="D18" s="17" t="s">
         <v>79</v>
       </c>
@@ -7834,16 +7834,16 @@
         <v>93</v>
       </c>
       <c r="G18" s="18"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="75"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="1:10" ht="19.350000000000001" customHeight="1">
-      <c r="A19" s="95" t="s">
+      <c r="A19" s="99" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="62"/>
-      <c r="C19" s="63"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="65"/>
       <c r="D19" s="17" t="s">
         <v>80</v>
       </c>
@@ -7856,18 +7856,18 @@
       <c r="G19" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="H19" s="91" t="s">
+      <c r="H19" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="I19" s="62"/>
-      <c r="J19" s="75"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="49"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="95" t="s">
+      <c r="A20" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="62"/>
-      <c r="C20" s="63"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="65"/>
       <c r="D20" s="17" t="s">
         <v>83</v>
       </c>
@@ -7878,16 +7878,16 @@
         <v>94</v>
       </c>
       <c r="G20" s="18"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="75"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="49"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="95" t="s">
+      <c r="A21" s="99" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="62"/>
-      <c r="C21" s="63"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="17" t="s">
         <v>84</v>
       </c>
@@ -7898,16 +7898,16 @@
         <v>90</v>
       </c>
       <c r="G21" s="18"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="75"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="49"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="95" t="s">
+      <c r="A22" s="99" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="102"/>
-      <c r="C22" s="103"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="101"/>
       <c r="D22" s="17" t="s">
         <v>85</v>
       </c>
@@ -7920,18 +7920,18 @@
       <c r="G22" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="H22" s="74" t="s">
+      <c r="H22" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="I22" s="104"/>
-      <c r="J22" s="105"/>
+      <c r="I22" s="97"/>
+      <c r="J22" s="98"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A23" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="94"/>
+      <c r="C23" s="95"/>
       <c r="D23" s="19" t="s">
         <v>92</v>
       </c>
@@ -7942,37 +7942,37 @@
       <c r="G23" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H23" s="85"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="86"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="41"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="94" t="s">
+      <c r="A24" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="75"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="49"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="94" t="s">
+      <c r="A25" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="62"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="74" t="s">
+      <c r="B25" s="48"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="63"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="65"/>
       <c r="I25" s="15" t="s">
         <v>24</v>
       </c>
@@ -7981,11 +7981,11 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="94" t="s">
+      <c r="A26" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="62"/>
-      <c r="C26" s="63"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="65"/>
       <c r="D26" s="15" t="s">
         <v>26</v>
       </c>
@@ -7998,18 +7998,18 @@
       <c r="G26" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="101" t="s">
+      <c r="H26" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="62"/>
-      <c r="J26" s="75"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="49"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A27" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="106"/>
-      <c r="C27" s="107"/>
+      <c r="B27" s="94"/>
+      <c r="C27" s="95"/>
       <c r="D27" s="19" t="s">
         <v>112</v>
       </c>
@@ -8020,9 +8020,9 @@
       <c r="G27" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="H27" s="85"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="86"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="41"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8992,24 +8992,9 @@
     <row r="993" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9024,12 +9009,27 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9053,19 +9053,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9077,190 +9077,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="57" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="39">
+      <c r="G2" s="78"/>
+      <c r="H2" s="90">
         <v>46125</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="43"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="49"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="44"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="96" t="s">
+      <c r="B5" s="43"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="103" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="88"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="75"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="49"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="97"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
+      <c r="A7" s="104"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="106"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="49"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="100"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="107"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="49"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="100"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="107"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="49"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="100"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="107"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="49"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="100"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="107"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="49"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="100"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="107"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="49"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="100"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="107"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="75"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="49"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="74" t="s">
+      <c r="B15" s="48"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
@@ -9269,11 +9269,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="94" t="s">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="63"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -9286,18 +9286,18 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="101" t="s">
+      <c r="H16" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="75"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="49"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A17" s="93" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="106"/>
-      <c r="C17" s="107"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="95"/>
       <c r="D17" s="19" t="s">
         <v>112</v>
       </c>
@@ -9308,1287 +9308,7 @@
       <c r="G17" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="85"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="109"/>
-    </row>
-    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="33" ht="12.75" customHeight="1"/>
-    <row r="34" ht="12.75" customHeight="1"/>
-    <row r="35" ht="12.75" customHeight="1"/>
-    <row r="36" ht="12.75" customHeight="1"/>
-    <row r="37" ht="12.75" customHeight="1"/>
-    <row r="38" ht="12.75" customHeight="1"/>
-    <row r="39" ht="12.75" customHeight="1"/>
-    <row r="40" ht="12.75" customHeight="1"/>
-    <row r="41" ht="12.75" customHeight="1"/>
-    <row r="42" ht="12.75" customHeight="1"/>
-    <row r="43" ht="12.75" customHeight="1"/>
-    <row r="44" ht="12.75" customHeight="1"/>
-    <row r="45" ht="12.75" customHeight="1"/>
-    <row r="46" ht="12.75" customHeight="1"/>
-    <row r="47" ht="12.75" customHeight="1"/>
-    <row r="48" ht="12.75" customHeight="1"/>
-    <row r="49" ht="12.75" customHeight="1"/>
-    <row r="50" ht="12.75" customHeight="1"/>
-    <row r="51" ht="12.75" customHeight="1"/>
-    <row r="52" ht="12.75" customHeight="1"/>
-    <row r="53" ht="12.75" customHeight="1"/>
-    <row r="54" ht="12.75" customHeight="1"/>
-    <row r="55" ht="12.75" customHeight="1"/>
-    <row r="56" ht="12.75" customHeight="1"/>
-    <row r="57" ht="12.75" customHeight="1"/>
-    <row r="58" ht="12.75" customHeight="1"/>
-    <row r="59" ht="12.75" customHeight="1"/>
-    <row r="60" ht="12.75" customHeight="1"/>
-    <row r="61" ht="12.75" customHeight="1"/>
-    <row r="62" ht="12.75" customHeight="1"/>
-    <row r="63" ht="12.75" customHeight="1"/>
-    <row r="64" ht="12.75" customHeight="1"/>
-    <row r="65" ht="12.75" customHeight="1"/>
-    <row r="66" ht="12.75" customHeight="1"/>
-    <row r="67" ht="12.75" customHeight="1"/>
-    <row r="68" ht="12.75" customHeight="1"/>
-    <row r="69" ht="12.75" customHeight="1"/>
-    <row r="70" ht="12.75" customHeight="1"/>
-    <row r="71" ht="12.75" customHeight="1"/>
-    <row r="72" ht="12.75" customHeight="1"/>
-    <row r="73" ht="12.75" customHeight="1"/>
-    <row r="74" ht="12.75" customHeight="1"/>
-    <row r="75" ht="12.75" customHeight="1"/>
-    <row r="76" ht="12.75" customHeight="1"/>
-    <row r="77" ht="12.75" customHeight="1"/>
-    <row r="78" ht="12.75" customHeight="1"/>
-    <row r="79" ht="12.75" customHeight="1"/>
-    <row r="80" ht="12.75" customHeight="1"/>
-    <row r="81" ht="12.75" customHeight="1"/>
-    <row r="82" ht="12.75" customHeight="1"/>
-    <row r="83" ht="12.75" customHeight="1"/>
-    <row r="84" ht="12.75" customHeight="1"/>
-    <row r="85" ht="12.75" customHeight="1"/>
-    <row r="86" ht="12.75" customHeight="1"/>
-    <row r="87" ht="12.75" customHeight="1"/>
-    <row r="88" ht="12.75" customHeight="1"/>
-    <row r="89" ht="12.75" customHeight="1"/>
-    <row r="90" ht="12.75" customHeight="1"/>
-    <row r="91" ht="12.75" customHeight="1"/>
-    <row r="92" ht="12.75" customHeight="1"/>
-    <row r="93" ht="12.75" customHeight="1"/>
-    <row r="94" ht="12.75" customHeight="1"/>
-    <row r="95" ht="12.75" customHeight="1"/>
-    <row r="96" ht="12.75" customHeight="1"/>
-    <row r="97" ht="12.75" customHeight="1"/>
-    <row r="98" ht="12.75" customHeight="1"/>
-    <row r="99" ht="12.75" customHeight="1"/>
-    <row r="100" ht="12.75" customHeight="1"/>
-    <row r="101" ht="12.75" customHeight="1"/>
-    <row r="102" ht="12.75" customHeight="1"/>
-    <row r="103" ht="12.75" customHeight="1"/>
-    <row r="104" ht="12.75" customHeight="1"/>
-    <row r="105" ht="12.75" customHeight="1"/>
-    <row r="106" ht="12.75" customHeight="1"/>
-    <row r="107" ht="12.75" customHeight="1"/>
-    <row r="108" ht="12.75" customHeight="1"/>
-    <row r="109" ht="12.75" customHeight="1"/>
-    <row r="110" ht="12.75" customHeight="1"/>
-    <row r="111" ht="12.75" customHeight="1"/>
-    <row r="112" ht="12.75" customHeight="1"/>
-    <row r="113" ht="12.75" customHeight="1"/>
-    <row r="114" ht="12.75" customHeight="1"/>
-    <row r="115" ht="12.75" customHeight="1"/>
-    <row r="116" ht="12.75" customHeight="1"/>
-    <row r="117" ht="12.75" customHeight="1"/>
-    <row r="118" ht="12.75" customHeight="1"/>
-    <row r="119" ht="12.75" customHeight="1"/>
-    <row r="120" ht="12.75" customHeight="1"/>
-    <row r="121" ht="12.75" customHeight="1"/>
-    <row r="122" ht="12.75" customHeight="1"/>
-    <row r="123" ht="12.75" customHeight="1"/>
-    <row r="124" ht="12.75" customHeight="1"/>
-    <row r="125" ht="12.75" customHeight="1"/>
-    <row r="126" ht="12.75" customHeight="1"/>
-    <row r="127" ht="12.75" customHeight="1"/>
-    <row r="128" ht="12.75" customHeight="1"/>
-    <row r="129" ht="12.75" customHeight="1"/>
-    <row r="130" ht="12.75" customHeight="1"/>
-    <row r="131" ht="12.75" customHeight="1"/>
-    <row r="132" ht="12.75" customHeight="1"/>
-    <row r="133" ht="12.75" customHeight="1"/>
-    <row r="134" ht="12.75" customHeight="1"/>
-    <row r="135" ht="12.75" customHeight="1"/>
-    <row r="136" ht="12.75" customHeight="1"/>
-    <row r="137" ht="12.75" customHeight="1"/>
-    <row r="138" ht="12.75" customHeight="1"/>
-    <row r="139" ht="12.75" customHeight="1"/>
-    <row r="140" ht="12.75" customHeight="1"/>
-    <row r="141" ht="12.75" customHeight="1"/>
-    <row r="142" ht="12.75" customHeight="1"/>
-    <row r="143" ht="12.75" customHeight="1"/>
-    <row r="144" ht="12.75" customHeight="1"/>
-    <row r="145" ht="12.75" customHeight="1"/>
-    <row r="146" ht="12.75" customHeight="1"/>
-    <row r="147" ht="12.75" customHeight="1"/>
-    <row r="148" ht="12.75" customHeight="1"/>
-    <row r="149" ht="12.75" customHeight="1"/>
-    <row r="150" ht="12.75" customHeight="1"/>
-    <row r="151" ht="12.75" customHeight="1"/>
-    <row r="152" ht="12.75" customHeight="1"/>
-    <row r="153" ht="12.75" customHeight="1"/>
-    <row r="154" ht="12.75" customHeight="1"/>
-    <row r="155" ht="12.75" customHeight="1"/>
-    <row r="156" ht="12.75" customHeight="1"/>
-    <row r="157" ht="12.75" customHeight="1"/>
-    <row r="158" ht="12.75" customHeight="1"/>
-    <row r="159" ht="12.75" customHeight="1"/>
-    <row r="160" ht="12.75" customHeight="1"/>
-    <row r="161" ht="12.75" customHeight="1"/>
-    <row r="162" ht="12.75" customHeight="1"/>
-    <row r="163" ht="12.75" customHeight="1"/>
-    <row r="164" ht="12.75" customHeight="1"/>
-    <row r="165" ht="12.75" customHeight="1"/>
-    <row r="166" ht="12.75" customHeight="1"/>
-    <row r="167" ht="12.75" customHeight="1"/>
-    <row r="168" ht="12.75" customHeight="1"/>
-    <row r="169" ht="12.75" customHeight="1"/>
-    <row r="170" ht="12.75" customHeight="1"/>
-    <row r="171" ht="12.75" customHeight="1"/>
-    <row r="172" ht="12.75" customHeight="1"/>
-    <row r="173" ht="12.75" customHeight="1"/>
-    <row r="174" ht="12.75" customHeight="1"/>
-    <row r="175" ht="12.75" customHeight="1"/>
-    <row r="176" ht="12.75" customHeight="1"/>
-    <row r="177" ht="12.75" customHeight="1"/>
-    <row r="178" ht="12.75" customHeight="1"/>
-    <row r="179" ht="12.75" customHeight="1"/>
-    <row r="180" ht="12.75" customHeight="1"/>
-    <row r="181" ht="12.75" customHeight="1"/>
-    <row r="182" ht="12.75" customHeight="1"/>
-    <row r="183" ht="12.75" customHeight="1"/>
-    <row r="184" ht="12.75" customHeight="1"/>
-    <row r="185" ht="12.75" customHeight="1"/>
-    <row r="186" ht="12.75" customHeight="1"/>
-    <row r="187" ht="12.75" customHeight="1"/>
-    <row r="188" ht="12.75" customHeight="1"/>
-    <row r="189" ht="12.75" customHeight="1"/>
-    <row r="190" ht="12.75" customHeight="1"/>
-    <row r="191" ht="12.75" customHeight="1"/>
-    <row r="192" ht="12.75" customHeight="1"/>
-    <row r="193" ht="12.75" customHeight="1"/>
-    <row r="194" ht="12.75" customHeight="1"/>
-    <row r="195" ht="12.75" customHeight="1"/>
-    <row r="196" ht="12.75" customHeight="1"/>
-    <row r="197" ht="12.75" customHeight="1"/>
-    <row r="198" ht="12.75" customHeight="1"/>
-    <row r="199" ht="12.75" customHeight="1"/>
-    <row r="200" ht="12.75" customHeight="1"/>
-    <row r="201" ht="12.75" customHeight="1"/>
-    <row r="202" ht="12.75" customHeight="1"/>
-    <row r="203" ht="12.75" customHeight="1"/>
-    <row r="204" ht="12.75" customHeight="1"/>
-    <row r="205" ht="12.75" customHeight="1"/>
-    <row r="206" ht="12.75" customHeight="1"/>
-    <row r="207" ht="12.75" customHeight="1"/>
-    <row r="208" ht="12.75" customHeight="1"/>
-    <row r="209" ht="12.75" customHeight="1"/>
-    <row r="210" ht="12.75" customHeight="1"/>
-    <row r="211" ht="12.75" customHeight="1"/>
-    <row r="212" ht="12.75" customHeight="1"/>
-    <row r="213" ht="12.75" customHeight="1"/>
-    <row r="214" ht="12.75" customHeight="1"/>
-    <row r="215" ht="12.75" customHeight="1"/>
-    <row r="216" ht="12.75" customHeight="1"/>
-    <row r="217" ht="12.75" customHeight="1"/>
-    <row r="218" ht="12.75" customHeight="1"/>
-    <row r="219" ht="12.75" customHeight="1"/>
-    <row r="220" ht="12.75" customHeight="1"/>
-    <row r="221" ht="12.75" customHeight="1"/>
-    <row r="222" ht="12.75" customHeight="1"/>
-    <row r="223" ht="12.75" customHeight="1"/>
-    <row r="224" ht="12.75" customHeight="1"/>
-    <row r="225" ht="12.75" customHeight="1"/>
-    <row r="226" ht="12.75" customHeight="1"/>
-    <row r="227" ht="12.75" customHeight="1"/>
-    <row r="228" ht="12.75" customHeight="1"/>
-    <row r="229" ht="12.75" customHeight="1"/>
-    <row r="230" ht="12.75" customHeight="1"/>
-    <row r="231" ht="12.75" customHeight="1"/>
-    <row r="232" ht="12.75" customHeight="1"/>
-    <row r="233" ht="12.75" customHeight="1"/>
-    <row r="234" ht="12.75" customHeight="1"/>
-    <row r="235" ht="12.75" customHeight="1"/>
-    <row r="236" ht="12.75" customHeight="1"/>
-    <row r="237" ht="12.75" customHeight="1"/>
-    <row r="238" ht="12.75" customHeight="1"/>
-    <row r="239" ht="12.75" customHeight="1"/>
-    <row r="240" ht="12.75" customHeight="1"/>
-    <row r="241" ht="12.75" customHeight="1"/>
-    <row r="242" ht="12.75" customHeight="1"/>
-    <row r="243" ht="12.75" customHeight="1"/>
-    <row r="244" ht="12.75" customHeight="1"/>
-    <row r="245" ht="12.75" customHeight="1"/>
-    <row r="246" ht="12.75" customHeight="1"/>
-    <row r="247" ht="12.75" customHeight="1"/>
-    <row r="248" ht="12.75" customHeight="1"/>
-    <row r="249" ht="12.75" customHeight="1"/>
-    <row r="250" ht="12.75" customHeight="1"/>
-    <row r="251" ht="12.75" customHeight="1"/>
-    <row r="252" ht="12.75" customHeight="1"/>
-    <row r="253" ht="12.75" customHeight="1"/>
-    <row r="254" ht="12.75" customHeight="1"/>
-    <row r="255" ht="12.75" customHeight="1"/>
-    <row r="256" ht="12.75" customHeight="1"/>
-    <row r="257" ht="12.75" customHeight="1"/>
-    <row r="258" ht="12.75" customHeight="1"/>
-    <row r="259" ht="12.75" customHeight="1"/>
-    <row r="260" ht="12.75" customHeight="1"/>
-    <row r="261" ht="12.75" customHeight="1"/>
-    <row r="262" ht="12.75" customHeight="1"/>
-    <row r="263" ht="12.75" customHeight="1"/>
-    <row r="264" ht="12.75" customHeight="1"/>
-    <row r="265" ht="12.75" customHeight="1"/>
-    <row r="266" ht="12.75" customHeight="1"/>
-    <row r="267" ht="12.75" customHeight="1"/>
-    <row r="268" ht="12.75" customHeight="1"/>
-    <row r="269" ht="12.75" customHeight="1"/>
-    <row r="270" ht="12.75" customHeight="1"/>
-    <row r="271" ht="12.75" customHeight="1"/>
-    <row r="272" ht="12.75" customHeight="1"/>
-    <row r="273" ht="12.75" customHeight="1"/>
-    <row r="274" ht="12.75" customHeight="1"/>
-    <row r="275" ht="12.75" customHeight="1"/>
-    <row r="276" ht="12.75" customHeight="1"/>
-    <row r="277" ht="12.75" customHeight="1"/>
-    <row r="278" ht="12.75" customHeight="1"/>
-    <row r="279" ht="12.75" customHeight="1"/>
-    <row r="280" ht="12.75" customHeight="1"/>
-    <row r="281" ht="12.75" customHeight="1"/>
-    <row r="282" ht="12.75" customHeight="1"/>
-    <row r="283" ht="12.75" customHeight="1"/>
-    <row r="284" ht="12.75" customHeight="1"/>
-    <row r="285" ht="12.75" customHeight="1"/>
-    <row r="286" ht="12.75" customHeight="1"/>
-    <row r="287" ht="12.75" customHeight="1"/>
-    <row r="288" ht="12.75" customHeight="1"/>
-    <row r="289" ht="12.75" customHeight="1"/>
-    <row r="290" ht="12.75" customHeight="1"/>
-    <row r="291" ht="12.75" customHeight="1"/>
-    <row r="292" ht="12.75" customHeight="1"/>
-    <row r="293" ht="12.75" customHeight="1"/>
-    <row r="294" ht="12.75" customHeight="1"/>
-    <row r="295" ht="12.75" customHeight="1"/>
-    <row r="296" ht="12.75" customHeight="1"/>
-    <row r="297" ht="12.75" customHeight="1"/>
-    <row r="298" ht="12.75" customHeight="1"/>
-    <row r="299" ht="12.75" customHeight="1"/>
-    <row r="300" ht="12.75" customHeight="1"/>
-    <row r="301" ht="12.75" customHeight="1"/>
-    <row r="302" ht="12.75" customHeight="1"/>
-    <row r="303" ht="12.75" customHeight="1"/>
-    <row r="304" ht="12.75" customHeight="1"/>
-    <row r="305" ht="12.75" customHeight="1"/>
-    <row r="306" ht="12.75" customHeight="1"/>
-    <row r="307" ht="12.75" customHeight="1"/>
-    <row r="308" ht="12.75" customHeight="1"/>
-    <row r="309" ht="12.75" customHeight="1"/>
-    <row r="310" ht="12.75" customHeight="1"/>
-    <row r="311" ht="12.75" customHeight="1"/>
-    <row r="312" ht="12.75" customHeight="1"/>
-    <row r="313" ht="12.75" customHeight="1"/>
-    <row r="314" ht="12.75" customHeight="1"/>
-    <row r="315" ht="12.75" customHeight="1"/>
-    <row r="316" ht="12.75" customHeight="1"/>
-    <row r="317" ht="12.75" customHeight="1"/>
-    <row r="318" ht="12.75" customHeight="1"/>
-    <row r="319" ht="12.75" customHeight="1"/>
-    <row r="320" ht="12.75" customHeight="1"/>
-    <row r="321" ht="12.75" customHeight="1"/>
-    <row r="322" ht="12.75" customHeight="1"/>
-    <row r="323" ht="12.75" customHeight="1"/>
-    <row r="324" ht="12.75" customHeight="1"/>
-    <row r="325" ht="12.75" customHeight="1"/>
-    <row r="326" ht="12.75" customHeight="1"/>
-    <row r="327" ht="12.75" customHeight="1"/>
-    <row r="328" ht="12.75" customHeight="1"/>
-    <row r="329" ht="12.75" customHeight="1"/>
-    <row r="330" ht="12.75" customHeight="1"/>
-    <row r="331" ht="12.75" customHeight="1"/>
-    <row r="332" ht="12.75" customHeight="1"/>
-    <row r="333" ht="12.75" customHeight="1"/>
-    <row r="334" ht="12.75" customHeight="1"/>
-    <row r="335" ht="12.75" customHeight="1"/>
-    <row r="336" ht="12.75" customHeight="1"/>
-    <row r="337" ht="12.75" customHeight="1"/>
-    <row r="338" ht="12.75" customHeight="1"/>
-    <row r="339" ht="12.75" customHeight="1"/>
-    <row r="340" ht="12.75" customHeight="1"/>
-    <row r="341" ht="12.75" customHeight="1"/>
-    <row r="342" ht="12.75" customHeight="1"/>
-    <row r="343" ht="12.75" customHeight="1"/>
-    <row r="344" ht="12.75" customHeight="1"/>
-    <row r="345" ht="12.75" customHeight="1"/>
-    <row r="346" ht="12.75" customHeight="1"/>
-    <row r="347" ht="12.75" customHeight="1"/>
-    <row r="348" ht="12.75" customHeight="1"/>
-    <row r="349" ht="12.75" customHeight="1"/>
-    <row r="350" ht="12.75" customHeight="1"/>
-    <row r="351" ht="12.75" customHeight="1"/>
-    <row r="352" ht="12.75" customHeight="1"/>
-    <row r="353" ht="12.75" customHeight="1"/>
-    <row r="354" ht="12.75" customHeight="1"/>
-    <row r="355" ht="12.75" customHeight="1"/>
-    <row r="356" ht="12.75" customHeight="1"/>
-    <row r="357" ht="12.75" customHeight="1"/>
-    <row r="358" ht="12.75" customHeight="1"/>
-    <row r="359" ht="12.75" customHeight="1"/>
-    <row r="360" ht="12.75" customHeight="1"/>
-    <row r="361" ht="12.75" customHeight="1"/>
-    <row r="362" ht="12.75" customHeight="1"/>
-    <row r="363" ht="12.75" customHeight="1"/>
-    <row r="364" ht="12.75" customHeight="1"/>
-    <row r="365" ht="12.75" customHeight="1"/>
-    <row r="366" ht="12.75" customHeight="1"/>
-    <row r="367" ht="12.75" customHeight="1"/>
-    <row r="368" ht="12.75" customHeight="1"/>
-    <row r="369" ht="12.75" customHeight="1"/>
-    <row r="370" ht="12.75" customHeight="1"/>
-    <row r="371" ht="12.75" customHeight="1"/>
-    <row r="372" ht="12.75" customHeight="1"/>
-    <row r="373" ht="12.75" customHeight="1"/>
-    <row r="374" ht="12.75" customHeight="1"/>
-    <row r="375" ht="12.75" customHeight="1"/>
-    <row r="376" ht="12.75" customHeight="1"/>
-    <row r="377" ht="12.75" customHeight="1"/>
-    <row r="378" ht="12.75" customHeight="1"/>
-    <row r="379" ht="12.75" customHeight="1"/>
-    <row r="380" ht="12.75" customHeight="1"/>
-    <row r="381" ht="12.75" customHeight="1"/>
-    <row r="382" ht="12.75" customHeight="1"/>
-    <row r="383" ht="12.75" customHeight="1"/>
-    <row r="384" ht="12.75" customHeight="1"/>
-    <row r="385" ht="12.75" customHeight="1"/>
-    <row r="386" ht="12.75" customHeight="1"/>
-    <row r="387" ht="12.75" customHeight="1"/>
-    <row r="388" ht="12.75" customHeight="1"/>
-    <row r="389" ht="12.75" customHeight="1"/>
-    <row r="390" ht="12.75" customHeight="1"/>
-    <row r="391" ht="12.75" customHeight="1"/>
-    <row r="392" ht="12.75" customHeight="1"/>
-    <row r="393" ht="12.75" customHeight="1"/>
-    <row r="394" ht="12.75" customHeight="1"/>
-    <row r="395" ht="12.75" customHeight="1"/>
-    <row r="396" ht="12.75" customHeight="1"/>
-    <row r="397" ht="12.75" customHeight="1"/>
-    <row r="398" ht="12.75" customHeight="1"/>
-    <row r="399" ht="12.75" customHeight="1"/>
-    <row r="400" ht="12.75" customHeight="1"/>
-    <row r="401" ht="12.75" customHeight="1"/>
-    <row r="402" ht="12.75" customHeight="1"/>
-    <row r="403" ht="12.75" customHeight="1"/>
-    <row r="404" ht="12.75" customHeight="1"/>
-    <row r="405" ht="12.75" customHeight="1"/>
-    <row r="406" ht="12.75" customHeight="1"/>
-    <row r="407" ht="12.75" customHeight="1"/>
-    <row r="408" ht="12.75" customHeight="1"/>
-    <row r="409" ht="12.75" customHeight="1"/>
-    <row r="410" ht="12.75" customHeight="1"/>
-    <row r="411" ht="12.75" customHeight="1"/>
-    <row r="412" ht="12.75" customHeight="1"/>
-    <row r="413" ht="12.75" customHeight="1"/>
-    <row r="414" ht="12.75" customHeight="1"/>
-    <row r="415" ht="12.75" customHeight="1"/>
-    <row r="416" ht="12.75" customHeight="1"/>
-    <row r="417" ht="12.75" customHeight="1"/>
-    <row r="418" ht="12.75" customHeight="1"/>
-    <row r="419" ht="12.75" customHeight="1"/>
-    <row r="420" ht="12.75" customHeight="1"/>
-    <row r="421" ht="12.75" customHeight="1"/>
-    <row r="422" ht="12.75" customHeight="1"/>
-    <row r="423" ht="12.75" customHeight="1"/>
-    <row r="424" ht="12.75" customHeight="1"/>
-    <row r="425" ht="12.75" customHeight="1"/>
-    <row r="426" ht="12.75" customHeight="1"/>
-    <row r="427" ht="12.75" customHeight="1"/>
-    <row r="428" ht="12.75" customHeight="1"/>
-    <row r="429" ht="12.75" customHeight="1"/>
-    <row r="430" ht="12.75" customHeight="1"/>
-    <row r="431" ht="12.75" customHeight="1"/>
-    <row r="432" ht="12.75" customHeight="1"/>
-    <row r="433" ht="12.75" customHeight="1"/>
-    <row r="434" ht="12.75" customHeight="1"/>
-    <row r="435" ht="12.75" customHeight="1"/>
-    <row r="436" ht="12.75" customHeight="1"/>
-    <row r="437" ht="12.75" customHeight="1"/>
-    <row r="438" ht="12.75" customHeight="1"/>
-    <row r="439" ht="12.75" customHeight="1"/>
-    <row r="440" ht="12.75" customHeight="1"/>
-    <row r="441" ht="12.75" customHeight="1"/>
-    <row r="442" ht="12.75" customHeight="1"/>
-    <row r="443" ht="12.75" customHeight="1"/>
-    <row r="444" ht="12.75" customHeight="1"/>
-    <row r="445" ht="12.75" customHeight="1"/>
-    <row r="446" ht="12.75" customHeight="1"/>
-    <row r="447" ht="12.75" customHeight="1"/>
-    <row r="448" ht="12.75" customHeight="1"/>
-    <row r="449" ht="12.75" customHeight="1"/>
-    <row r="450" ht="12.75" customHeight="1"/>
-    <row r="451" ht="12.75" customHeight="1"/>
-    <row r="452" ht="12.75" customHeight="1"/>
-    <row r="453" ht="12.75" customHeight="1"/>
-    <row r="454" ht="12.75" customHeight="1"/>
-    <row r="455" ht="12.75" customHeight="1"/>
-    <row r="456" ht="12.75" customHeight="1"/>
-    <row r="457" ht="12.75" customHeight="1"/>
-    <row r="458" ht="12.75" customHeight="1"/>
-    <row r="459" ht="12.75" customHeight="1"/>
-    <row r="460" ht="12.75" customHeight="1"/>
-    <row r="461" ht="12.75" customHeight="1"/>
-    <row r="462" ht="12.75" customHeight="1"/>
-    <row r="463" ht="12.75" customHeight="1"/>
-    <row r="464" ht="12.75" customHeight="1"/>
-    <row r="465" ht="12.75" customHeight="1"/>
-    <row r="466" ht="12.75" customHeight="1"/>
-    <row r="467" ht="12.75" customHeight="1"/>
-    <row r="468" ht="12.75" customHeight="1"/>
-    <row r="469" ht="12.75" customHeight="1"/>
-    <row r="470" ht="12.75" customHeight="1"/>
-    <row r="471" ht="12.75" customHeight="1"/>
-    <row r="472" ht="12.75" customHeight="1"/>
-    <row r="473" ht="12.75" customHeight="1"/>
-    <row r="474" ht="12.75" customHeight="1"/>
-    <row r="475" ht="12.75" customHeight="1"/>
-    <row r="476" ht="12.75" customHeight="1"/>
-    <row r="477" ht="12.75" customHeight="1"/>
-    <row r="478" ht="12.75" customHeight="1"/>
-    <row r="479" ht="12.75" customHeight="1"/>
-    <row r="480" ht="12.75" customHeight="1"/>
-    <row r="481" ht="12.75" customHeight="1"/>
-    <row r="482" ht="12.75" customHeight="1"/>
-    <row r="483" ht="12.75" customHeight="1"/>
-    <row r="484" ht="12.75" customHeight="1"/>
-    <row r="485" ht="12.75" customHeight="1"/>
-    <row r="486" ht="12.75" customHeight="1"/>
-    <row r="487" ht="12.75" customHeight="1"/>
-    <row r="488" ht="12.75" customHeight="1"/>
-    <row r="489" ht="12.75" customHeight="1"/>
-    <row r="490" ht="12.75" customHeight="1"/>
-    <row r="491" ht="12.75" customHeight="1"/>
-    <row r="492" ht="12.75" customHeight="1"/>
-    <row r="493" ht="12.75" customHeight="1"/>
-    <row r="494" ht="12.75" customHeight="1"/>
-    <row r="495" ht="12.75" customHeight="1"/>
-    <row r="496" ht="12.75" customHeight="1"/>
-    <row r="497" ht="12.75" customHeight="1"/>
-    <row r="498" ht="12.75" customHeight="1"/>
-    <row r="499" ht="12.75" customHeight="1"/>
-    <row r="500" ht="12.75" customHeight="1"/>
-    <row r="501" ht="12.75" customHeight="1"/>
-    <row r="502" ht="12.75" customHeight="1"/>
-    <row r="503" ht="12.75" customHeight="1"/>
-    <row r="504" ht="12.75" customHeight="1"/>
-    <row r="505" ht="12.75" customHeight="1"/>
-    <row r="506" ht="12.75" customHeight="1"/>
-    <row r="507" ht="12.75" customHeight="1"/>
-    <row r="508" ht="12.75" customHeight="1"/>
-    <row r="509" ht="12.75" customHeight="1"/>
-    <row r="510" ht="12.75" customHeight="1"/>
-    <row r="511" ht="12.75" customHeight="1"/>
-    <row r="512" ht="12.75" customHeight="1"/>
-    <row r="513" ht="12.75" customHeight="1"/>
-    <row r="514" ht="12.75" customHeight="1"/>
-    <row r="515" ht="12.75" customHeight="1"/>
-    <row r="516" ht="12.75" customHeight="1"/>
-    <row r="517" ht="12.75" customHeight="1"/>
-    <row r="518" ht="12.75" customHeight="1"/>
-    <row r="519" ht="12.75" customHeight="1"/>
-    <row r="520" ht="12.75" customHeight="1"/>
-    <row r="521" ht="12.75" customHeight="1"/>
-    <row r="522" ht="12.75" customHeight="1"/>
-    <row r="523" ht="12.75" customHeight="1"/>
-    <row r="524" ht="12.75" customHeight="1"/>
-    <row r="525" ht="12.75" customHeight="1"/>
-    <row r="526" ht="12.75" customHeight="1"/>
-    <row r="527" ht="12.75" customHeight="1"/>
-    <row r="528" ht="12.75" customHeight="1"/>
-    <row r="529" ht="12.75" customHeight="1"/>
-    <row r="530" ht="12.75" customHeight="1"/>
-    <row r="531" ht="12.75" customHeight="1"/>
-    <row r="532" ht="12.75" customHeight="1"/>
-    <row r="533" ht="12.75" customHeight="1"/>
-    <row r="534" ht="12.75" customHeight="1"/>
-    <row r="535" ht="12.75" customHeight="1"/>
-    <row r="536" ht="12.75" customHeight="1"/>
-    <row r="537" ht="12.75" customHeight="1"/>
-    <row r="538" ht="12.75" customHeight="1"/>
-    <row r="539" ht="12.75" customHeight="1"/>
-    <row r="540" ht="12.75" customHeight="1"/>
-    <row r="541" ht="12.75" customHeight="1"/>
-    <row r="542" ht="12.75" customHeight="1"/>
-    <row r="543" ht="12.75" customHeight="1"/>
-    <row r="544" ht="12.75" customHeight="1"/>
-    <row r="545" ht="12.75" customHeight="1"/>
-    <row r="546" ht="12.75" customHeight="1"/>
-    <row r="547" ht="12.75" customHeight="1"/>
-    <row r="548" ht="12.75" customHeight="1"/>
-    <row r="549" ht="12.75" customHeight="1"/>
-    <row r="550" ht="12.75" customHeight="1"/>
-    <row r="551" ht="12.75" customHeight="1"/>
-    <row r="552" ht="12.75" customHeight="1"/>
-    <row r="553" ht="12.75" customHeight="1"/>
-    <row r="554" ht="12.75" customHeight="1"/>
-    <row r="555" ht="12.75" customHeight="1"/>
-    <row r="556" ht="12.75" customHeight="1"/>
-    <row r="557" ht="12.75" customHeight="1"/>
-    <row r="558" ht="12.75" customHeight="1"/>
-    <row r="559" ht="12.75" customHeight="1"/>
-    <row r="560" ht="12.75" customHeight="1"/>
-    <row r="561" ht="12.75" customHeight="1"/>
-    <row r="562" ht="12.75" customHeight="1"/>
-    <row r="563" ht="12.75" customHeight="1"/>
-    <row r="564" ht="12.75" customHeight="1"/>
-    <row r="565" ht="12.75" customHeight="1"/>
-    <row r="566" ht="12.75" customHeight="1"/>
-    <row r="567" ht="12.75" customHeight="1"/>
-    <row r="568" ht="12.75" customHeight="1"/>
-    <row r="569" ht="12.75" customHeight="1"/>
-    <row r="570" ht="12.75" customHeight="1"/>
-    <row r="571" ht="12.75" customHeight="1"/>
-    <row r="572" ht="12.75" customHeight="1"/>
-    <row r="573" ht="12.75" customHeight="1"/>
-    <row r="574" ht="12.75" customHeight="1"/>
-    <row r="575" ht="12.75" customHeight="1"/>
-    <row r="576" ht="12.75" customHeight="1"/>
-    <row r="577" ht="12.75" customHeight="1"/>
-    <row r="578" ht="12.75" customHeight="1"/>
-    <row r="579" ht="12.75" customHeight="1"/>
-    <row r="580" ht="12.75" customHeight="1"/>
-    <row r="581" ht="12.75" customHeight="1"/>
-    <row r="582" ht="12.75" customHeight="1"/>
-    <row r="583" ht="12.75" customHeight="1"/>
-    <row r="584" ht="12.75" customHeight="1"/>
-    <row r="585" ht="12.75" customHeight="1"/>
-    <row r="586" ht="12.75" customHeight="1"/>
-    <row r="587" ht="12.75" customHeight="1"/>
-    <row r="588" ht="12.75" customHeight="1"/>
-    <row r="589" ht="12.75" customHeight="1"/>
-    <row r="590" ht="12.75" customHeight="1"/>
-    <row r="591" ht="12.75" customHeight="1"/>
-    <row r="592" ht="12.75" customHeight="1"/>
-    <row r="593" ht="12.75" customHeight="1"/>
-    <row r="594" ht="12.75" customHeight="1"/>
-    <row r="595" ht="12.75" customHeight="1"/>
-    <row r="596" ht="12.75" customHeight="1"/>
-    <row r="597" ht="12.75" customHeight="1"/>
-    <row r="598" ht="12.75" customHeight="1"/>
-    <row r="599" ht="12.75" customHeight="1"/>
-    <row r="600" ht="12.75" customHeight="1"/>
-    <row r="601" ht="12.75" customHeight="1"/>
-    <row r="602" ht="12.75" customHeight="1"/>
-    <row r="603" ht="12.75" customHeight="1"/>
-    <row r="604" ht="12.75" customHeight="1"/>
-    <row r="605" ht="12.75" customHeight="1"/>
-    <row r="606" ht="12.75" customHeight="1"/>
-    <row r="607" ht="12.75" customHeight="1"/>
-    <row r="608" ht="12.75" customHeight="1"/>
-    <row r="609" ht="12.75" customHeight="1"/>
-    <row r="610" ht="12.75" customHeight="1"/>
-    <row r="611" ht="12.75" customHeight="1"/>
-    <row r="612" ht="12.75" customHeight="1"/>
-    <row r="613" ht="12.75" customHeight="1"/>
-    <row r="614" ht="12.75" customHeight="1"/>
-    <row r="615" ht="12.75" customHeight="1"/>
-    <row r="616" ht="12.75" customHeight="1"/>
-    <row r="617" ht="12.75" customHeight="1"/>
-    <row r="618" ht="12.75" customHeight="1"/>
-    <row r="619" ht="12.75" customHeight="1"/>
-    <row r="620" ht="12.75" customHeight="1"/>
-    <row r="621" ht="12.75" customHeight="1"/>
-    <row r="622" ht="12.75" customHeight="1"/>
-    <row r="623" ht="12.75" customHeight="1"/>
-    <row r="624" ht="12.75" customHeight="1"/>
-    <row r="625" ht="12.75" customHeight="1"/>
-    <row r="626" ht="12.75" customHeight="1"/>
-    <row r="627" ht="12.75" customHeight="1"/>
-    <row r="628" ht="12.75" customHeight="1"/>
-    <row r="629" ht="12.75" customHeight="1"/>
-    <row r="630" ht="12.75" customHeight="1"/>
-    <row r="631" ht="12.75" customHeight="1"/>
-    <row r="632" ht="12.75" customHeight="1"/>
-    <row r="633" ht="12.75" customHeight="1"/>
-    <row r="634" ht="12.75" customHeight="1"/>
-    <row r="635" ht="12.75" customHeight="1"/>
-    <row r="636" ht="12.75" customHeight="1"/>
-    <row r="637" ht="12.75" customHeight="1"/>
-    <row r="638" ht="12.75" customHeight="1"/>
-    <row r="639" ht="12.75" customHeight="1"/>
-    <row r="640" ht="12.75" customHeight="1"/>
-    <row r="641" ht="12.75" customHeight="1"/>
-    <row r="642" ht="12.75" customHeight="1"/>
-    <row r="643" ht="12.75" customHeight="1"/>
-    <row r="644" ht="12.75" customHeight="1"/>
-    <row r="645" ht="12.75" customHeight="1"/>
-    <row r="646" ht="12.75" customHeight="1"/>
-    <row r="647" ht="12.75" customHeight="1"/>
-    <row r="648" ht="12.75" customHeight="1"/>
-    <row r="649" ht="12.75" customHeight="1"/>
-    <row r="650" ht="12.75" customHeight="1"/>
-    <row r="651" ht="12.75" customHeight="1"/>
-    <row r="652" ht="12.75" customHeight="1"/>
-    <row r="653" ht="12.75" customHeight="1"/>
-    <row r="654" ht="12.75" customHeight="1"/>
-    <row r="655" ht="12.75" customHeight="1"/>
-    <row r="656" ht="12.75" customHeight="1"/>
-    <row r="657" ht="12.75" customHeight="1"/>
-    <row r="658" ht="12.75" customHeight="1"/>
-    <row r="659" ht="12.75" customHeight="1"/>
-    <row r="660" ht="12.75" customHeight="1"/>
-    <row r="661" ht="12.75" customHeight="1"/>
-    <row r="662" ht="12.75" customHeight="1"/>
-    <row r="663" ht="12.75" customHeight="1"/>
-    <row r="664" ht="12.75" customHeight="1"/>
-    <row r="665" ht="12.75" customHeight="1"/>
-    <row r="666" ht="12.75" customHeight="1"/>
-    <row r="667" ht="12.75" customHeight="1"/>
-    <row r="668" ht="12.75" customHeight="1"/>
-    <row r="669" ht="12.75" customHeight="1"/>
-    <row r="670" ht="12.75" customHeight="1"/>
-    <row r="671" ht="12.75" customHeight="1"/>
-    <row r="672" ht="12.75" customHeight="1"/>
-    <row r="673" ht="12.75" customHeight="1"/>
-    <row r="674" ht="12.75" customHeight="1"/>
-    <row r="675" ht="12.75" customHeight="1"/>
-    <row r="676" ht="12.75" customHeight="1"/>
-    <row r="677" ht="12.75" customHeight="1"/>
-    <row r="678" ht="12.75" customHeight="1"/>
-    <row r="679" ht="12.75" customHeight="1"/>
-    <row r="680" ht="12.75" customHeight="1"/>
-    <row r="681" ht="12.75" customHeight="1"/>
-    <row r="682" ht="12.75" customHeight="1"/>
-    <row r="683" ht="12.75" customHeight="1"/>
-    <row r="684" ht="12.75" customHeight="1"/>
-    <row r="685" ht="12.75" customHeight="1"/>
-    <row r="686" ht="12.75" customHeight="1"/>
-    <row r="687" ht="12.75" customHeight="1"/>
-    <row r="688" ht="12.75" customHeight="1"/>
-    <row r="689" ht="12.75" customHeight="1"/>
-    <row r="690" ht="12.75" customHeight="1"/>
-    <row r="691" ht="12.75" customHeight="1"/>
-    <row r="692" ht="12.75" customHeight="1"/>
-    <row r="693" ht="12.75" customHeight="1"/>
-    <row r="694" ht="12.75" customHeight="1"/>
-    <row r="695" ht="12.75" customHeight="1"/>
-    <row r="696" ht="12.75" customHeight="1"/>
-    <row r="697" ht="12.75" customHeight="1"/>
-    <row r="698" ht="12.75" customHeight="1"/>
-    <row r="699" ht="12.75" customHeight="1"/>
-    <row r="700" ht="12.75" customHeight="1"/>
-    <row r="701" ht="12.75" customHeight="1"/>
-    <row r="702" ht="12.75" customHeight="1"/>
-    <row r="703" ht="12.75" customHeight="1"/>
-    <row r="704" ht="12.75" customHeight="1"/>
-    <row r="705" ht="12.75" customHeight="1"/>
-    <row r="706" ht="12.75" customHeight="1"/>
-    <row r="707" ht="12.75" customHeight="1"/>
-    <row r="708" ht="12.75" customHeight="1"/>
-    <row r="709" ht="12.75" customHeight="1"/>
-    <row r="710" ht="12.75" customHeight="1"/>
-    <row r="711" ht="12.75" customHeight="1"/>
-    <row r="712" ht="12.75" customHeight="1"/>
-    <row r="713" ht="12.75" customHeight="1"/>
-    <row r="714" ht="12.75" customHeight="1"/>
-    <row r="715" ht="12.75" customHeight="1"/>
-    <row r="716" ht="12.75" customHeight="1"/>
-    <row r="717" ht="12.75" customHeight="1"/>
-    <row r="718" ht="12.75" customHeight="1"/>
-    <row r="719" ht="12.75" customHeight="1"/>
-    <row r="720" ht="12.75" customHeight="1"/>
-    <row r="721" ht="12.75" customHeight="1"/>
-    <row r="722" ht="12.75" customHeight="1"/>
-    <row r="723" ht="12.75" customHeight="1"/>
-    <row r="724" ht="12.75" customHeight="1"/>
-    <row r="725" ht="12.75" customHeight="1"/>
-    <row r="726" ht="12.75" customHeight="1"/>
-    <row r="727" ht="12.75" customHeight="1"/>
-    <row r="728" ht="12.75" customHeight="1"/>
-    <row r="729" ht="12.75" customHeight="1"/>
-    <row r="730" ht="12.75" customHeight="1"/>
-    <row r="731" ht="12.75" customHeight="1"/>
-    <row r="732" ht="12.75" customHeight="1"/>
-    <row r="733" ht="12.75" customHeight="1"/>
-    <row r="734" ht="12.75" customHeight="1"/>
-    <row r="735" ht="12.75" customHeight="1"/>
-    <row r="736" ht="12.75" customHeight="1"/>
-    <row r="737" ht="12.75" customHeight="1"/>
-    <row r="738" ht="12.75" customHeight="1"/>
-    <row r="739" ht="12.75" customHeight="1"/>
-    <row r="740" ht="12.75" customHeight="1"/>
-    <row r="741" ht="12.75" customHeight="1"/>
-    <row r="742" ht="12.75" customHeight="1"/>
-    <row r="743" ht="12.75" customHeight="1"/>
-    <row r="744" ht="12.75" customHeight="1"/>
-    <row r="745" ht="12.75" customHeight="1"/>
-    <row r="746" ht="12.75" customHeight="1"/>
-    <row r="747" ht="12.75" customHeight="1"/>
-    <row r="748" ht="12.75" customHeight="1"/>
-    <row r="749" ht="12.75" customHeight="1"/>
-    <row r="750" ht="12.75" customHeight="1"/>
-    <row r="751" ht="12.75" customHeight="1"/>
-    <row r="752" ht="12.75" customHeight="1"/>
-    <row r="753" ht="12.75" customHeight="1"/>
-    <row r="754" ht="12.75" customHeight="1"/>
-    <row r="755" ht="12.75" customHeight="1"/>
-    <row r="756" ht="12.75" customHeight="1"/>
-    <row r="757" ht="12.75" customHeight="1"/>
-    <row r="758" ht="12.75" customHeight="1"/>
-    <row r="759" ht="12.75" customHeight="1"/>
-    <row r="760" ht="12.75" customHeight="1"/>
-    <row r="761" ht="12.75" customHeight="1"/>
-    <row r="762" ht="12.75" customHeight="1"/>
-    <row r="763" ht="12.75" customHeight="1"/>
-    <row r="764" ht="12.75" customHeight="1"/>
-    <row r="765" ht="12.75" customHeight="1"/>
-    <row r="766" ht="12.75" customHeight="1"/>
-    <row r="767" ht="12.75" customHeight="1"/>
-    <row r="768" ht="12.75" customHeight="1"/>
-    <row r="769" ht="12.75" customHeight="1"/>
-    <row r="770" ht="12.75" customHeight="1"/>
-    <row r="771" ht="12.75" customHeight="1"/>
-    <row r="772" ht="12.75" customHeight="1"/>
-    <row r="773" ht="12.75" customHeight="1"/>
-    <row r="774" ht="12.75" customHeight="1"/>
-    <row r="775" ht="12.75" customHeight="1"/>
-    <row r="776" ht="12.75" customHeight="1"/>
-    <row r="777" ht="12.75" customHeight="1"/>
-    <row r="778" ht="12.75" customHeight="1"/>
-    <row r="779" ht="12.75" customHeight="1"/>
-    <row r="780" ht="12.75" customHeight="1"/>
-    <row r="781" ht="12.75" customHeight="1"/>
-    <row r="782" ht="12.75" customHeight="1"/>
-    <row r="783" ht="12.75" customHeight="1"/>
-    <row r="784" ht="12.75" customHeight="1"/>
-    <row r="785" ht="12.75" customHeight="1"/>
-    <row r="786" ht="12.75" customHeight="1"/>
-    <row r="787" ht="12.75" customHeight="1"/>
-    <row r="788" ht="12.75" customHeight="1"/>
-    <row r="789" ht="12.75" customHeight="1"/>
-    <row r="790" ht="12.75" customHeight="1"/>
-    <row r="791" ht="12.75" customHeight="1"/>
-    <row r="792" ht="12.75" customHeight="1"/>
-    <row r="793" ht="12.75" customHeight="1"/>
-    <row r="794" ht="12.75" customHeight="1"/>
-    <row r="795" ht="12.75" customHeight="1"/>
-    <row r="796" ht="12.75" customHeight="1"/>
-    <row r="797" ht="12.75" customHeight="1"/>
-    <row r="798" ht="12.75" customHeight="1"/>
-    <row r="799" ht="12.75" customHeight="1"/>
-    <row r="800" ht="12.75" customHeight="1"/>
-    <row r="801" ht="12.75" customHeight="1"/>
-    <row r="802" ht="12.75" customHeight="1"/>
-    <row r="803" ht="12.75" customHeight="1"/>
-    <row r="804" ht="12.75" customHeight="1"/>
-    <row r="805" ht="12.75" customHeight="1"/>
-    <row r="806" ht="12.75" customHeight="1"/>
-    <row r="807" ht="12.75" customHeight="1"/>
-    <row r="808" ht="12.75" customHeight="1"/>
-    <row r="809" ht="12.75" customHeight="1"/>
-    <row r="810" ht="12.75" customHeight="1"/>
-    <row r="811" ht="12.75" customHeight="1"/>
-    <row r="812" ht="12.75" customHeight="1"/>
-    <row r="813" ht="12.75" customHeight="1"/>
-    <row r="814" ht="12.75" customHeight="1"/>
-    <row r="815" ht="12.75" customHeight="1"/>
-    <row r="816" ht="12.75" customHeight="1"/>
-    <row r="817" ht="12.75" customHeight="1"/>
-    <row r="818" ht="12.75" customHeight="1"/>
-    <row r="819" ht="12.75" customHeight="1"/>
-    <row r="820" ht="12.75" customHeight="1"/>
-    <row r="821" ht="12.75" customHeight="1"/>
-    <row r="822" ht="12.75" customHeight="1"/>
-    <row r="823" ht="12.75" customHeight="1"/>
-    <row r="824" ht="12.75" customHeight="1"/>
-    <row r="825" ht="12.75" customHeight="1"/>
-    <row r="826" ht="12.75" customHeight="1"/>
-    <row r="827" ht="12.75" customHeight="1"/>
-    <row r="828" ht="12.75" customHeight="1"/>
-    <row r="829" ht="12.75" customHeight="1"/>
-    <row r="830" ht="12.75" customHeight="1"/>
-    <row r="831" ht="12.75" customHeight="1"/>
-    <row r="832" ht="12.75" customHeight="1"/>
-    <row r="833" ht="12.75" customHeight="1"/>
-    <row r="834" ht="12.75" customHeight="1"/>
-    <row r="835" ht="12.75" customHeight="1"/>
-    <row r="836" ht="12.75" customHeight="1"/>
-    <row r="837" ht="12.75" customHeight="1"/>
-    <row r="838" ht="12.75" customHeight="1"/>
-    <row r="839" ht="12.75" customHeight="1"/>
-    <row r="840" ht="12.75" customHeight="1"/>
-    <row r="841" ht="12.75" customHeight="1"/>
-    <row r="842" ht="12.75" customHeight="1"/>
-    <row r="843" ht="12.75" customHeight="1"/>
-    <row r="844" ht="12.75" customHeight="1"/>
-    <row r="845" ht="12.75" customHeight="1"/>
-    <row r="846" ht="12.75" customHeight="1"/>
-    <row r="847" ht="12.75" customHeight="1"/>
-    <row r="848" ht="12.75" customHeight="1"/>
-    <row r="849" ht="12.75" customHeight="1"/>
-    <row r="850" ht="12.75" customHeight="1"/>
-    <row r="851" ht="12.75" customHeight="1"/>
-    <row r="852" ht="12.75" customHeight="1"/>
-    <row r="853" ht="12.75" customHeight="1"/>
-    <row r="854" ht="12.75" customHeight="1"/>
-    <row r="855" ht="12.75" customHeight="1"/>
-    <row r="856" ht="12.75" customHeight="1"/>
-    <row r="857" ht="12.75" customHeight="1"/>
-    <row r="858" ht="12.75" customHeight="1"/>
-    <row r="859" ht="12.75" customHeight="1"/>
-    <row r="860" ht="12.75" customHeight="1"/>
-    <row r="861" ht="12.75" customHeight="1"/>
-    <row r="862" ht="12.75" customHeight="1"/>
-    <row r="863" ht="12.75" customHeight="1"/>
-    <row r="864" ht="12.75" customHeight="1"/>
-    <row r="865" ht="12.75" customHeight="1"/>
-    <row r="866" ht="12.75" customHeight="1"/>
-    <row r="867" ht="12.75" customHeight="1"/>
-    <row r="868" ht="12.75" customHeight="1"/>
-    <row r="869" ht="12.75" customHeight="1"/>
-    <row r="870" ht="12.75" customHeight="1"/>
-    <row r="871" ht="12.75" customHeight="1"/>
-    <row r="872" ht="12.75" customHeight="1"/>
-    <row r="873" ht="12.75" customHeight="1"/>
-    <row r="874" ht="12.75" customHeight="1"/>
-    <row r="875" ht="12.75" customHeight="1"/>
-    <row r="876" ht="12.75" customHeight="1"/>
-    <row r="877" ht="12.75" customHeight="1"/>
-    <row r="878" ht="12.75" customHeight="1"/>
-    <row r="879" ht="12.75" customHeight="1"/>
-    <row r="880" ht="12.75" customHeight="1"/>
-    <row r="881" ht="12.75" customHeight="1"/>
-    <row r="882" ht="12.75" customHeight="1"/>
-    <row r="883" ht="12.75" customHeight="1"/>
-    <row r="884" ht="12.75" customHeight="1"/>
-    <row r="885" ht="12.75" customHeight="1"/>
-    <row r="886" ht="12.75" customHeight="1"/>
-    <row r="887" ht="12.75" customHeight="1"/>
-    <row r="888" ht="12.75" customHeight="1"/>
-    <row r="889" ht="12.75" customHeight="1"/>
-    <row r="890" ht="12.75" customHeight="1"/>
-    <row r="891" ht="12.75" customHeight="1"/>
-    <row r="892" ht="12.75" customHeight="1"/>
-    <row r="893" ht="12.75" customHeight="1"/>
-    <row r="894" ht="12.75" customHeight="1"/>
-    <row r="895" ht="12.75" customHeight="1"/>
-    <row r="896" ht="12.75" customHeight="1"/>
-    <row r="897" ht="12.75" customHeight="1"/>
-    <row r="898" ht="12.75" customHeight="1"/>
-    <row r="899" ht="12.75" customHeight="1"/>
-    <row r="900" ht="12.75" customHeight="1"/>
-    <row r="901" ht="12.75" customHeight="1"/>
-    <row r="902" ht="12.75" customHeight="1"/>
-    <row r="903" ht="12.75" customHeight="1"/>
-    <row r="904" ht="12.75" customHeight="1"/>
-    <row r="905" ht="12.75" customHeight="1"/>
-    <row r="906" ht="12.75" customHeight="1"/>
-    <row r="907" ht="12.75" customHeight="1"/>
-    <row r="908" ht="12.75" customHeight="1"/>
-    <row r="909" ht="12.75" customHeight="1"/>
-    <row r="910" ht="12.75" customHeight="1"/>
-    <row r="911" ht="12.75" customHeight="1"/>
-    <row r="912" ht="12.75" customHeight="1"/>
-    <row r="913" ht="12.75" customHeight="1"/>
-    <row r="914" ht="12.75" customHeight="1"/>
-    <row r="915" ht="12.75" customHeight="1"/>
-    <row r="916" ht="12.75" customHeight="1"/>
-    <row r="917" ht="12.75" customHeight="1"/>
-    <row r="918" ht="12.75" customHeight="1"/>
-    <row r="919" ht="12.75" customHeight="1"/>
-    <row r="920" ht="12.75" customHeight="1"/>
-    <row r="921" ht="12.75" customHeight="1"/>
-    <row r="922" ht="12.75" customHeight="1"/>
-    <row r="923" ht="12.75" customHeight="1"/>
-    <row r="924" ht="12.75" customHeight="1"/>
-    <row r="925" ht="12.75" customHeight="1"/>
-    <row r="926" ht="12.75" customHeight="1"/>
-    <row r="927" ht="12.75" customHeight="1"/>
-    <row r="928" ht="12.75" customHeight="1"/>
-    <row r="929" ht="12.75" customHeight="1"/>
-    <row r="930" ht="12.75" customHeight="1"/>
-    <row r="931" ht="12.75" customHeight="1"/>
-    <row r="932" ht="12.75" customHeight="1"/>
-    <row r="933" ht="12.75" customHeight="1"/>
-    <row r="934" ht="12.75" customHeight="1"/>
-    <row r="935" ht="12.75" customHeight="1"/>
-    <row r="936" ht="12.75" customHeight="1"/>
-    <row r="937" ht="12.75" customHeight="1"/>
-    <row r="938" ht="12.75" customHeight="1"/>
-    <row r="939" ht="12.75" customHeight="1"/>
-    <row r="940" ht="12.75" customHeight="1"/>
-    <row r="941" ht="12.75" customHeight="1"/>
-    <row r="942" ht="12.75" customHeight="1"/>
-    <row r="943" ht="12.75" customHeight="1"/>
-    <row r="944" ht="12.75" customHeight="1"/>
-    <row r="945" ht="12.75" customHeight="1"/>
-    <row r="946" ht="12.75" customHeight="1"/>
-    <row r="947" ht="12.75" customHeight="1"/>
-    <row r="948" ht="12.75" customHeight="1"/>
-    <row r="949" ht="12.75" customHeight="1"/>
-    <row r="950" ht="12.75" customHeight="1"/>
-    <row r="951" ht="12.75" customHeight="1"/>
-    <row r="952" ht="12.75" customHeight="1"/>
-    <row r="953" ht="12.75" customHeight="1"/>
-    <row r="954" ht="12.75" customHeight="1"/>
-    <row r="955" ht="12.75" customHeight="1"/>
-    <row r="956" ht="12.75" customHeight="1"/>
-    <row r="957" ht="12.75" customHeight="1"/>
-    <row r="958" ht="12.75" customHeight="1"/>
-    <row r="959" ht="12.75" customHeight="1"/>
-    <row r="960" ht="12.75" customHeight="1"/>
-    <row r="961" ht="12.75" customHeight="1"/>
-    <row r="962" ht="12.75" customHeight="1"/>
-    <row r="963" ht="12.75" customHeight="1"/>
-    <row r="964" ht="12.75" customHeight="1"/>
-    <row r="965" ht="12.75" customHeight="1"/>
-    <row r="966" ht="12.75" customHeight="1"/>
-    <row r="967" ht="12.75" customHeight="1"/>
-    <row r="968" ht="12.75" customHeight="1"/>
-    <row r="969" ht="12.75" customHeight="1"/>
-    <row r="970" ht="12.75" customHeight="1"/>
-    <row r="971" ht="12.75" customHeight="1"/>
-    <row r="972" ht="12.75" customHeight="1"/>
-    <row r="973" ht="12.75" customHeight="1"/>
-    <row r="974" ht="12.75" customHeight="1"/>
-    <row r="975" ht="12.75" customHeight="1"/>
-    <row r="976" ht="12.75" customHeight="1"/>
-    <row r="977" ht="12.75" customHeight="1"/>
-    <row r="978" ht="12.75" customHeight="1"/>
-    <row r="979" ht="12.75" customHeight="1"/>
-    <row r="980" ht="12.75" customHeight="1"/>
-    <row r="981" ht="12.75" customHeight="1"/>
-    <row r="982" ht="12.75" customHeight="1"/>
-    <row r="983" ht="12.75" customHeight="1"/>
-    <row r="984" ht="12.75" customHeight="1"/>
-    <row r="985" ht="12.75" customHeight="1"/>
-    <row r="986" ht="12.75" customHeight="1"/>
-    <row r="987" ht="12.75" customHeight="1"/>
-    <row r="988" ht="12.75" customHeight="1"/>
-    <row r="989" ht="12.75" customHeight="1"/>
-    <row r="990" ht="12.75" customHeight="1"/>
-    <row r="991" ht="12.75" customHeight="1"/>
-    <row r="992" ht="12.75" customHeight="1"/>
-    <row r="993" ht="12.75" customHeight="1"/>
-    <row r="994" ht="12.75" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B70C3665-E52C-464E-B22A-6BC197D77956}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J994"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="56"/>
-      <c r="H1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="57" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="39">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="43"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="49"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="44"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="96" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="88"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="75"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="97"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="49"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="100"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="49"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="100"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="49"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="100"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="49"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="100"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="49"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="100"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="49"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="100"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="75"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="94" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="75"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A17" s="93" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="106"/>
-      <c r="C17" s="107"/>
-      <c r="D17" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="85"/>
+      <c r="H17" s="39"/>
       <c r="I17" s="108"/>
       <c r="J17" s="109"/>
     </row>
@@ -11573,6 +10293,1289 @@
   <mergeCells count="19">
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B70C3665-E52C-464E-B22A-6BC197D77956}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J994"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="91" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="63"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="78"/>
+      <c r="H2" s="90">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="73"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="102" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="103" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="44"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="49"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="104"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="106"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="107"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="107"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="107"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="107"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="107"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="107"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="49"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="48"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="96" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="48"/>
+      <c r="J16" s="49"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="94"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" s="39"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="109"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -11587,9 +11590,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11609,186 +11609,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="55" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="55" t="s">
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="55" t="s">
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="55" t="s">
+      <c r="P1" s="63"/>
+      <c r="Q1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="56"/>
-      <c r="S1" s="55" t="s">
+      <c r="R1" s="63"/>
+      <c r="S1" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="88"/>
+      <c r="T1" s="44"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="57" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="57" t="s">
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="99"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="106"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="100"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="107"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="114"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="118"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="87" t="s">
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="81"/>
-      <c r="R5" s="81"/>
-      <c r="S5" s="81"/>
-      <c r="T5" s="88"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="44"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="74" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="75"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="49"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="74" t="s">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="62"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="62"/>
-      <c r="T7" s="75"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="49"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11987,37 +11987,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="63"/>
+      <c r="B15" s="65"/>
       <c r="C15" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="63"/>
-      <c r="E15" s="101" t="s">
+      <c r="D15" s="65"/>
+      <c r="E15" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="63"/>
-      <c r="G15" s="101" t="s">
+      <c r="F15" s="65"/>
+      <c r="G15" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="62"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="101" t="s">
+      <c r="H15" s="48"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="63"/>
-      <c r="L15" s="101" t="s">
+      <c r="K15" s="65"/>
+      <c r="L15" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="62"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="101" t="s">
+      <c r="M15" s="48"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="63"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="65"/>
       <c r="R15" s="15" t="s">
         <v>48</v>
       </c>
@@ -12029,37 +12029,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="115">
+      <c r="A16" s="110">
         <v>1</v>
       </c>
-      <c r="B16" s="63"/>
-      <c r="C16" s="116" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="63"/>
-      <c r="E16" s="116" t="s">
+      <c r="D16" s="65"/>
+      <c r="E16" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="63"/>
-      <c r="G16" s="110" t="s">
+      <c r="F16" s="65"/>
+      <c r="G16" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="62"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="110" t="s">
+      <c r="H16" s="48"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="116" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="63"/>
-      <c r="L16" s="112" t="s">
+      <c r="K16" s="65"/>
+      <c r="L16" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="62"/>
-      <c r="N16" s="63"/>
-      <c r="O16" s="112" t="s">
+      <c r="M16" s="48"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="62"/>
-      <c r="Q16" s="63"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="65"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12071,37 +12071,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="115">
+      <c r="A17" s="110">
         <v>2</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="116" t="s">
+      <c r="B17" s="65"/>
+      <c r="C17" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="63"/>
-      <c r="E17" s="116" t="s">
+      <c r="D17" s="65"/>
+      <c r="E17" s="111" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="63"/>
-      <c r="G17" s="110" t="s">
+      <c r="F17" s="65"/>
+      <c r="G17" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="62"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="110" t="s">
+      <c r="H17" s="48"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="116" t="s">
         <v>60</v>
       </c>
-      <c r="K17" s="63"/>
-      <c r="L17" s="112" t="s">
+      <c r="K17" s="65"/>
+      <c r="L17" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="62"/>
-      <c r="N17" s="63"/>
-      <c r="O17" s="112" t="s">
+      <c r="M17" s="48"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="P17" s="62"/>
-      <c r="Q17" s="63"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="65"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12113,23 +12113,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="112"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="63"/>
+      <c r="A18" s="110"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="116"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="114"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="65"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -12141,23 +12141,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="115"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="63"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="62"/>
-      <c r="Q19" s="63"/>
+      <c r="A19" s="110"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="114"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="65"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -12169,23 +12169,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="115"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="112"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="63"/>
+      <c r="A20" s="110"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="116"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="114"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="65"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -12197,23 +12197,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="115"/>
-      <c r="B21" s="63"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="112"/>
-      <c r="P21" s="62"/>
-      <c r="Q21" s="63"/>
+      <c r="A21" s="110"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="116"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="65"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -12225,23 +12225,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="115"/>
-      <c r="B22" s="63"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="110"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="112"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="112"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="63"/>
+      <c r="A22" s="110"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="116"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="114"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="65"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -12253,23 +12253,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="115"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="116"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="112"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="63"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="63"/>
+      <c r="A23" s="110"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="111"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="114"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="65"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -12281,23 +12281,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="115"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="116"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="116"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="112"/>
-      <c r="M24" s="62"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="62"/>
-      <c r="Q24" s="63"/>
+      <c r="A24" s="110"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="114"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="114"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="65"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -12309,23 +12309,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="115"/>
-      <c r="B25" s="63"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="116"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="63"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="63"/>
-      <c r="L25" s="112"/>
-      <c r="M25" s="62"/>
-      <c r="N25" s="63"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="62"/>
-      <c r="Q25" s="63"/>
+      <c r="A25" s="110"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="116"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="116"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="65"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -12337,23 +12337,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="115"/>
-      <c r="B26" s="63"/>
-      <c r="C26" s="116"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="63"/>
-      <c r="L26" s="112"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="62"/>
-      <c r="Q26" s="63"/>
+      <c r="A26" s="110"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="114"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="65"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -12365,23 +12365,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="115"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="112"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="63"/>
+      <c r="A27" s="110"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="65"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -12393,23 +12393,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="115"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="116"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="112"/>
-      <c r="M28" s="62"/>
-      <c r="N28" s="63"/>
-      <c r="O28" s="112"/>
-      <c r="P28" s="62"/>
-      <c r="Q28" s="63"/>
+      <c r="A28" s="110"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="116"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="116"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="65"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -12421,23 +12421,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="115"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="116"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="110"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="63"/>
-      <c r="L29" s="112"/>
-      <c r="M29" s="62"/>
-      <c r="N29" s="63"/>
-      <c r="O29" s="112"/>
-      <c r="P29" s="62"/>
-      <c r="Q29" s="63"/>
+      <c r="A29" s="110"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="111"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="111"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="116"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="116"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="114"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="65"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -12449,23 +12449,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="115"/>
-      <c r="B30" s="63"/>
-      <c r="C30" s="116"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="110"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="110"/>
-      <c r="K30" s="63"/>
-      <c r="L30" s="112"/>
-      <c r="M30" s="62"/>
-      <c r="N30" s="63"/>
-      <c r="O30" s="112"/>
-      <c r="P30" s="62"/>
-      <c r="Q30" s="63"/>
+      <c r="A30" s="110"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="111"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="111"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="116"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="116"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="114"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="65"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -12477,23 +12477,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="118"/>
-      <c r="B31" s="78"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="113"/>
-      <c r="M31" s="77"/>
-      <c r="N31" s="78"/>
-      <c r="O31" s="113"/>
-      <c r="P31" s="77"/>
-      <c r="Q31" s="78"/>
+      <c r="A31" s="112"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="113"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="119"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="119"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="115"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="52"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -13491,6 +13491,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -13515,118 +13627,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク登録機能.xlsx
+++ b/document/成果物ドキュメント_タスク登録機能.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96654957-C9C2-4091-B8FF-AC2E6B4F602F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -1516,46 +1516,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1570,44 +1591,77 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1627,47 +1681,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1675,7 +1723,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1687,17 +1741,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1705,59 +1753,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2313,85 +2313,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2411,46 +2411,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="88" t="s">
+      <c r="E8" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="84" t="s">
+      <c r="G13" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="65"/>
-      <c r="I13" s="89">
+      <c r="H13" s="41"/>
+      <c r="I13" s="84">
         <v>46127</v>
       </c>
-      <c r="J13" s="48"/>
-      <c r="K13" s="65"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="41"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="84"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="65"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="41"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="84"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="65"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2459,13 +2459,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="85" t="s">
+      <c r="G17" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3479,19 +3479,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -3503,192 +3503,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
+      <c r="G2" s="50"/>
+      <c r="H2" s="85">
         <v>46121</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="42" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="44"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="68"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="45" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="47"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="104"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="45" t="s">
+      <c r="B7" s="40"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="73"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="45" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="49"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="73"/>
     </row>
     <row r="9" spans="1:10" ht="93.75" customHeight="1">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="50" t="s">
+      <c r="C9" s="41"/>
+      <c r="D9" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="73"/>
     </row>
     <row r="10" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A10" s="67"/>
-      <c r="B10" s="69" t="s">
+      <c r="A10" s="99"/>
+      <c r="B10" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="50" t="s">
+      <c r="C10" s="41"/>
+      <c r="D10" s="105" t="s">
         <v>108</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="49"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="73"/>
     </row>
     <row r="11" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69" t="s">
+      <c r="A11" s="100"/>
+      <c r="B11" s="94" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="50" t="s">
+      <c r="C11" s="41"/>
+      <c r="D11" s="105" t="s">
         <v>109</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="73"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="45" t="s">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="49"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="73"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="41"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="102"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4679,17 +4679,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4698,14 +4695,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4724,19 +4724,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -4748,48 +4748,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="90">
+      <c r="G2" s="50"/>
+      <c r="H2" s="106">
         <v>46125</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6143,19 +6143,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -6167,48 +6167,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="90">
+      <c r="G2" s="50"/>
+      <c r="H2" s="106">
         <v>46125</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7557,19 +7557,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7581,190 +7581,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="90">
+      <c r="G2" s="50"/>
+      <c r="H2" s="106">
         <v>46121</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="103" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="109" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="44"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="68"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="73"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="104"/>
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="106"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="107"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="107"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="107"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="107"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="107"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="107"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="92" t="s">
+      <c r="A14" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="49"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="73"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="45" t="s">
+      <c r="B15" s="40"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
@@ -7773,11 +7773,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -7790,18 +7790,18 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="96" t="s">
+      <c r="H16" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="48"/>
-      <c r="J16" s="49"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="73"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="65"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="17" t="s">
         <v>78</v>
       </c>
@@ -7812,18 +7812,18 @@
         <v>77</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="I17" s="48"/>
-      <c r="J17" s="49"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="73"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="65"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="17" t="s">
         <v>79</v>
       </c>
@@ -7834,16 +7834,16 @@
         <v>93</v>
       </c>
       <c r="G18" s="18"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="49"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="73"/>
     </row>
     <row r="19" spans="1:10" ht="19.350000000000001" customHeight="1">
-      <c r="A19" s="99" t="s">
+      <c r="A19" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="65"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="17" t="s">
         <v>80</v>
       </c>
@@ -7856,18 +7856,18 @@
       <c r="G19" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="H19" s="50" t="s">
+      <c r="H19" s="105" t="s">
         <v>113</v>
       </c>
-      <c r="I19" s="48"/>
-      <c r="J19" s="49"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="73"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="99" t="s">
+      <c r="A20" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="48"/>
-      <c r="C20" s="65"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="17" t="s">
         <v>83</v>
       </c>
@@ -7878,16 +7878,16 @@
         <v>94</v>
       </c>
       <c r="G20" s="18"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="49"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="73"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="65"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="17" t="s">
         <v>84</v>
       </c>
@@ -7898,16 +7898,16 @@
         <v>90</v>
       </c>
       <c r="G21" s="18"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="49"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="73"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="99" t="s">
+      <c r="A22" s="108" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="100"/>
-      <c r="C22" s="101"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="117"/>
       <c r="D22" s="17" t="s">
         <v>85</v>
       </c>
@@ -7920,18 +7920,18 @@
       <c r="G22" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="72" t="s">
         <v>116</v>
       </c>
-      <c r="I22" s="97"/>
-      <c r="J22" s="98"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="115"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="93" t="s">
+      <c r="A23" s="111" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="94"/>
-      <c r="C23" s="95"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="19" t="s">
         <v>92</v>
       </c>
@@ -7942,37 +7942,37 @@
       <c r="G23" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="41"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="102"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="92" t="s">
+      <c r="A24" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="49"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="73"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="92" t="s">
+      <c r="A25" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="45" t="s">
+      <c r="B25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="65"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
       <c r="I25" s="15" t="s">
         <v>24</v>
       </c>
@@ -7981,11 +7981,11 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="92" t="s">
+      <c r="A26" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="65"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41"/>
       <c r="D26" s="15" t="s">
         <v>26</v>
       </c>
@@ -7998,18 +7998,18 @@
       <c r="G26" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="96" t="s">
+      <c r="H26" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="48"/>
-      <c r="J26" s="49"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="73"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A27" s="93" t="s">
+      <c r="A27" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="94"/>
-      <c r="C27" s="95"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="113"/>
       <c r="D27" s="19" t="s">
         <v>112</v>
       </c>
@@ -8020,9 +8020,9 @@
       <c r="G27" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="41"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="102"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8992,25 +8992,13 @@
     <row r="993" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="H19:J19"/>
@@ -9023,13 +9011,25 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9053,19 +9053,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9077,190 +9077,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="90">
+      <c r="G2" s="50"/>
+      <c r="H2" s="106">
         <v>46125</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="103" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="109" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="44"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="68"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="73"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="104"/>
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="106"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="107"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="107"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="107"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="107"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="107"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="107"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="92" t="s">
+      <c r="A14" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="49"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="73"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="45" t="s">
+      <c r="B15" s="40"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
@@ -9269,11 +9269,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -9286,18 +9286,18 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="96" t="s">
+      <c r="H16" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="48"/>
-      <c r="J16" s="49"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="73"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A17" s="93" t="s">
+      <c r="A17" s="111" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="94"/>
-      <c r="C17" s="95"/>
+      <c r="B17" s="112"/>
+      <c r="C17" s="113"/>
       <c r="D17" s="19" t="s">
         <v>112</v>
       </c>
@@ -9308,9 +9308,9 @@
       <c r="G17" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="109"/>
+      <c r="H17" s="101"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="119"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10291,13 +10291,6 @@
     <row r="994" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -10310,6 +10303,13 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10333,19 +10333,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="67"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10357,190 +10357,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="90">
+      <c r="G2" s="50"/>
+      <c r="H2" s="106">
         <v>46125</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="103" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="109" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="44"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="68"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="73"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="104"/>
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="106"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="107"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="107"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="107"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="107"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="107"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="107"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="92" t="s">
+      <c r="A14" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="49"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="73"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="45" t="s">
+      <c r="B15" s="40"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="65"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
@@ -10549,11 +10549,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="65"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -10566,18 +10566,18 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="96" t="s">
+      <c r="H16" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="48"/>
-      <c r="J16" s="49"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="73"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A17" s="93" t="s">
+      <c r="A17" s="111" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="94"/>
-      <c r="C17" s="95"/>
+      <c r="B17" s="112"/>
+      <c r="C17" s="113"/>
       <c r="D17" s="19" t="s">
         <v>111</v>
       </c>
@@ -10588,9 +10588,9 @@
       <c r="G17" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="109"/>
+      <c r="H17" s="101"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="119"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11571,16 +11571,8 @@
     <row r="994" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -11588,8 +11580,16 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11609,186 +11609,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="76" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="76" t="s">
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="76" t="s">
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="76" t="s">
+      <c r="P1" s="67"/>
+      <c r="Q1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="63"/>
-      <c r="S1" s="76" t="s">
+      <c r="R1" s="67"/>
+      <c r="S1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="44"/>
+      <c r="T1" s="68"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="77" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="77" t="s">
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="106"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="57"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="107"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="58"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="118"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="54"/>
+      <c r="T4" s="59"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="42" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="44"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="66"/>
+      <c r="S5" s="66"/>
+      <c r="T5" s="68"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="45" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="49"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="73"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="45" t="s">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="49"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="73"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11987,37 +11987,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="117" t="s">
+      <c r="B15" s="41"/>
+      <c r="C15" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="96" t="s">
+      <c r="D15" s="41"/>
+      <c r="E15" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="96" t="s">
+      <c r="F15" s="41"/>
+      <c r="G15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="96" t="s">
+      <c r="H15" s="40"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="96" t="s">
+      <c r="K15" s="41"/>
+      <c r="L15" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="48"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="96" t="s">
+      <c r="M15" s="40"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="65"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="41"/>
       <c r="R15" s="15" t="s">
         <v>48</v>
       </c>
@@ -12029,37 +12029,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="110">
+      <c r="A16" s="74">
         <v>1</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="111" t="s">
+      <c r="B16" s="41"/>
+      <c r="C16" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="111" t="s">
+      <c r="D16" s="41"/>
+      <c r="E16" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="116" t="s">
+      <c r="F16" s="41"/>
+      <c r="G16" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="48"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="116" t="s">
+      <c r="H16" s="40"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="114" t="s">
+      <c r="K16" s="41"/>
+      <c r="L16" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="48"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="114" t="s">
+      <c r="M16" s="40"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="41"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12071,37 +12071,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="110">
+      <c r="A17" s="74">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="111" t="s">
+      <c r="B17" s="41"/>
+      <c r="C17" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="111" t="s">
+      <c r="D17" s="41"/>
+      <c r="E17" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="116" t="s">
+      <c r="F17" s="41"/>
+      <c r="G17" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="48"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="116" t="s">
+      <c r="H17" s="40"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="114" t="s">
+      <c r="K17" s="41"/>
+      <c r="L17" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="48"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="114" t="s">
+      <c r="M17" s="40"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="65"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="41"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12113,23 +12113,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="110"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="114"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="114"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="65"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="41"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -12141,23 +12141,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="110"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="114"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="114"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="65"/>
+      <c r="A19" s="74"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="41"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -12169,23 +12169,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="110"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="114"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="74"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="41"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -12197,23 +12197,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="110"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="114"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="74"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="41"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -12225,23 +12225,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="110"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="114"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="74"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="46"/>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="41"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -12253,23 +12253,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="110"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="111"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="116"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="114"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="114"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="74"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="41"/>
+      <c r="O23" s="46"/>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="41"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -12281,23 +12281,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="110"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="111"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="116"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="114"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="114"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="74"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="41"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -12309,23 +12309,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="110"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="111"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="116"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="114"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="114"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="40"/>
+      <c r="Q25" s="41"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -12337,23 +12337,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="110"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="111"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="114"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="74"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="40"/>
+      <c r="Q26" s="41"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -12365,23 +12365,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="110"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="111"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="74"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="40"/>
+      <c r="Q27" s="41"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -12393,23 +12393,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="110"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="111"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="114"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="114"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="74"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="41"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -12421,23 +12421,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="110"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="111"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="114"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="114"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="41"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -12449,23 +12449,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="110"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="111"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="111"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="116"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="116"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="114"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="114"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="40"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="41"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -12477,23 +12477,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="112"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="113"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="113"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="119"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="119"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="115"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="115"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="52"/>
+      <c r="A31" s="77"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="78"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="47"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="47"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="45"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -13491,62 +13491,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -13571,62 +13571,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
